--- a/Kameraman_metadata.xlsx
+++ b/Kameraman_metadata.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\04-PROJELER\EU PROJECT\02_DATA\Mediterranean\00_ALL_SPRING_LIST\02_discharge_edited\01_Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/selimcalli/Documents/onemli belgeler/04-PROJELER/EU PROJECT/02_DATA/Mediterranean/00_ALL_SPRING_LIST/02_discharge_edited/01_Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E755788D-1259-A649-9FA3-453A52692AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7665"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="368">
   <si>
     <t>Region</t>
   </si>
@@ -90,6 +91,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>www.ehyd.gv.at</t>
     </r>
@@ -340,6 +342,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://apps.arpa.umbria.it/acqua/contenuto/portata-delle-Sorgenti</t>
     </r>
@@ -354,6 +357,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://apps.arpa.umbria.it/acqua/contenuto/portata-delle-Sorgenti</t>
     </r>
@@ -368,6 +372,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://apps.arpa.umbria.it/acqua/contenuto/portata-delle-Sorgenti</t>
     </r>
@@ -382,6 +387,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://apps.arpa.umbria.it/acqua/contenuto/portata-delle-Sorgenti</t>
     </r>
@@ -516,6 +522,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.hidmet.gov.rs/data/hidro_pov_godisnjaci/</t>
     </r>
@@ -539,6 +546,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://isvs.chmi.cz/ords/f?p=11002:2:113580288468140:::RP,2:P2_SEQ:%5C759%5C</t>
     </r>
@@ -562,6 +570,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">HIDROLOŠKI GODIŠNJAK, </t>
     </r>
@@ -571,6 +580,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.fhmzbih.gov.ba/latinica/HIDRO/godisnjaci.php#</t>
     </r>
@@ -588,6 +598,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">HIDROLOŠKI GODIŠNJAK, </t>
     </r>
@@ -597,6 +608,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.fhmzbih.gov.ba/latinica/HIDRO/godisnjaci.php#</t>
     </r>
@@ -611,6 +623,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">HIDROLOŠKI GODIŠNJAK, </t>
     </r>
@@ -620,6 +633,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.fhmzbih.gov.ba/latinica/HIDRO/godisnjaci.php#</t>
     </r>
@@ -649,6 +663,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://hidro.dhz.hr/</t>
     </r>
@@ -663,6 +678,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://hidro.dhz.hr/</t>
     </r>
@@ -677,6 +693,7 @@
         <sz val="12"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://hidro.dhz.hr/</t>
     </r>
@@ -909,6 +926,7 @@
         <sz val="11"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>www.dsi.gov.tr</t>
     </r>
@@ -923,6 +941,7 @@
         <sz val="11"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>www.dsi.gov.tr</t>
     </r>
@@ -937,6 +956,7 @@
         <sz val="11"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>www.dsi.gov.tr</t>
     </r>
@@ -1333,12 +1353,27 @@
   </si>
   <si>
     <t>Hourly</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Pasnyag</t>
+  </si>
+  <si>
+    <t>Nagy-Tohonya</t>
+  </si>
+  <si>
+    <t>Lófej</t>
+  </si>
+  <si>
+    <t>Kis-Tohonya</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="d\.m\.yyyy"/>
@@ -1346,7 +1381,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1358,44 +1393,52 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1413,54 +1456,63 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1483,6 +1535,7 @@
       <sz val="12"/>
       <color rgb="FF1155CC"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1504,6 +1557,7 @@
       <sz val="11"/>
       <color rgb="FF1155CC"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1521,8 +1575,14 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1637,8 +1697,14 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1714,85 +1780,125 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+  <cellXfs count="127">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1802,8 +1908,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1817,8 +1922,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1828,20 +1932,15 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1851,29 +1950,14 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1883,27 +1967,8 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1913,8 +1978,8 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1924,21 +1989,18 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1951,8 +2013,8 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1962,10 +2024,10 @@
     <xf numFmtId="0" fontId="3" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1978,18 +2040,13 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2026,6 +2083,23 @@
     <xf numFmtId="166" fontId="3" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2240,22 +2314,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P121"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:P125"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="45.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="13" max="13" width="70.140625" customWidth="1"/>
-    <col min="14" max="14" width="28.28515625" customWidth="1"/>
-    <col min="15" max="15" width="158.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.28515625" customWidth="1"/>
+    <col min="13" max="13" width="70.1640625" customWidth="1"/>
+    <col min="14" max="14" width="28.33203125" customWidth="1"/>
+    <col min="15" max="15" width="158.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1">
@@ -2324,35 +2398,35 @@
       <c r="E2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="135">
+      <c r="F2" s="106">
         <v>47.36</v>
       </c>
-      <c r="G2" s="135">
+      <c r="G2" s="106">
         <v>10.172000000000001</v>
       </c>
       <c r="H2" s="12">
         <v>1078</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="14">
+      <c r="I2" s="10"/>
+      <c r="J2" s="13">
         <v>36161</v>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="14">
         <v>44926</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="131" t="s">
+      <c r="P2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2372,35 +2446,35 @@
       <c r="E3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="135">
+      <c r="F3" s="106">
         <v>47.670999999999999</v>
       </c>
-      <c r="G3" s="135">
+      <c r="G3" s="106">
         <v>12.188000000000001</v>
       </c>
       <c r="H3" s="12">
         <v>471</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14">
+      <c r="I3" s="10"/>
+      <c r="J3" s="13">
         <v>33843</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="14">
         <v>44926</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="131" t="s">
+      <c r="P3" t="s">
         <v>245</v>
       </c>
     </row>
@@ -2420,35 +2494,35 @@
       <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="135">
+      <c r="F4" s="106">
         <v>47.807000000000002</v>
       </c>
-      <c r="G4" s="135">
+      <c r="G4" s="106">
         <v>14.096</v>
       </c>
       <c r="H4" s="12">
         <v>538</v>
       </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="14">
+      <c r="I4" s="10"/>
+      <c r="J4" s="13">
         <v>27760</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="14">
         <v>44926</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="N4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="131" t="s">
+      <c r="P4" t="s">
         <v>246</v>
       </c>
     </row>
@@ -2468,35 +2542,35 @@
       <c r="E5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="135">
+      <c r="F5" s="106">
         <v>47.545000000000002</v>
       </c>
-      <c r="G5" s="135">
+      <c r="G5" s="106">
         <v>13.332000000000001</v>
       </c>
       <c r="H5" s="12">
         <v>710</v>
       </c>
-      <c r="I5" s="19"/>
-      <c r="J5" s="14">
+      <c r="I5" s="10"/>
+      <c r="J5" s="13">
         <v>38718</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="14">
         <v>44926</v>
       </c>
       <c r="L5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="17" t="s">
+      <c r="N5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="18" t="s">
+      <c r="O5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P5" s="131" t="s">
+      <c r="P5" t="s">
         <v>247</v>
       </c>
     </row>
@@ -2513,36 +2587,36 @@
       <c r="D6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="135">
+      <c r="E6" s="10"/>
+      <c r="F6" s="106">
         <v>47.316000000000003</v>
       </c>
-      <c r="G6" s="135">
+      <c r="G6" s="106">
         <v>10.497999999999999</v>
       </c>
       <c r="H6" s="12">
         <v>993</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="14">
+      <c r="I6" s="10"/>
+      <c r="J6" s="13">
         <v>37756</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="14">
         <v>44926</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="M6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="N6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="18" t="s">
+      <c r="O6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P6" s="131" t="s">
+      <c r="P6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -2562,35 +2636,35 @@
       <c r="E7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="135">
+      <c r="F7" s="106">
         <v>47.530999999999999</v>
       </c>
-      <c r="G7" s="135">
+      <c r="G7" s="106">
         <v>14.609</v>
       </c>
       <c r="H7" s="12">
         <v>880</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="14">
+      <c r="I7" s="10"/>
+      <c r="J7" s="13">
         <v>41640</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="14">
         <v>44926</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="O7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P7" s="131" t="s">
+      <c r="P7" t="s">
         <v>249</v>
       </c>
     </row>
@@ -2610,35 +2684,35 @@
       <c r="E8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="135">
+      <c r="F8" s="106">
         <v>46.743000000000002</v>
       </c>
-      <c r="G8" s="135">
+      <c r="G8" s="106">
         <v>13.331</v>
       </c>
       <c r="H8" s="12">
         <v>888</v>
       </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="14">
+      <c r="I8" s="10"/>
+      <c r="J8" s="13">
         <v>36305</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="14">
         <v>44926</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M8" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="18" t="s">
+      <c r="O8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P8" s="131" t="s">
+      <c r="P8" t="s">
         <v>250</v>
       </c>
     </row>
@@ -2658,35 +2732,35 @@
       <c r="E9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="135">
+      <c r="F9" s="106">
         <v>46.984999999999999</v>
       </c>
-      <c r="G9" s="135">
+      <c r="G9" s="106">
         <v>9.9320000000000004</v>
       </c>
       <c r="H9" s="12">
         <v>1299</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="14">
+      <c r="I9" s="10"/>
+      <c r="J9" s="13">
         <v>35796</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="14">
         <v>44926</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="18" t="s">
+      <c r="O9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P9" s="131" t="s">
+      <c r="P9" t="s">
         <v>251</v>
       </c>
     </row>
@@ -2706,35 +2780,35 @@
       <c r="E10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="135">
+      <c r="F10" s="106">
         <v>47.383000000000003</v>
       </c>
-      <c r="G10" s="135">
+      <c r="G10" s="106">
         <v>10.047000000000001</v>
       </c>
       <c r="H10" s="12">
         <v>1000</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="14">
+      <c r="I10" s="10"/>
+      <c r="J10" s="13">
         <v>35448</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="14">
         <v>44926</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N10" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="18" t="s">
+      <c r="O10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="131" t="s">
+      <c r="P10" t="s">
         <v>252</v>
       </c>
     </row>
@@ -2754,35 +2828,35 @@
       <c r="E11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="135">
+      <c r="F11" s="106">
         <v>47.601999999999997</v>
       </c>
-      <c r="G11" s="135">
+      <c r="G11" s="106">
         <v>13.138</v>
       </c>
       <c r="H11" s="12">
         <v>555</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="14">
+      <c r="I11" s="10"/>
+      <c r="J11" s="13">
         <v>36161</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="14">
         <v>44926</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="18" t="s">
+      <c r="O11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P11" s="131" t="s">
+      <c r="P11" t="s">
         <v>253</v>
       </c>
     </row>
@@ -2802,35 +2876,35 @@
       <c r="E12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="135">
+      <c r="F12" s="106">
         <v>47.908999999999999</v>
       </c>
-      <c r="G12" s="135">
+      <c r="G12" s="106">
         <v>15.202999999999999</v>
       </c>
       <c r="H12" s="12">
         <v>540</v>
       </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="14">
+      <c r="I12" s="10"/>
+      <c r="J12" s="13">
         <v>34730</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="14">
         <v>44926</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O12" s="18" t="s">
+      <c r="O12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P12" s="131" t="s">
+      <c r="P12" t="s">
         <v>254</v>
       </c>
     </row>
@@ -2850,35 +2924,35 @@
       <c r="E13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="135">
+      <c r="F13" s="106">
         <v>47.21</v>
       </c>
-      <c r="G13" s="135">
+      <c r="G13" s="106">
         <v>15.348000000000001</v>
       </c>
       <c r="H13" s="12">
         <v>410</v>
       </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="14">
+      <c r="I13" s="10"/>
+      <c r="J13" s="13">
         <v>34700</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="14">
         <v>44926</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="18" t="s">
+      <c r="O13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P13" s="131" t="s">
+      <c r="P13" t="s">
         <v>255</v>
       </c>
     </row>
@@ -2898,35 +2972,35 @@
       <c r="E14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="135">
+      <c r="F14" s="106">
         <v>47.3</v>
       </c>
-      <c r="G14" s="135">
+      <c r="G14" s="106">
         <v>10.722</v>
       </c>
       <c r="H14" s="12">
         <v>1561</v>
       </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="14">
+      <c r="I14" s="10"/>
+      <c r="J14" s="13">
         <v>39083</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="14">
         <v>44196</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M14" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O14" s="18" t="s">
+      <c r="O14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P14" s="131" t="s">
+      <c r="P14" t="s">
         <v>256</v>
       </c>
     </row>
@@ -2946,35 +3020,35 @@
       <c r="E15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="135">
+      <c r="F15" s="106">
         <v>47.546999999999997</v>
       </c>
-      <c r="G15" s="135">
+      <c r="G15" s="106">
         <v>13.659000000000001</v>
       </c>
       <c r="H15" s="12">
         <v>508</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="14">
+      <c r="I15" s="10"/>
+      <c r="J15" s="13">
         <v>39582</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="14">
         <v>44926</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="N15" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="18" t="s">
+      <c r="O15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P15" s="131" t="s">
+      <c r="P15" t="s">
         <v>257</v>
       </c>
     </row>
@@ -2994,35 +3068,35 @@
       <c r="E16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="135">
+      <c r="F16" s="106">
         <v>47.786000000000001</v>
       </c>
-      <c r="G16" s="135">
+      <c r="G16" s="106">
         <v>13.734</v>
       </c>
       <c r="H16" s="12">
         <v>435</v>
       </c>
-      <c r="I16" s="19"/>
-      <c r="J16" s="14">
+      <c r="I16" s="10"/>
+      <c r="J16" s="13">
         <v>35431</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="14">
         <v>44926</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M16" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="N16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O16" s="18" t="s">
+      <c r="O16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="131" t="s">
+      <c r="P16" t="s">
         <v>258</v>
       </c>
     </row>
@@ -3042,35 +3116,35 @@
       <c r="E17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="135">
+      <c r="F17" s="106">
         <v>46.725000000000001</v>
       </c>
-      <c r="G17" s="135">
+      <c r="G17" s="106">
         <v>13.042999999999999</v>
       </c>
       <c r="H17" s="12">
         <v>870</v>
       </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="14">
+      <c r="I17" s="10"/>
+      <c r="J17" s="13">
         <v>36161</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="14">
         <v>44926</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M17" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O17" s="18" t="s">
+      <c r="O17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P17" s="131" t="s">
+      <c r="P17" t="s">
         <v>259</v>
       </c>
     </row>
@@ -3090,35 +3164,35 @@
       <c r="E18" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="135">
+      <c r="F18" s="106">
         <v>47.253</v>
       </c>
-      <c r="G18" s="135">
+      <c r="G18" s="106">
         <v>13.414</v>
       </c>
       <c r="H18" s="12">
         <v>1046</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="14">
+      <c r="I18" s="10"/>
+      <c r="J18" s="13">
         <v>35796</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="14">
         <v>44926</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M18" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N18" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O18" s="18" t="s">
+      <c r="O18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P18" s="131" t="s">
+      <c r="P18" t="s">
         <v>260</v>
       </c>
     </row>
@@ -3138,35 +3212,35 @@
       <c r="E19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="135">
+      <c r="F19" s="106">
         <v>46.951999999999998</v>
       </c>
-      <c r="G19" s="135">
+      <c r="G19" s="106">
         <v>9.9109999999999996</v>
       </c>
       <c r="H19" s="12">
         <v>1682</v>
       </c>
-      <c r="I19" s="19"/>
-      <c r="J19" s="14">
+      <c r="I19" s="10"/>
+      <c r="J19" s="13">
         <v>39470</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="14">
         <v>44926</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="M19" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N19" s="17" t="s">
+      <c r="N19" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O19" s="18" t="s">
+      <c r="O19" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P19" s="131" t="s">
+      <c r="P19" t="s">
         <v>261</v>
       </c>
     </row>
@@ -3186,35 +3260,35 @@
       <c r="E20" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="135">
+      <c r="F20" s="106">
         <v>47.564</v>
       </c>
-      <c r="G20" s="135">
+      <c r="G20" s="106">
         <v>13.826000000000001</v>
       </c>
       <c r="H20" s="12">
         <v>770</v>
       </c>
-      <c r="I20" s="19"/>
-      <c r="J20" s="14">
+      <c r="I20" s="10"/>
+      <c r="J20" s="13">
         <v>35977</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="14">
         <v>44926</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="M20" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N20" s="17" t="s">
+      <c r="N20" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O20" s="18" t="s">
+      <c r="O20" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P20" s="131" t="s">
+      <c r="P20" t="s">
         <v>262</v>
       </c>
     </row>
@@ -3234,35 +3308,35 @@
       <c r="E21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="135">
+      <c r="F21" s="106">
         <v>46.832999999999998</v>
       </c>
-      <c r="G21" s="135">
+      <c r="G21" s="106">
         <v>13.769</v>
       </c>
       <c r="H21" s="12">
         <v>1208</v>
       </c>
-      <c r="I21" s="19"/>
-      <c r="J21" s="14">
+      <c r="I21" s="10"/>
+      <c r="J21" s="13">
         <v>38455</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="14">
         <v>44926</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M21" s="16" t="s">
+      <c r="M21" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N21" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O21" s="18" t="s">
+      <c r="O21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P21" s="131" t="s">
+      <c r="P21" t="s">
         <v>263</v>
       </c>
     </row>
@@ -3282,35 +3356,35 @@
       <c r="E22" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="135">
+      <c r="F22" s="106">
         <v>47.704999999999998</v>
       </c>
-      <c r="G22" s="135">
+      <c r="G22" s="106">
         <v>15.324999999999999</v>
       </c>
       <c r="H22" s="12">
         <v>794</v>
       </c>
-      <c r="I22" s="19"/>
-      <c r="J22" s="14">
+      <c r="I22" s="10"/>
+      <c r="J22" s="13">
         <v>34705</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="14">
         <v>44926</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N22" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O22" s="18" t="s">
+      <c r="O22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P22" s="131" t="s">
+      <c r="P22" t="s">
         <v>264</v>
       </c>
     </row>
@@ -3330,35 +3404,35 @@
       <c r="E23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="135">
+      <c r="F23" s="106">
         <v>47.692999999999998</v>
       </c>
-      <c r="G23" s="135">
+      <c r="G23" s="106">
         <v>14.276</v>
       </c>
       <c r="H23" s="12">
         <v>753</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="14">
+      <c r="I23" s="10"/>
+      <c r="J23" s="13">
         <v>29373</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="14">
         <v>44926</v>
       </c>
       <c r="L23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="M23" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="17" t="s">
+      <c r="N23" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O23" s="18" t="s">
+      <c r="O23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="131" t="s">
+      <c r="P23" t="s">
         <v>265</v>
       </c>
     </row>
@@ -3378,35 +3452,35 @@
       <c r="E24" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="135">
+      <c r="F24" s="106">
         <v>47.036000000000001</v>
       </c>
-      <c r="G24" s="135">
+      <c r="G24" s="106">
         <v>14.374000000000001</v>
       </c>
       <c r="H24" s="12">
         <v>1150</v>
       </c>
-      <c r="I24" s="19"/>
-      <c r="J24" s="14">
+      <c r="I24" s="10"/>
+      <c r="J24" s="13">
         <v>40738</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="14">
         <v>44926</v>
       </c>
       <c r="L24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M24" s="16" t="s">
+      <c r="M24" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N24" s="17" t="s">
+      <c r="N24" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="O24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P24" s="131" t="s">
+      <c r="P24" t="s">
         <v>266</v>
       </c>
     </row>
@@ -3426,35 +3500,35 @@
       <c r="E25" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="135">
+      <c r="F25" s="106">
         <v>47.43</v>
       </c>
-      <c r="G25" s="135">
+      <c r="G25" s="106">
         <v>12.693</v>
       </c>
       <c r="H25" s="12">
         <v>955</v>
       </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="14">
+      <c r="I25" s="10"/>
+      <c r="J25" s="13">
         <v>38952</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="14">
         <v>44926</v>
       </c>
       <c r="L25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="M25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N25" s="17" t="s">
+      <c r="N25" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O25" s="18" t="s">
+      <c r="O25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P25" s="131" t="s">
+      <c r="P25" t="s">
         <v>267</v>
       </c>
     </row>
@@ -3474,39 +3548,39 @@
       <c r="E26" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="135">
+      <c r="F26" s="106">
         <v>47.843000000000004</v>
       </c>
-      <c r="G26" s="135">
+      <c r="G26" s="106">
         <v>14.879</v>
       </c>
       <c r="H26" s="12">
         <v>560</v>
       </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="14">
+      <c r="I26" s="10"/>
+      <c r="J26" s="13">
         <v>35065</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="14">
         <v>44926</v>
       </c>
       <c r="L26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="M26" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N26" s="17" t="s">
+      <c r="N26" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O26" s="18" t="s">
+      <c r="O26" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P26" s="131" t="s">
+      <c r="P26" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" ht="16">
       <c r="A27" s="10" t="s">
         <v>16</v>
       </c>
@@ -3522,39 +3596,39 @@
       <c r="E27" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="135">
+      <c r="F27" s="106">
         <v>47.755000000000003</v>
       </c>
-      <c r="G27" s="135">
+      <c r="G27" s="106">
         <v>14.315</v>
       </c>
       <c r="H27" s="12">
         <v>613</v>
       </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="14">
+      <c r="I27" s="10"/>
+      <c r="J27" s="13">
         <v>33239</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="14">
         <v>44926</v>
       </c>
       <c r="L27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N27" s="17" t="s">
+      <c r="N27" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O27" s="18" t="s">
+      <c r="O27" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P27" s="131" t="s">
+      <c r="P27" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" ht="16">
       <c r="A28" s="10" t="s">
         <v>16</v>
       </c>
@@ -3570,39 +3644,39 @@
       <c r="E28" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F28" s="135">
+      <c r="F28" s="106">
         <v>47.546999999999997</v>
       </c>
-      <c r="G28" s="135">
+      <c r="G28" s="106">
         <v>13.867000000000001</v>
       </c>
       <c r="H28" s="12">
         <v>820</v>
       </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="14">
+      <c r="I28" s="10"/>
+      <c r="J28" s="13">
         <v>39448</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="14">
         <v>44926</v>
       </c>
       <c r="L28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M28" s="16" t="s">
+      <c r="M28" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N28" s="17" t="s">
+      <c r="N28" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O28" s="18" t="s">
+      <c r="O28" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P28" s="131" t="s">
+      <c r="P28" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" ht="16">
       <c r="A29" s="10" t="s">
         <v>16</v>
       </c>
@@ -3618,39 +3692,39 @@
       <c r="E29" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="135">
+      <c r="F29" s="106">
         <v>47.582999999999998</v>
       </c>
-      <c r="G29" s="135">
+      <c r="G29" s="106">
         <v>14.031000000000001</v>
       </c>
       <c r="H29" s="12">
         <v>970</v>
       </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="14">
+      <c r="I29" s="10"/>
+      <c r="J29" s="13">
         <v>35975</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="14">
         <v>44926</v>
       </c>
       <c r="L29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="M29" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N29" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O29" s="18" t="s">
+      <c r="O29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P29" s="131" t="s">
+      <c r="P29" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" ht="16">
       <c r="A30" s="10" t="s">
         <v>16</v>
       </c>
@@ -3666,39 +3740,39 @@
       <c r="E30" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="135">
+      <c r="F30" s="106">
         <v>47.433999999999997</v>
       </c>
-      <c r="G30" s="135">
+      <c r="G30" s="106">
         <v>12.58</v>
       </c>
       <c r="H30" s="12">
         <v>980</v>
       </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="14">
+      <c r="I30" s="10"/>
+      <c r="J30" s="13">
         <v>35796</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="14">
         <v>44926</v>
       </c>
       <c r="L30" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="M30" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N30" s="17" t="s">
+      <c r="N30" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O30" s="18" t="s">
+      <c r="O30" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P30" s="131" t="s">
+      <c r="P30" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" ht="16">
       <c r="A31" s="10" t="s">
         <v>16</v>
       </c>
@@ -3714,39 +3788,39 @@
       <c r="E31" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="135">
+      <c r="F31" s="106">
         <v>47.609000000000002</v>
       </c>
-      <c r="G31" s="135">
+      <c r="G31" s="106">
         <v>14.849</v>
       </c>
       <c r="H31" s="12">
         <v>800</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="14">
+      <c r="I31" s="10"/>
+      <c r="J31" s="13">
         <v>36267</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="14">
         <v>44926</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M31" s="16" t="s">
+      <c r="M31" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N31" s="17" t="s">
+      <c r="N31" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O31" s="18" t="s">
+      <c r="O31" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P31" s="131" t="s">
+      <c r="P31" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" ht="16">
       <c r="A32" s="10" t="s">
         <v>16</v>
       </c>
@@ -3762,39 +3836,39 @@
       <c r="E32" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="135">
+      <c r="F32" s="106">
         <v>47.374000000000002</v>
       </c>
-      <c r="G32" s="135">
+      <c r="G32" s="106">
         <v>11.005000000000001</v>
       </c>
       <c r="H32" s="12">
         <v>1454</v>
       </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="14">
+      <c r="I32" s="10"/>
+      <c r="J32" s="13">
         <v>36069</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="14">
         <v>44926</v>
       </c>
       <c r="L32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M32" s="16" t="s">
+      <c r="M32" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N32" s="17" t="s">
+      <c r="N32" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O32" s="18" t="s">
+      <c r="O32" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P32" s="131" t="s">
+      <c r="P32" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" ht="16">
       <c r="A33" s="10" t="s">
         <v>16</v>
       </c>
@@ -3810,39 +3884,39 @@
       <c r="E33" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F33" s="135">
+      <c r="F33" s="106">
         <v>47.566000000000003</v>
       </c>
-      <c r="G33" s="135">
+      <c r="G33" s="106">
         <v>13.118</v>
       </c>
       <c r="H33" s="12">
         <v>518</v>
       </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="14">
+      <c r="I33" s="10"/>
+      <c r="J33" s="13">
         <v>42171</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="14">
         <v>44926</v>
       </c>
       <c r="L33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M33" s="16" t="s">
+      <c r="M33" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N33" s="17" t="s">
+      <c r="N33" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O33" s="18" t="s">
+      <c r="O33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P33" s="131" t="s">
+      <c r="P33" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" ht="16">
       <c r="A34" s="10" t="s">
         <v>16</v>
       </c>
@@ -3858,39 +3932,39 @@
       <c r="E34" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="135">
+      <c r="F34" s="106">
         <v>47.426000000000002</v>
       </c>
-      <c r="G34" s="135">
+      <c r="G34" s="106">
         <v>11.483000000000001</v>
       </c>
       <c r="H34" s="12">
         <v>1199</v>
       </c>
-      <c r="I34" s="19"/>
-      <c r="J34" s="14">
+      <c r="I34" s="10"/>
+      <c r="J34" s="13">
         <v>35433</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="14">
         <v>44926</v>
       </c>
       <c r="L34" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M34" s="16" t="s">
+      <c r="M34" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="17" t="s">
+      <c r="N34" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O34" s="18" t="s">
+      <c r="O34" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P34" s="131" t="s">
+      <c r="P34" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" ht="16">
       <c r="A35" s="10" t="s">
         <v>16</v>
       </c>
@@ -3906,39 +3980,39 @@
       <c r="E35" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="135">
+      <c r="F35" s="106">
         <v>47.683</v>
       </c>
-      <c r="G35" s="135">
+      <c r="G35" s="106">
         <v>15.567</v>
       </c>
       <c r="H35" s="12">
         <v>797</v>
       </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="14">
+      <c r="I35" s="10"/>
+      <c r="J35" s="13">
         <v>34700</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="14">
         <v>44926</v>
       </c>
       <c r="L35" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M35" s="16" t="s">
+      <c r="M35" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N35" s="17" t="s">
+      <c r="N35" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O35" s="18" t="s">
+      <c r="O35" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P35" s="131" t="s">
+      <c r="P35" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" ht="16">
       <c r="A36" s="10" t="s">
         <v>16</v>
       </c>
@@ -3954,39 +4028,39 @@
       <c r="E36" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="135">
+      <c r="F36" s="106">
         <v>47.814</v>
       </c>
-      <c r="G36" s="135">
+      <c r="G36" s="106">
         <v>14.768000000000001</v>
       </c>
       <c r="H36" s="12">
         <v>500</v>
       </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="14">
+      <c r="I36" s="10"/>
+      <c r="J36" s="13">
         <v>36342</v>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="14">
         <v>44926</v>
       </c>
       <c r="L36" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="M36" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N36" s="17" t="s">
+      <c r="N36" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O36" s="18" t="s">
+      <c r="O36" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P36" s="131" t="s">
+      <c r="P36" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" ht="16">
       <c r="A37" s="10" t="s">
         <v>16</v>
       </c>
@@ -4002,39 +4076,39 @@
       <c r="E37" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="135">
+      <c r="F37" s="106">
         <v>47.825000000000003</v>
       </c>
-      <c r="G37" s="135">
+      <c r="G37" s="106">
         <v>14.353</v>
       </c>
       <c r="H37" s="12">
         <v>546</v>
       </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="14">
+      <c r="I37" s="10"/>
+      <c r="J37" s="13">
         <v>35796</v>
       </c>
-      <c r="K37" s="15">
+      <c r="K37" s="14">
         <v>44926</v>
       </c>
       <c r="L37" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="M37" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N37" s="17" t="s">
+      <c r="N37" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O37" s="18" t="s">
+      <c r="O37" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P37" s="131" t="s">
+      <c r="P37" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" ht="16">
       <c r="A38" s="10" t="s">
         <v>16</v>
       </c>
@@ -4050,39 +4124,39 @@
       <c r="E38" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F38" s="135">
+      <c r="F38" s="106">
         <v>47.787999999999997</v>
       </c>
-      <c r="G38" s="135">
+      <c r="G38" s="106">
         <v>14.206</v>
       </c>
       <c r="H38" s="12">
         <v>541</v>
       </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="14">
+      <c r="I38" s="10"/>
+      <c r="J38" s="13">
         <v>34921</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="14">
         <v>44926</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="16" t="s">
+      <c r="M38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N38" s="17" t="s">
+      <c r="N38" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O38" s="18" t="s">
+      <c r="O38" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P38" s="131" t="s">
+      <c r="P38" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" ht="16">
       <c r="A39" s="10" t="s">
         <v>16</v>
       </c>
@@ -4098,39 +4172,39 @@
       <c r="E39" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F39" s="135">
+      <c r="F39" s="106">
         <v>47.731000000000002</v>
       </c>
-      <c r="G39" s="135">
+      <c r="G39" s="106">
         <v>15.488</v>
       </c>
       <c r="H39" s="12">
         <v>880</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="14">
+      <c r="I39" s="10"/>
+      <c r="J39" s="13">
         <v>42709</v>
       </c>
-      <c r="K39" s="15">
+      <c r="K39" s="14">
         <v>44926</v>
       </c>
       <c r="L39" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M39" s="16" t="s">
+      <c r="M39" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N39" s="17" t="s">
+      <c r="N39" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O39" s="18" t="s">
+      <c r="O39" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P39" s="131" t="s">
+      <c r="P39" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" ht="16">
       <c r="A40" s="10" t="s">
         <v>16</v>
       </c>
@@ -4146,39 +4220,39 @@
       <c r="E40" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="135">
+      <c r="F40" s="106">
         <v>46.63</v>
       </c>
-      <c r="G40" s="135">
+      <c r="G40" s="106">
         <v>13.804</v>
       </c>
       <c r="H40" s="12">
         <v>556</v>
       </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="14">
+      <c r="I40" s="10"/>
+      <c r="J40" s="13">
         <v>34701</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="14">
         <v>44926</v>
       </c>
       <c r="L40" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M40" s="16" t="s">
+      <c r="M40" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N40" s="17" t="s">
+      <c r="N40" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O40" s="18" t="s">
+      <c r="O40" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P40" s="131" t="s">
+      <c r="P40" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" ht="16">
       <c r="A41" s="10" t="s">
         <v>16</v>
       </c>
@@ -4194,39 +4268,39 @@
       <c r="E41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F41" s="135">
+      <c r="F41" s="106">
         <v>47.335000000000001</v>
       </c>
-      <c r="G41" s="135">
+      <c r="G41" s="106">
         <v>10.927</v>
       </c>
       <c r="H41" s="12">
         <v>1593</v>
       </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="14">
+      <c r="I41" s="10"/>
+      <c r="J41" s="13">
         <v>37622</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="14">
         <v>44926</v>
       </c>
       <c r="L41" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M41" s="16" t="s">
+      <c r="M41" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N41" s="17" t="s">
+      <c r="N41" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O41" s="18" t="s">
+      <c r="O41" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P41" s="131" t="s">
+      <c r="P41" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" ht="16">
       <c r="A42" s="10" t="s">
         <v>16</v>
       </c>
@@ -4242,39 +4316,39 @@
       <c r="E42" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="135">
+      <c r="F42" s="106">
         <v>47.545000000000002</v>
       </c>
-      <c r="G42" s="135">
+      <c r="G42" s="106">
         <v>13.608000000000001</v>
       </c>
       <c r="H42" s="12">
         <v>874</v>
       </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="14">
+      <c r="I42" s="10"/>
+      <c r="J42" s="13">
         <v>35125</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="14">
         <v>44926</v>
       </c>
       <c r="L42" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M42" s="16" t="s">
+      <c r="M42" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N42" s="17" t="s">
+      <c r="N42" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O42" s="18" t="s">
+      <c r="O42" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P42" s="131" t="s">
+      <c r="P42" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" ht="16">
       <c r="A43" s="10" t="s">
         <v>16</v>
       </c>
@@ -4290,39 +4364,39 @@
       <c r="E43" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="135">
+      <c r="F43" s="106">
         <v>47.732999999999997</v>
       </c>
-      <c r="G43" s="135">
+      <c r="G43" s="106">
         <v>15.647</v>
       </c>
       <c r="H43" s="12">
         <v>802</v>
       </c>
-      <c r="I43" s="19"/>
-      <c r="J43" s="14">
+      <c r="I43" s="10"/>
+      <c r="J43" s="13">
         <v>34700</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="14">
         <v>44926</v>
       </c>
       <c r="L43" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M43" s="16" t="s">
+      <c r="M43" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N43" s="17" t="s">
+      <c r="N43" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O43" s="18" t="s">
+      <c r="O43" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P43" s="131" t="s">
+      <c r="P43" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" ht="16">
       <c r="A44" s="10" t="s">
         <v>16</v>
       </c>
@@ -4338,39 +4412,39 @@
       <c r="E44" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F44" s="135">
+      <c r="F44" s="106">
         <v>47.582000000000001</v>
       </c>
-      <c r="G44" s="135">
+      <c r="G44" s="106">
         <v>14.827999999999999</v>
       </c>
       <c r="H44" s="12">
         <v>585</v>
       </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="14">
+      <c r="I44" s="10"/>
+      <c r="J44" s="13">
         <v>35432</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="14">
         <v>44926</v>
       </c>
       <c r="L44" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M44" s="16" t="s">
+      <c r="M44" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N44" s="17" t="s">
+      <c r="N44" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O44" s="18" t="s">
+      <c r="O44" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P44" s="131" t="s">
+      <c r="P44" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" ht="16">
       <c r="A45" s="10" t="s">
         <v>16</v>
       </c>
@@ -4383,3605 +4457,3761 @@
       <c r="D45" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E45" s="19"/>
-      <c r="F45" s="135">
+      <c r="E45" s="10"/>
+      <c r="F45" s="106">
         <v>47.326000000000001</v>
       </c>
-      <c r="G45" s="135">
+      <c r="G45" s="106">
         <v>9.9779999999999998</v>
       </c>
       <c r="H45" s="12">
         <v>787</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="14">
+      <c r="I45" s="10"/>
+      <c r="J45" s="13">
         <v>43704</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="14">
         <v>44926</v>
       </c>
       <c r="L45" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="M45" s="16" t="s">
+      <c r="M45" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="N45" s="17" t="s">
+      <c r="N45" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="O45" s="18" t="s">
+      <c r="O45" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P45" s="131" t="s">
+      <c r="P45" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="20" t="s">
+    <row r="46" spans="1:16" ht="16">
+      <c r="A46" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="18">
         <v>45</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="135">
+      <c r="E46" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="106">
         <v>44.76</v>
       </c>
-      <c r="G46" s="135">
+      <c r="G46" s="106">
         <v>5.8879999999999999</v>
       </c>
-      <c r="H46" s="22">
+      <c r="H46" s="12">
         <v>870</v>
       </c>
-      <c r="I46" s="22">
+      <c r="I46" s="12">
         <v>150</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46" s="12">
         <v>2015</v>
       </c>
-      <c r="K46" s="22">
+      <c r="K46" s="12">
         <v>2019</v>
       </c>
-      <c r="L46" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" s="23" t="s">
+      <c r="L46" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="N46" s="24" t="s">
+      <c r="N46" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="O46" s="25"/>
-      <c r="P46" s="132" t="s">
+      <c r="O46" s="17"/>
+      <c r="P46" s="104" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="20" t="s">
+    <row r="47" spans="1:16" ht="16">
+      <c r="A47" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="21">
+      <c r="C47" s="18">
         <v>46</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" s="135">
+      <c r="E47" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="106">
         <v>46.223999999999997</v>
       </c>
-      <c r="G47" s="135">
+      <c r="G47" s="106">
         <v>14.617000000000001</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="12">
         <v>385</v>
       </c>
-      <c r="I47" s="26"/>
-      <c r="J47" s="22">
+      <c r="I47" s="21"/>
+      <c r="J47" s="12">
         <v>1970</v>
       </c>
-      <c r="K47" s="22">
+      <c r="K47" s="12">
         <v>2023</v>
       </c>
-      <c r="L47" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M47" s="27" t="s">
+      <c r="L47" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="N47" s="24" t="s">
+      <c r="N47" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="P47" s="132" t="s">
+      <c r="P47" s="104" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="20" t="s">
+    <row r="48" spans="1:16" ht="16">
+      <c r="A48" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C48" s="21">
+      <c r="C48" s="18">
         <v>47</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E48" s="20"/>
-      <c r="F48" s="135">
+      <c r="E48" s="10"/>
+      <c r="F48" s="106">
         <v>46.292999999999999</v>
       </c>
-      <c r="G48" s="135">
+      <c r="G48" s="106">
         <v>13.797000000000001</v>
       </c>
-      <c r="H48" s="22">
+      <c r="H48" s="12">
         <v>838</v>
       </c>
-      <c r="I48" s="26"/>
-      <c r="J48" s="22">
+      <c r="I48" s="21"/>
+      <c r="J48" s="12">
         <v>1954</v>
       </c>
-      <c r="K48" s="22">
+      <c r="K48" s="12">
         <v>2024</v>
       </c>
-      <c r="L48" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M48" s="28" t="s">
+      <c r="L48" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="N48" s="24" t="s">
+      <c r="N48" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O48" s="29"/>
-      <c r="P48" s="132" t="s">
+      <c r="O48" s="24"/>
+      <c r="P48" s="104" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
-      <c r="A49" s="20" t="s">
+    <row r="49" spans="1:16" ht="16">
+      <c r="A49" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="21">
+      <c r="C49" s="18">
         <v>48</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="135">
+      <c r="E49" s="10"/>
+      <c r="F49" s="106">
         <v>46.411999999999999</v>
       </c>
-      <c r="G49" s="135">
+      <c r="G49" s="106">
         <v>13.724</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="12">
         <v>990</v>
       </c>
-      <c r="I49" s="26"/>
-      <c r="J49" s="22">
+      <c r="I49" s="21"/>
+      <c r="J49" s="12">
         <v>1955</v>
       </c>
-      <c r="K49" s="22">
+      <c r="K49" s="12">
         <v>1982</v>
       </c>
-      <c r="L49" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M49" s="28" t="s">
+      <c r="L49" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="N49" s="24" t="s">
+      <c r="N49" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O49" s="29"/>
-      <c r="P49" s="132" t="s">
+      <c r="O49" s="24"/>
+      <c r="P49" s="104" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
-      <c r="A50" s="20" t="s">
+    <row r="50" spans="1:16" ht="16">
+      <c r="A50" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="18">
         <v>49</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="20"/>
-      <c r="F50" s="135">
+      <c r="E50" s="10"/>
+      <c r="F50" s="106">
         <v>46.259</v>
       </c>
-      <c r="G50" s="135">
+      <c r="G50" s="106">
         <v>13.725</v>
       </c>
-      <c r="H50" s="22">
+      <c r="H50" s="12">
         <v>680</v>
       </c>
-      <c r="I50" s="26"/>
-      <c r="J50" s="22">
+      <c r="I50" s="21"/>
+      <c r="J50" s="12">
         <v>1953</v>
       </c>
-      <c r="K50" s="22">
+      <c r="K50" s="12">
         <v>2024</v>
       </c>
-      <c r="L50" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M50" s="28" t="s">
+      <c r="L50" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="N50" s="24" t="s">
+      <c r="N50" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O50" s="29"/>
-      <c r="P50" s="132" t="s">
+      <c r="O50" s="24"/>
+      <c r="P50" s="104" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
-      <c r="A51" s="20" t="s">
+    <row r="51" spans="1:16" ht="16">
+      <c r="A51" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="21">
+      <c r="C51" s="18">
         <v>50</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E51" s="20"/>
-      <c r="F51" s="135">
+      <c r="E51" s="10"/>
+      <c r="F51" s="106">
         <v>47.539000000000001</v>
       </c>
-      <c r="G51" s="135">
+      <c r="G51" s="106">
         <v>10.772</v>
       </c>
-      <c r="H51" s="22">
+      <c r="H51" s="12">
         <v>1220</v>
       </c>
-      <c r="I51" s="26"/>
-      <c r="J51" s="22">
+      <c r="I51" s="21"/>
+      <c r="J51" s="12">
         <v>2018</v>
       </c>
-      <c r="K51" s="22">
+      <c r="K51" s="12">
         <v>2026</v>
       </c>
-      <c r="L51" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M51" s="30" t="s">
+      <c r="L51" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="N51" s="24" t="s">
+      <c r="N51" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O51" s="29"/>
-      <c r="P51" s="132" t="s">
+      <c r="O51" s="24"/>
+      <c r="P51" s="104" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
-      <c r="A52" s="31" t="s">
+    <row r="52" spans="1:16" ht="16">
+      <c r="A52" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="26">
         <v>1</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E52" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F52" s="136">
+      <c r="E52" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="107">
         <v>42.89</v>
       </c>
-      <c r="G52" s="136">
+      <c r="G52" s="107">
         <v>13.723000000000001</v>
       </c>
-      <c r="H52" s="32">
+      <c r="H52" s="27">
         <v>850</v>
       </c>
-      <c r="I52" s="33"/>
-      <c r="J52" s="34">
+      <c r="I52" s="28"/>
+      <c r="J52" s="27">
         <v>2004</v>
       </c>
-      <c r="K52" s="34">
+      <c r="K52" s="27">
         <v>2026</v>
       </c>
-      <c r="L52" s="32" t="s">
+      <c r="L52" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="M52" s="35" t="s">
+      <c r="M52" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="N52" s="24"/>
-      <c r="O52" s="36" t="s">
+      <c r="N52" s="20"/>
+      <c r="O52" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="P52" s="131" t="s">
+      <c r="P52" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="31" t="s">
+    <row r="53" spans="1:16" ht="16">
+      <c r="A53" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="26">
         <v>2</v>
       </c>
-      <c r="D53" s="31" t="s">
+      <c r="D53" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="E53" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" s="136">
+      <c r="E53" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="107">
         <v>42.942</v>
       </c>
-      <c r="G53" s="136">
+      <c r="G53" s="107">
         <v>13.202</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="27">
         <v>1350</v>
       </c>
-      <c r="I53" s="33"/>
-      <c r="J53" s="34">
+      <c r="I53" s="28"/>
+      <c r="J53" s="27">
         <v>2021</v>
       </c>
-      <c r="K53" s="34">
+      <c r="K53" s="27">
         <v>2026</v>
       </c>
-      <c r="L53" s="32" t="s">
+      <c r="L53" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="M53" s="37" t="s">
+      <c r="M53" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="N53" s="24" t="s">
+      <c r="N53" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O53" s="36" t="s">
+      <c r="O53" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="P53" s="131" t="s">
+      <c r="P53" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
-      <c r="A54" s="31" t="s">
+    <row r="54" spans="1:16" ht="16">
+      <c r="A54" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="31" t="s">
+      <c r="B54" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="26">
         <v>3</v>
       </c>
-      <c r="D54" s="31" t="s">
+      <c r="D54" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E54" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F54" s="136">
+      <c r="E54" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="107">
         <v>42.582000000000001</v>
       </c>
-      <c r="G54" s="136">
+      <c r="G54" s="107">
         <v>12.813000000000001</v>
       </c>
-      <c r="H54" s="38">
+      <c r="H54" s="32">
         <v>490</v>
       </c>
-      <c r="I54" s="39"/>
-      <c r="J54" s="40">
+      <c r="I54" s="27"/>
+      <c r="J54" s="33">
         <v>1997</v>
       </c>
-      <c r="K54" s="34">
+      <c r="K54" s="27">
         <v>2024</v>
       </c>
-      <c r="L54" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="M54" s="37"/>
-      <c r="N54" s="24"/>
-      <c r="O54" s="36" t="s">
+      <c r="L54" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M54" s="31"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="P54" s="131" t="s">
+      <c r="P54" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
-      <c r="A55" s="31" t="s">
+    <row r="55" spans="1:16" ht="16">
+      <c r="A55" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B55" s="31" t="s">
+      <c r="B55" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="26">
         <v>4</v>
       </c>
-      <c r="D55" s="31" t="s">
+      <c r="D55" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="E55" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" s="136">
+      <c r="E55" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="107">
         <v>42.959000000000003</v>
       </c>
-      <c r="G55" s="136">
+      <c r="G55" s="107">
         <v>12.861000000000001</v>
       </c>
-      <c r="H55" s="38">
+      <c r="H55" s="32">
         <v>630</v>
       </c>
-      <c r="I55" s="39"/>
-      <c r="J55" s="40">
+      <c r="I55" s="27"/>
+      <c r="J55" s="33">
         <v>1998</v>
       </c>
-      <c r="K55" s="34">
+      <c r="K55" s="27">
         <v>2024</v>
       </c>
-      <c r="L55" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="M55" s="37"/>
-      <c r="N55" s="24"/>
-      <c r="O55" s="36" t="s">
+      <c r="L55" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M55" s="31"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="P55" s="131" t="s">
+      <c r="P55" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
-      <c r="A56" s="31" t="s">
+    <row r="56" spans="1:16" ht="16">
+      <c r="A56" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="26">
         <v>5</v>
       </c>
-      <c r="D56" s="31" t="s">
+      <c r="D56" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E56" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F56" s="136">
+      <c r="E56" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="107">
         <v>43.353999999999999</v>
       </c>
-      <c r="G56" s="136">
+      <c r="G56" s="107">
         <v>12.73</v>
       </c>
-      <c r="H56" s="38">
+      <c r="H56" s="32">
         <v>590</v>
       </c>
-      <c r="I56" s="39"/>
-      <c r="J56" s="40">
+      <c r="I56" s="27"/>
+      <c r="J56" s="33">
         <v>2007</v>
       </c>
-      <c r="K56" s="34">
+      <c r="K56" s="27">
         <v>2024</v>
       </c>
-      <c r="L56" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="M56" s="41" t="s">
+      <c r="L56" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="N56" s="24" t="s">
+      <c r="N56" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O56" s="42"/>
-      <c r="P56" s="131" t="s">
+      <c r="O56" s="30"/>
+      <c r="P56" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
-      <c r="A57" s="31" t="s">
+    <row r="57" spans="1:16" ht="16">
+      <c r="A57" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="31" t="s">
+      <c r="B57" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="26">
         <v>6</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E57" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" s="136">
+      <c r="E57" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="107">
         <v>43.103000000000002</v>
       </c>
-      <c r="G57" s="136">
+      <c r="G57" s="107">
         <v>12.826000000000001</v>
       </c>
-      <c r="H57" s="38">
+      <c r="H57" s="32">
         <v>475</v>
       </c>
-      <c r="I57" s="39"/>
-      <c r="J57" s="40">
+      <c r="I57" s="27"/>
+      <c r="J57" s="33">
         <v>1998</v>
       </c>
-      <c r="K57" s="34">
+      <c r="K57" s="27">
         <v>2024</v>
       </c>
-      <c r="L57" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="M57" s="41" t="s">
+      <c r="L57" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="N57" s="24" t="s">
+      <c r="N57" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O57" s="42"/>
-      <c r="P57" s="131" t="s">
+      <c r="O57" s="30"/>
+      <c r="P57" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
-      <c r="A58" s="31" t="s">
+    <row r="58" spans="1:16" ht="16">
+      <c r="A58" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B58" s="31" t="s">
+      <c r="B58" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="26">
         <v>7</v>
       </c>
-      <c r="D58" s="31" t="s">
+      <c r="D58" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E58" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" s="136">
+      <c r="E58" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="107">
         <v>43.19</v>
       </c>
-      <c r="G58" s="136">
+      <c r="G58" s="107">
         <v>12.804</v>
       </c>
-      <c r="H58" s="38">
+      <c r="H58" s="32">
         <v>700</v>
       </c>
-      <c r="I58" s="39"/>
-      <c r="J58" s="40">
+      <c r="I58" s="27"/>
+      <c r="J58" s="33">
         <v>2007</v>
       </c>
-      <c r="K58" s="34">
+      <c r="K58" s="27">
         <v>2024</v>
       </c>
-      <c r="L58" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="M58" s="41" t="s">
+      <c r="L58" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="N58" s="24" t="s">
+      <c r="N58" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O58" s="42"/>
-      <c r="P58" s="131" t="s">
+      <c r="O58" s="30"/>
+      <c r="P58" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
-      <c r="A59" s="31" t="s">
+    <row r="59" spans="1:16" ht="16">
+      <c r="A59" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B59" s="31" t="s">
+      <c r="B59" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="26">
         <v>8</v>
       </c>
-      <c r="D59" s="31" t="s">
+      <c r="D59" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="E59" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="136">
+      <c r="E59" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="107">
         <v>43.109000000000002</v>
       </c>
-      <c r="G59" s="136">
+      <c r="G59" s="107">
         <v>12.856</v>
       </c>
-      <c r="H59" s="38">
+      <c r="H59" s="32">
         <v>630</v>
       </c>
-      <c r="I59" s="39"/>
-      <c r="J59" s="40">
+      <c r="I59" s="27"/>
+      <c r="J59" s="33">
         <v>1998</v>
       </c>
-      <c r="K59" s="34">
+      <c r="K59" s="27">
         <v>2024</v>
       </c>
-      <c r="L59" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="M59" s="41" t="s">
+      <c r="L59" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="N59" s="24" t="s">
+      <c r="N59" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O59" s="42"/>
-      <c r="P59" s="131" t="s">
+      <c r="O59" s="30"/>
+      <c r="P59" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
-      <c r="A60" s="43" t="s">
+    <row r="60" spans="1:16" ht="16">
+      <c r="A60" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B60" s="43" t="s">
+      <c r="B60" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="43">
+      <c r="C60" s="35">
         <v>1</v>
       </c>
-      <c r="D60" s="43" t="s">
+      <c r="D60" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="E60" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" s="137">
+      <c r="E60" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="108">
         <v>35.417000000000002</v>
       </c>
-      <c r="G60" s="137">
+      <c r="G60" s="108">
         <v>7.9640000000000004</v>
       </c>
-      <c r="H60" s="44">
+      <c r="H60" s="36">
         <v>975</v>
       </c>
-      <c r="I60" s="45">
+      <c r="I60" s="37">
         <v>148</v>
       </c>
-      <c r="J60" s="46">
+      <c r="J60" s="38">
         <v>1973</v>
       </c>
-      <c r="K60" s="45">
+      <c r="K60" s="37">
         <v>1977</v>
       </c>
-      <c r="L60" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="M60" s="47" t="s">
+      <c r="L60" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="M60" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="N60" s="48" t="s">
+      <c r="N60" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="O60" s="25"/>
-      <c r="P60" s="131" t="s">
+      <c r="O60" s="17"/>
+      <c r="P60" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
-      <c r="A61" s="43" t="s">
+    <row r="61" spans="1:16" ht="17">
+      <c r="A61" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B61" s="43" t="s">
+      <c r="B61" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="C61" s="43">
+      <c r="C61" s="35">
         <v>2</v>
       </c>
-      <c r="D61" s="49" t="s">
+      <c r="D61" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="E61" s="50"/>
-      <c r="F61" s="138">
+      <c r="E61" s="41"/>
+      <c r="F61" s="109">
         <v>34.15</v>
       </c>
-      <c r="G61" s="138">
+      <c r="G61" s="109">
         <v>-4.04</v>
       </c>
-      <c r="H61" s="51">
+      <c r="H61" s="42">
         <v>960</v>
       </c>
-      <c r="I61" s="50"/>
-      <c r="J61" s="52">
+      <c r="I61" s="41"/>
+      <c r="J61" s="43">
         <v>1989</v>
       </c>
-      <c r="K61" s="52">
+      <c r="K61" s="43">
         <v>2020</v>
       </c>
-      <c r="L61" s="53" t="s">
+      <c r="L61" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="M61" s="47" t="s">
+      <c r="M61" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="N61" s="48" t="s">
+      <c r="N61" s="16" t="s">
         <v>76</v>
       </c>
       <c r="O61" s="9"/>
-      <c r="P61" s="131" t="s">
+      <c r="P61" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
-      <c r="A62" s="95" t="s">
+    <row r="62" spans="1:16" ht="16">
+      <c r="A62" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="B62" s="95" t="s">
+      <c r="B62" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="C62" s="95">
+      <c r="C62" s="70">
         <v>1</v>
       </c>
-      <c r="D62" s="95" t="s">
+      <c r="D62" s="70" t="s">
         <v>192</v>
       </c>
-      <c r="E62" s="95"/>
-      <c r="F62" s="139">
+      <c r="E62" s="70"/>
+      <c r="F62" s="110">
         <v>41.854999999999997</v>
       </c>
-      <c r="G62" s="139">
+      <c r="G62" s="110">
         <v>23.427</v>
       </c>
-      <c r="H62" s="102">
+      <c r="H62" s="77">
         <v>942</v>
       </c>
-      <c r="I62" s="97" t="s">
+      <c r="I62" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="J62" s="98">
+      <c r="J62" s="73">
         <v>1963</v>
       </c>
-      <c r="K62" s="97">
+      <c r="K62" s="72">
         <v>2018</v>
       </c>
-      <c r="L62" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="M62" s="101" t="s">
+      <c r="L62" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="N62" s="24" t="s">
+      <c r="N62" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="O62" s="25"/>
-      <c r="P62" s="131" t="s">
+      <c r="O62" s="17"/>
+      <c r="P62" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
-      <c r="A63" s="95" t="s">
+    <row r="63" spans="1:16" ht="16">
+      <c r="A63" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="B63" s="95" t="s">
+      <c r="B63" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="C63" s="95">
+      <c r="C63" s="70">
         <v>2</v>
       </c>
-      <c r="D63" s="95" t="s">
+      <c r="D63" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="E63" s="95"/>
-      <c r="F63" s="139">
+      <c r="E63" s="70"/>
+      <c r="F63" s="110">
         <v>41.853999999999999</v>
       </c>
-      <c r="G63" s="139">
+      <c r="G63" s="110">
         <v>23.436</v>
       </c>
-      <c r="H63" s="102">
+      <c r="H63" s="77">
         <v>912</v>
       </c>
-      <c r="I63" s="97" t="s">
+      <c r="I63" s="72" t="s">
         <v>196</v>
       </c>
-      <c r="J63" s="98">
+      <c r="J63" s="73">
         <v>1963</v>
       </c>
-      <c r="K63" s="97">
+      <c r="K63" s="72">
         <v>2018</v>
       </c>
-      <c r="L63" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="M63" s="101" t="s">
+      <c r="L63" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="N63" s="24" t="s">
+      <c r="N63" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="O63" s="25"/>
-      <c r="P63" s="131" t="s">
+      <c r="O63" s="17"/>
+      <c r="P63" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
-      <c r="A64" s="95" t="s">
+    <row r="64" spans="1:16" ht="16">
+      <c r="A64" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="B64" s="95" t="s">
+      <c r="B64" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="C64" s="95">
+      <c r="C64" s="70">
         <v>3</v>
       </c>
-      <c r="D64" s="95" t="s">
+      <c r="D64" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="E64" s="95"/>
-      <c r="F64" s="139">
+      <c r="E64" s="70"/>
+      <c r="F64" s="110">
         <v>41.706000000000003</v>
       </c>
-      <c r="G64" s="139">
+      <c r="G64" s="110">
         <v>24.466000000000001</v>
       </c>
-      <c r="H64" s="96">
+      <c r="H64" s="71">
         <v>800</v>
       </c>
-      <c r="I64" s="97">
+      <c r="I64" s="72">
         <v>170</v>
       </c>
-      <c r="J64" s="98">
+      <c r="J64" s="73">
         <v>2000</v>
       </c>
-      <c r="K64" s="97">
+      <c r="K64" s="72">
         <v>2020</v>
       </c>
-      <c r="L64" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="M64" s="101" t="s">
+      <c r="L64" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="N64" s="24" t="s">
+      <c r="N64" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="O64" s="25"/>
-      <c r="P64" s="133" t="s">
+      <c r="O64" s="17"/>
+      <c r="P64" s="104" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
-      <c r="A65" s="95" t="s">
+    <row r="65" spans="1:16" ht="16">
+      <c r="A65" s="70" t="s">
         <v>187</v>
       </c>
-      <c r="B65" s="95" t="s">
+      <c r="B65" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="C65" s="95">
+      <c r="C65" s="70">
         <v>4</v>
       </c>
-      <c r="D65" s="95" t="s">
+      <c r="D65" s="70" t="s">
         <v>191</v>
       </c>
-      <c r="E65" s="95"/>
-      <c r="F65" s="139">
+      <c r="E65" s="70"/>
+      <c r="F65" s="110">
         <v>41.616</v>
       </c>
-      <c r="G65" s="139">
+      <c r="G65" s="110">
         <v>24.492999999999999</v>
       </c>
-      <c r="H65" s="96">
+      <c r="H65" s="71">
         <v>1357</v>
       </c>
-      <c r="I65" s="97">
+      <c r="I65" s="72">
         <v>45</v>
       </c>
-      <c r="J65" s="98">
+      <c r="J65" s="73">
         <v>2000</v>
       </c>
-      <c r="K65" s="97">
+      <c r="K65" s="72">
         <v>2009</v>
       </c>
-      <c r="L65" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="M65" s="101" t="s">
+      <c r="L65" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M65" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="N65" s="24" t="s">
+      <c r="N65" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="O65" s="25"/>
-      <c r="P65" s="131" t="s">
+      <c r="O65" s="17"/>
+      <c r="P65" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
-      <c r="A66" s="54" t="s">
+    <row r="66" spans="1:16" ht="16">
+      <c r="A66" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="C66" s="55">
+      <c r="C66" s="45">
         <v>1</v>
       </c>
-      <c r="D66" s="54" t="s">
+      <c r="D66" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="E66" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" s="62">
+      <c r="E66" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" s="50">
         <v>36.726999999999997</v>
       </c>
-      <c r="G66" s="62">
+      <c r="G66" s="50">
         <v>-5.2380000000000004</v>
       </c>
-      <c r="H66" s="56">
+      <c r="H66" s="46">
         <v>435</v>
       </c>
-      <c r="I66" s="57"/>
-      <c r="J66" s="58">
+      <c r="I66" s="47"/>
+      <c r="J66" s="48">
         <v>1944</v>
       </c>
-      <c r="K66" s="59">
+      <c r="K66" s="47">
         <v>2015</v>
       </c>
-      <c r="L66" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="M66" s="60" t="s">
+      <c r="L66" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="N66" s="24" t="s">
+      <c r="N66" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O66" s="61"/>
-      <c r="P66" s="131" t="s">
+      <c r="O66" s="17"/>
+      <c r="P66" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
-      <c r="A67" s="54" t="s">
+    <row r="67" spans="1:16" ht="16">
+      <c r="A67" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="C67" s="55">
+      <c r="C67" s="45">
         <v>2</v>
       </c>
-      <c r="D67" s="54" t="s">
+      <c r="D67" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="E67" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" s="62">
+      <c r="E67" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" s="50">
         <v>36.718000000000004</v>
       </c>
-      <c r="G67" s="62">
+      <c r="G67" s="50">
         <v>-5.2510000000000003</v>
       </c>
-      <c r="H67" s="56">
+      <c r="H67" s="46">
         <v>520</v>
       </c>
-      <c r="I67" s="57"/>
-      <c r="J67" s="58">
+      <c r="I67" s="47"/>
+      <c r="J67" s="48">
         <v>1999</v>
       </c>
-      <c r="K67" s="59">
+      <c r="K67" s="47">
         <v>2017</v>
       </c>
-      <c r="L67" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="M67" s="60" t="s">
+      <c r="L67" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="M67" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="N67" s="24" t="s">
+      <c r="N67" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O67" s="61"/>
-      <c r="P67" s="131" t="s">
+      <c r="O67" s="17"/>
+      <c r="P67" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
-      <c r="A68" s="54" t="s">
+    <row r="68" spans="1:16" ht="16">
+      <c r="A68" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="B68" s="54" t="s">
+      <c r="B68" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="C68" s="55">
+      <c r="C68" s="45">
         <v>3</v>
       </c>
-      <c r="D68" s="54" t="s">
+      <c r="D68" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="E68" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="62">
+      <c r="E68" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" s="50">
         <v>37.888230559999997</v>
       </c>
-      <c r="G68" s="62">
+      <c r="G68" s="50">
         <v>-2.6912444440000001</v>
       </c>
-      <c r="H68" s="56">
+      <c r="H68" s="46">
         <v>1140</v>
       </c>
-      <c r="I68" s="59">
+      <c r="I68" s="47">
         <v>33.799999999999997</v>
       </c>
-      <c r="J68" s="58">
+      <c r="J68" s="48">
         <v>2019</v>
       </c>
-      <c r="K68" s="59">
+      <c r="K68" s="47">
         <v>2022</v>
       </c>
-      <c r="L68" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="M68" s="63" t="s">
+      <c r="L68" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="M68" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="N68" s="24" t="s">
+      <c r="N68" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O68" s="61" t="s">
+      <c r="O68" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="P68" s="131" t="s">
+      <c r="P68" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
-      <c r="A69" s="54" t="s">
+    <row r="69" spans="1:16" ht="16">
+      <c r="A69" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="B69" s="54" t="s">
+      <c r="B69" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="C69" s="55">
+      <c r="C69" s="45">
         <v>4</v>
       </c>
-      <c r="D69" s="54" t="s">
+      <c r="D69" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="E69" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="F69" s="62">
+      <c r="E69" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="50">
         <v>37.892372219999999</v>
       </c>
-      <c r="G69" s="62">
+      <c r="G69" s="50">
         <v>-2.6756416669999998</v>
       </c>
-      <c r="H69" s="56">
+      <c r="H69" s="46">
         <v>1090</v>
       </c>
-      <c r="I69" s="64">
+      <c r="I69" s="52">
         <v>45</v>
       </c>
-      <c r="J69" s="58">
+      <c r="J69" s="48">
         <v>2019</v>
       </c>
-      <c r="K69" s="59">
+      <c r="K69" s="47">
         <v>2022</v>
       </c>
-      <c r="L69" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="M69" s="63" t="s">
+      <c r="L69" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="M69" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="N69" s="24" t="s">
+      <c r="N69" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O69" s="61" t="s">
+      <c r="O69" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="P69" s="131" t="s">
+      <c r="P69" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
-      <c r="A70" s="65" t="s">
+    <row r="70" spans="1:16" ht="16">
+      <c r="A70" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="C70" s="66">
+      <c r="C70" s="53">
         <v>1</v>
       </c>
-      <c r="D70" s="65" t="s">
+      <c r="D70" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="E70" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" s="140">
+      <c r="E70" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" s="111">
         <v>48.86</v>
       </c>
-      <c r="G70" s="140">
+      <c r="G70" s="111">
         <v>19.527000000000001</v>
       </c>
-      <c r="H70" s="67">
+      <c r="H70" s="54">
         <v>600</v>
       </c>
-      <c r="I70" s="68"/>
-      <c r="J70" s="69">
+      <c r="I70" s="55"/>
+      <c r="J70" s="56">
         <v>2016</v>
       </c>
-      <c r="K70" s="70">
+      <c r="K70" s="55">
         <v>2024</v>
       </c>
-      <c r="L70" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="M70" s="72" t="s">
+      <c r="L70" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="N70" s="24" t="s">
+      <c r="N70" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="O70" s="61" t="s">
+      <c r="O70" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="P70" s="131" t="s">
+      <c r="P70" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
-      <c r="A71" s="65" t="s">
+    <row r="71" spans="1:16" ht="16">
+      <c r="A71" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="C71" s="66">
+      <c r="C71" s="53">
         <v>2</v>
       </c>
-      <c r="D71" s="65" t="s">
+      <c r="D71" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="E71" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" s="140">
+      <c r="E71" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="111">
         <v>48.929000000000002</v>
       </c>
-      <c r="G71" s="140">
+      <c r="G71" s="111">
         <v>20.123999999999999</v>
       </c>
-      <c r="H71" s="67">
+      <c r="H71" s="54">
         <v>990</v>
       </c>
-      <c r="I71" s="68"/>
-      <c r="J71" s="71">
+      <c r="I71" s="55"/>
+      <c r="J71" s="57">
         <v>2016</v>
       </c>
-      <c r="K71" s="70">
+      <c r="K71" s="55">
         <v>2024</v>
       </c>
-      <c r="L71" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="M71" s="72" t="s">
+      <c r="L71" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="M71" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="N71" s="24" t="s">
+      <c r="N71" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O71" s="61" t="s">
+      <c r="O71" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="P71" s="131" t="s">
+      <c r="P71" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
-      <c r="A72" s="65" t="s">
+    <row r="72" spans="1:16" ht="16">
+      <c r="A72" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B72" s="65" t="s">
+      <c r="B72" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="C72" s="66">
+      <c r="C72" s="53">
         <v>3</v>
       </c>
-      <c r="D72" s="65" t="s">
+      <c r="D72" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="E72" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" s="140">
+      <c r="E72" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="111">
         <v>49.252000000000002</v>
       </c>
-      <c r="G72" s="140">
+      <c r="G72" s="111">
         <v>20.103000000000002</v>
       </c>
-      <c r="H72" s="67">
+      <c r="H72" s="54">
         <v>995</v>
       </c>
-      <c r="I72" s="68"/>
-      <c r="J72" s="71">
+      <c r="I72" s="55"/>
+      <c r="J72" s="57">
         <v>2016</v>
       </c>
-      <c r="K72" s="70">
+      <c r="K72" s="55">
         <v>2024</v>
       </c>
-      <c r="L72" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="M72" s="72" t="s">
+      <c r="L72" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="M72" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="N72" s="24" t="s">
+      <c r="N72" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="O72" s="61" t="s">
+      <c r="O72" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="P72" s="131" t="s">
+      <c r="P72" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
-      <c r="A73" s="65" t="s">
+    <row r="73" spans="1:16" ht="16">
+      <c r="A73" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B73" s="65" t="s">
+      <c r="B73" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="C73" s="66">
+      <c r="C73" s="53">
         <v>4</v>
       </c>
-      <c r="D73" s="65" t="s">
+      <c r="D73" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="E73" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" s="140">
+      <c r="E73" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" s="111">
         <v>48.756999999999998</v>
       </c>
-      <c r="G73" s="140">
+      <c r="G73" s="111">
         <v>20.07</v>
       </c>
-      <c r="H73" s="67">
+      <c r="H73" s="54">
         <v>430</v>
       </c>
-      <c r="I73" s="68"/>
-      <c r="J73" s="71">
+      <c r="I73" s="55"/>
+      <c r="J73" s="57">
         <v>2016</v>
       </c>
-      <c r="K73" s="71">
+      <c r="K73" s="57">
         <v>2024</v>
       </c>
-      <c r="L73" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="M73" s="72" t="s">
+      <c r="L73" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="M73" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="N73" s="24" t="s">
+      <c r="N73" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="O73" s="61" t="s">
+      <c r="O73" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="P73" s="131" t="s">
+      <c r="P73" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
-      <c r="A74" s="65" t="s">
+    <row r="74" spans="1:16" ht="16">
+      <c r="A74" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B74" s="65" t="s">
+      <c r="B74" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="C74" s="66">
+      <c r="C74" s="53">
         <v>5</v>
       </c>
-      <c r="D74" s="65" t="s">
+      <c r="D74" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="E74" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" s="140">
+      <c r="E74" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="111">
         <v>48.561999999999998</v>
       </c>
-      <c r="G74" s="140">
+      <c r="G74" s="111">
         <v>20.465</v>
       </c>
-      <c r="H74" s="67">
+      <c r="H74" s="54">
         <v>250</v>
       </c>
-      <c r="I74" s="68"/>
-      <c r="J74" s="71">
+      <c r="I74" s="55"/>
+      <c r="J74" s="57">
         <v>2016</v>
       </c>
-      <c r="K74" s="71">
+      <c r="K74" s="57">
         <v>2024</v>
       </c>
-      <c r="L74" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="M74" s="72" t="s">
+      <c r="L74" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M74" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="N74" s="24" t="s">
+      <c r="N74" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="O74" s="61" t="s">
+      <c r="O74" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="P74" s="131" t="s">
+      <c r="P74" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
-      <c r="A75" s="66" t="s">
+    <row r="75" spans="1:16" ht="16">
+      <c r="A75" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B75" s="66" t="s">
+      <c r="B75" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="C75" s="66">
+      <c r="C75" s="53">
         <v>6</v>
       </c>
-      <c r="D75" s="66" t="s">
+      <c r="D75" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="E75" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" s="140">
+      <c r="E75" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="111">
         <v>43.96</v>
       </c>
-      <c r="G75" s="140">
+      <c r="G75" s="111">
         <v>21.62</v>
       </c>
-      <c r="H75" s="73">
+      <c r="H75" s="54">
         <v>560</v>
       </c>
-      <c r="I75" s="74"/>
-      <c r="J75" s="75">
+      <c r="I75" s="55"/>
+      <c r="J75" s="57">
         <v>1988</v>
       </c>
-      <c r="K75" s="76">
+      <c r="K75" s="55">
         <v>1991</v>
       </c>
-      <c r="L75" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="M75" s="37" t="s">
+      <c r="L75" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M75" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="N75" s="24" t="s">
+      <c r="N75" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O75" s="42"/>
-      <c r="P75" s="131" t="s">
+      <c r="O75" s="30"/>
+      <c r="P75" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
-      <c r="A76" s="66" t="s">
+    <row r="76" spans="1:16" ht="16">
+      <c r="A76" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="B76" s="66" t="s">
+      <c r="B76" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="C76" s="66">
+      <c r="C76" s="53">
         <v>7</v>
       </c>
-      <c r="D76" s="66" t="s">
+      <c r="D76" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="E76" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" s="140">
+      <c r="E76" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" s="111">
         <v>44.192</v>
       </c>
-      <c r="G76" s="140">
+      <c r="G76" s="111">
         <v>21.783999999999999</v>
       </c>
-      <c r="H76" s="73">
+      <c r="H76" s="54">
         <v>320</v>
       </c>
-      <c r="I76" s="74"/>
-      <c r="J76" s="75">
+      <c r="I76" s="55"/>
+      <c r="J76" s="57">
         <v>1991</v>
       </c>
-      <c r="K76" s="76">
+      <c r="K76" s="55">
         <v>1999</v>
       </c>
-      <c r="L76" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="M76" s="41" t="s">
+      <c r="L76" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M76" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="N76" s="24" t="s">
+      <c r="N76" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="O76" s="42"/>
-      <c r="P76" s="131" t="s">
+      <c r="O76" s="30"/>
+      <c r="P76" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
-      <c r="A77" s="66" t="s">
+    <row r="77" spans="1:16" ht="16">
+      <c r="A77" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="B77" s="66" t="s">
+      <c r="B77" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C77" s="66">
+      <c r="C77" s="53">
         <v>8</v>
       </c>
-      <c r="D77" s="66" t="s">
+      <c r="D77" s="119" t="s">
         <v>141</v>
       </c>
-      <c r="E77" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="F77" s="140">
+      <c r="E77" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="120">
         <v>49.332999999999998</v>
       </c>
-      <c r="G77" s="140">
+      <c r="G77" s="120">
         <v>16.649999999999999</v>
       </c>
-      <c r="H77" s="77">
+      <c r="H77" s="59">
         <v>300</v>
       </c>
-      <c r="I77" s="76">
+      <c r="I77" s="55">
         <v>153</v>
       </c>
-      <c r="J77" s="75">
+      <c r="J77" s="57">
         <v>1980</v>
       </c>
-      <c r="K77" s="76">
+      <c r="K77" s="55">
         <v>2023</v>
       </c>
-      <c r="L77" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="M77" s="41" t="s">
+      <c r="L77" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M77" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="N77" s="24" t="s">
+      <c r="N77" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O77" s="36" t="s">
+      <c r="O77" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="P77" s="131" t="s">
+      <c r="P77" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
-      <c r="A78" s="78" t="s">
+    <row r="78" spans="1:16" ht="16">
+      <c r="A78" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B78" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="C78" s="118">
+        <v>9</v>
+      </c>
+      <c r="D78" s="126" t="s">
+        <v>364</v>
+      </c>
+      <c r="E78" s="123" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" s="124">
+        <v>48.557000000000002</v>
+      </c>
+      <c r="G78" s="124">
+        <v>20.763999999999999</v>
+      </c>
+      <c r="H78" s="54">
+        <v>173</v>
+      </c>
+      <c r="I78" s="55"/>
+      <c r="J78" s="57">
+        <v>1969</v>
+      </c>
+      <c r="K78" s="55">
+        <v>2024</v>
+      </c>
+      <c r="L78" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78" s="34"/>
+      <c r="N78" s="20"/>
+      <c r="O78" s="30"/>
+    </row>
+    <row r="79" spans="1:16" ht="16">
+      <c r="A79" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B79" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="C79" s="118">
+        <v>10</v>
+      </c>
+      <c r="D79" s="126" t="s">
+        <v>365</v>
+      </c>
+      <c r="E79" s="123" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="124">
+        <v>48.487000000000002</v>
+      </c>
+      <c r="G79" s="124">
+        <v>20.550999999999998</v>
+      </c>
+      <c r="H79" s="54">
+        <v>236</v>
+      </c>
+      <c r="I79" s="55"/>
+      <c r="J79" s="57">
+        <v>1964</v>
+      </c>
+      <c r="K79" s="55">
+        <v>2024</v>
+      </c>
+      <c r="L79" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M79" s="34"/>
+      <c r="N79" s="20"/>
+      <c r="O79" s="30"/>
+    </row>
+    <row r="80" spans="1:16" ht="16">
+      <c r="A80" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="C80" s="118">
+        <v>11</v>
+      </c>
+      <c r="D80" s="126" t="s">
+        <v>366</v>
+      </c>
+      <c r="E80" s="123" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="125">
+        <v>48.521999999999998</v>
+      </c>
+      <c r="G80" s="125">
+        <v>20.545999999999999</v>
+      </c>
+      <c r="H80" s="54">
+        <v>462</v>
+      </c>
+      <c r="I80" s="55"/>
+      <c r="J80" s="57">
+        <v>1965</v>
+      </c>
+      <c r="K80" s="55">
+        <v>2023</v>
+      </c>
+      <c r="L80" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M80" s="34"/>
+      <c r="N80" s="20"/>
+      <c r="O80" s="30"/>
+    </row>
+    <row r="81" spans="1:16" ht="16">
+      <c r="A81" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="C81" s="118">
+        <v>12</v>
+      </c>
+      <c r="D81" s="126" t="s">
+        <v>367</v>
+      </c>
+      <c r="E81" s="123" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="125">
+        <v>48.494999999999997</v>
+      </c>
+      <c r="G81" s="125">
+        <v>20.538</v>
+      </c>
+      <c r="H81" s="54">
+        <v>262</v>
+      </c>
+      <c r="I81" s="55"/>
+      <c r="J81" s="57">
+        <v>1960</v>
+      </c>
+      <c r="K81" s="55">
+        <v>2024</v>
+      </c>
+      <c r="L81" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" s="34"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="30"/>
+    </row>
+    <row r="82" spans="1:16" ht="16">
+      <c r="A82" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B78" s="78" t="s">
+      <c r="B82" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="C78" s="78">
+      <c r="C82" s="60">
         <v>1</v>
       </c>
-      <c r="D78" s="78" t="s">
+      <c r="D82" s="121" t="s">
         <v>146</v>
       </c>
-      <c r="E78" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F78" s="141">
+      <c r="E82" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="122">
         <v>43.826999999999998</v>
       </c>
-      <c r="G78" s="141">
+      <c r="G82" s="122">
         <v>18.271000000000001</v>
       </c>
-      <c r="H78" s="79">
+      <c r="H82" s="61">
         <v>497</v>
       </c>
-      <c r="I78" s="80"/>
-      <c r="J78" s="81">
+      <c r="I82" s="62"/>
+      <c r="J82" s="63">
         <v>2007</v>
       </c>
-      <c r="K78" s="82">
+      <c r="K82" s="62">
         <v>2019</v>
       </c>
-      <c r="L78" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M78" s="83" t="s">
+      <c r="L82" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="N78" s="24" t="s">
+      <c r="N82" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O78" s="42"/>
-      <c r="P78" s="131" t="s">
+      <c r="O82" s="30"/>
+      <c r="P82" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
-      <c r="A79" s="78" t="s">
+    <row r="83" spans="1:16" ht="16">
+      <c r="A83" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B79" s="78" t="s">
+      <c r="B83" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="C79" s="78">
+      <c r="C83" s="60">
         <v>2</v>
       </c>
-      <c r="D79" s="78" t="s">
+      <c r="D83" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="E79" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F79" s="141">
+      <c r="E83" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="112">
         <v>43.774000000000001</v>
       </c>
-      <c r="G79" s="141">
+      <c r="G83" s="112">
         <v>17.023</v>
       </c>
-      <c r="H79" s="79">
+      <c r="H83" s="61">
         <v>738</v>
       </c>
-      <c r="I79" s="80"/>
-      <c r="J79" s="81">
+      <c r="I83" s="62"/>
+      <c r="J83" s="63">
         <v>2004</v>
       </c>
-      <c r="K79" s="82">
+      <c r="K83" s="62">
         <v>2019</v>
       </c>
-      <c r="L79" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M79" s="41" t="s">
+      <c r="L83" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="N79" s="24" t="s">
+      <c r="N83" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O79" s="42"/>
-      <c r="P79" s="131" t="s">
+      <c r="O83" s="30"/>
+      <c r="P83" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
-      <c r="A80" s="78" t="s">
+    <row r="84" spans="1:16" ht="16">
+      <c r="A84" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B80" s="78" t="s">
+      <c r="B84" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="C80" s="78">
+      <c r="C84" s="60">
         <v>3</v>
       </c>
-      <c r="D80" s="78" t="s">
+      <c r="D84" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="E80" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" s="141">
+      <c r="E84" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="112">
         <v>43.808</v>
       </c>
-      <c r="G80" s="141">
+      <c r="G84" s="112">
         <v>17.007000000000001</v>
       </c>
-      <c r="H80" s="79">
+      <c r="H84" s="61">
         <v>721</v>
       </c>
-      <c r="I80" s="80"/>
-      <c r="J80" s="81">
+      <c r="I84" s="62"/>
+      <c r="J84" s="63">
         <v>2007</v>
       </c>
-      <c r="K80" s="82">
+      <c r="K84" s="62">
         <v>2019</v>
       </c>
-      <c r="L80" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M80" s="41" t="s">
+      <c r="L84" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="N80" s="24" t="s">
+      <c r="N84" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O80" s="42"/>
-      <c r="P80" s="131" t="s">
+      <c r="O84" s="30"/>
+      <c r="P84" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
-      <c r="A81" s="78" t="s">
+    <row r="85" spans="1:16" ht="16">
+      <c r="A85" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B81" s="78" t="s">
+      <c r="B85" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C81" s="78">
+      <c r="C85" s="60">
         <v>4</v>
       </c>
-      <c r="D81" s="78" t="s">
+      <c r="D85" s="60" t="s">
         <v>153</v>
       </c>
-      <c r="E81" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F81" s="141">
+      <c r="E85" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="112">
         <v>45.828000000000003</v>
       </c>
-      <c r="G81" s="141">
+      <c r="G85" s="112">
         <v>14.260999999999999</v>
       </c>
-      <c r="H81" s="79">
+      <c r="H85" s="61">
         <v>450</v>
       </c>
-      <c r="I81" s="80"/>
-      <c r="J81" s="81">
+      <c r="I85" s="62"/>
+      <c r="J85" s="63">
         <v>1936</v>
       </c>
-      <c r="K81" s="82">
+      <c r="K85" s="62">
         <v>2023</v>
       </c>
-      <c r="L81" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M81" s="41" t="s">
+      <c r="L85" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M85" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="N81" s="24" t="s">
+      <c r="N85" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="O81" s="29" t="s">
+      <c r="O85" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="P81" s="133" t="s">
+      <c r="P85" s="104" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
-      <c r="A82" s="78" t="s">
+    <row r="86" spans="1:16" ht="16">
+      <c r="A86" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B82" s="78" t="s">
+      <c r="B86" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C82" s="78">
+      <c r="C86" s="60">
         <v>5</v>
       </c>
-      <c r="D82" s="78" t="s">
+      <c r="D86" s="60" t="s">
         <v>154</v>
       </c>
-      <c r="E82" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F82" s="141">
+      <c r="E86" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="112">
         <v>45.899000000000001</v>
       </c>
-      <c r="G82" s="141">
+      <c r="G86" s="112">
         <v>13.909000000000001</v>
       </c>
-      <c r="H82" s="79">
+      <c r="H86" s="61">
         <v>183</v>
       </c>
-      <c r="I82" s="80"/>
-      <c r="J82" s="81">
+      <c r="I86" s="62"/>
+      <c r="J86" s="63">
         <v>1970</v>
       </c>
-      <c r="K82" s="82">
+      <c r="K86" s="62">
         <v>2023</v>
       </c>
-      <c r="L82" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M82" s="41" t="s">
+      <c r="L86" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M86" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="N82" s="24" t="s">
+      <c r="N86" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="O82" s="29" t="s">
+      <c r="O86" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="P82" s="133" t="s">
+      <c r="P86" s="104" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
-      <c r="A83" s="78" t="s">
+    <row r="87" spans="1:16" ht="16">
+      <c r="A87" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B83" s="78" t="s">
+      <c r="B87" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C83" s="78">
+      <c r="C87" s="60">
         <v>6</v>
       </c>
-      <c r="D83" s="78" t="s">
+      <c r="D87" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="E83" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" s="141">
+      <c r="E87" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="112">
         <v>45.43</v>
       </c>
-      <c r="G83" s="141">
+      <c r="G87" s="112">
         <v>13.89</v>
       </c>
-      <c r="H83" s="79">
+      <c r="H87" s="61">
         <v>400</v>
       </c>
-      <c r="I83" s="80"/>
-      <c r="J83" s="81">
+      <c r="I87" s="62"/>
+      <c r="J87" s="63">
         <v>2015</v>
       </c>
-      <c r="K83" s="82">
+      <c r="K87" s="62">
         <v>2023</v>
       </c>
-      <c r="L83" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M83" s="41" t="s">
+      <c r="L87" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M87" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="N83" s="24" t="s">
+      <c r="N87" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="O83" s="29" t="s">
+      <c r="O87" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="P83" s="133" t="s">
+      <c r="P87" s="104" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
-      <c r="A84" s="78" t="s">
+    <row r="88" spans="1:16" ht="16">
+      <c r="A88" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B84" s="78" t="s">
+      <c r="B88" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="C84" s="78">
+      <c r="C88" s="60">
         <v>7</v>
       </c>
-      <c r="D84" s="78" t="s">
+      <c r="D88" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="E84" s="78"/>
-      <c r="F84" s="141">
+      <c r="E88" s="60"/>
+      <c r="F88" s="112">
         <v>44.042000000000002</v>
       </c>
-      <c r="G84" s="141">
+      <c r="G88" s="112">
         <v>16.234999999999999</v>
       </c>
-      <c r="H84" s="79">
+      <c r="H88" s="61">
         <v>250</v>
       </c>
-      <c r="I84" s="80"/>
-      <c r="J84" s="81">
+      <c r="I88" s="62"/>
+      <c r="J88" s="63">
         <v>1998</v>
       </c>
-      <c r="K84" s="82">
+      <c r="K88" s="62">
         <v>2015</v>
       </c>
-      <c r="L84" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M84" s="41" t="s">
+      <c r="L88" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M88" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="N84" s="24" t="s">
+      <c r="N88" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="O84" s="84"/>
-      <c r="P84" s="133" t="s">
+      <c r="O88" s="24"/>
+      <c r="P88" s="104" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
-      <c r="A85" s="78" t="s">
+    <row r="89" spans="1:16" ht="16">
+      <c r="A89" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="78" t="s">
+      <c r="B89" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="C85" s="78">
+      <c r="C89" s="60">
         <v>8</v>
       </c>
-      <c r="D85" s="78" t="s">
+      <c r="D89" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="E85" s="78"/>
-      <c r="F85" s="141">
+      <c r="E89" s="60"/>
+      <c r="F89" s="112">
         <v>44.203000000000003</v>
       </c>
-      <c r="G85" s="141">
+      <c r="G89" s="112">
         <v>16.082999999999998</v>
       </c>
-      <c r="H85" s="79">
+      <c r="H89" s="61">
         <v>325</v>
       </c>
-      <c r="I85" s="80"/>
-      <c r="J85" s="81">
+      <c r="I89" s="62"/>
+      <c r="J89" s="63">
         <v>2001</v>
       </c>
-      <c r="K85" s="82">
+      <c r="K89" s="62">
         <v>2015</v>
       </c>
-      <c r="L85" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M85" s="41" t="s">
+      <c r="L89" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M89" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="N85" s="24" t="s">
+      <c r="N89" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="O85" s="84"/>
-      <c r="P85" s="133" t="s">
+      <c r="O89" s="24"/>
+      <c r="P89" s="104" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
-      <c r="A86" s="78" t="s">
+    <row r="90" spans="1:16" ht="16">
+      <c r="A90" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B86" s="78" t="s">
+      <c r="B90" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="C86" s="78">
+      <c r="C90" s="60">
         <v>9</v>
       </c>
-      <c r="D86" s="78" t="s">
+      <c r="D90" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="E86" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" s="141">
+      <c r="E90" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" s="112">
         <v>43.509</v>
       </c>
-      <c r="G86" s="141">
+      <c r="G90" s="112">
         <v>17.096</v>
       </c>
-      <c r="H86" s="79">
+      <c r="H90" s="61">
         <v>410</v>
       </c>
-      <c r="I86" s="80"/>
-      <c r="J86" s="81">
+      <c r="I90" s="62"/>
+      <c r="J90" s="63">
         <v>2001</v>
       </c>
-      <c r="K86" s="82">
+      <c r="K90" s="62">
         <v>2023</v>
       </c>
-      <c r="L86" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M86" s="41" t="s">
+      <c r="L90" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M90" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="N86" s="24" t="s">
+      <c r="N90" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O86" s="84"/>
-      <c r="P86" s="133" t="s">
+      <c r="O90" s="24"/>
+      <c r="P90" s="104" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
-      <c r="A87" s="85" t="s">
+    <row r="91" spans="1:16" ht="16">
+      <c r="A91" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B87" s="85" t="s">
+      <c r="B91" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="C87" s="78">
+      <c r="C91" s="60">
         <v>10</v>
       </c>
-      <c r="D87" s="85" t="s">
+      <c r="D91" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="E87" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="142">
+      <c r="E91" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="113">
         <v>45.554000000000002</v>
       </c>
-      <c r="G87" s="141">
+      <c r="G91" s="112">
         <v>17.337</v>
       </c>
-      <c r="H87" s="86">
+      <c r="H91" s="61">
         <v>234</v>
       </c>
-      <c r="I87" s="87"/>
-      <c r="J87" s="88">
+      <c r="I91" s="62"/>
+      <c r="J91" s="63">
         <v>2001</v>
       </c>
-      <c r="K87" s="89">
+      <c r="K91" s="62">
         <v>2023</v>
       </c>
-      <c r="L87" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M87" s="72" t="s">
+      <c r="L91" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="N87" s="24" t="s">
+      <c r="N91" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O87" s="84"/>
-      <c r="P87" s="133" t="s">
+      <c r="O91" s="24"/>
+      <c r="P91" s="104" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
-      <c r="A88" s="85" t="s">
+    <row r="92" spans="1:16" ht="16">
+      <c r="A92" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B88" s="85" t="s">
+      <c r="B92" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="C88" s="78">
+      <c r="C92" s="60">
         <v>11</v>
       </c>
-      <c r="D88" s="85" t="s">
+      <c r="D92" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="E88" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F88" s="141">
+      <c r="E92" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="112">
         <v>44.838999999999999</v>
       </c>
-      <c r="G88" s="141">
+      <c r="G92" s="112">
         <v>15.603</v>
       </c>
-      <c r="H88" s="86">
+      <c r="H92" s="61">
         <v>687</v>
       </c>
-      <c r="I88" s="87"/>
-      <c r="J88" s="88">
+      <c r="I92" s="62"/>
+      <c r="J92" s="63">
         <v>1996</v>
       </c>
-      <c r="K88" s="89">
+      <c r="K92" s="62">
         <v>2023</v>
       </c>
-      <c r="L88" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M88" s="72" t="s">
+      <c r="L92" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M92" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="N88" s="24" t="s">
+      <c r="N92" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O88" s="84"/>
-      <c r="P88" s="133" t="s">
+      <c r="O92" s="24"/>
+      <c r="P92" s="104" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
-      <c r="A89" s="90" t="s">
+    <row r="93" spans="1:16" ht="16">
+      <c r="A93" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="B89" s="90" t="s">
+      <c r="B93" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="C89" s="90">
+      <c r="C93" s="65">
         <v>1</v>
       </c>
-      <c r="D89" s="90" t="s">
+      <c r="D93" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="E89" s="90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F89" s="143">
+      <c r="E93" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" s="114">
         <v>46.704999999999998</v>
       </c>
-      <c r="G89" s="143">
+      <c r="G93" s="114">
         <v>6.2089999999999996</v>
       </c>
-      <c r="H89" s="91">
+      <c r="H93" s="66">
         <v>945</v>
       </c>
-      <c r="I89" s="92">
+      <c r="I93" s="67">
         <v>55</v>
       </c>
-      <c r="J89" s="93">
+      <c r="J93" s="68">
         <v>2009</v>
       </c>
-      <c r="K89" s="92">
+      <c r="K93" s="67">
         <v>2024</v>
       </c>
-      <c r="L89" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="M89" s="94" t="s">
+      <c r="L93" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="M93" s="69" t="s">
         <v>170</v>
       </c>
-      <c r="N89" s="24" t="s">
+      <c r="N93" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O89" s="25"/>
-      <c r="P89" s="131" t="s">
+      <c r="O93" s="17"/>
+      <c r="P93" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
-      <c r="A90" s="90" t="s">
+    <row r="94" spans="1:16" ht="16">
+      <c r="A94" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="B90" s="90" t="s">
+      <c r="B94" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="C90" s="90">
+      <c r="C94" s="65">
         <v>2</v>
       </c>
-      <c r="D90" s="90" t="s">
+      <c r="D94" s="65" t="s">
         <v>171</v>
       </c>
-      <c r="E90" s="90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" s="143">
+      <c r="E94" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="114">
         <v>47.011000000000003</v>
       </c>
-      <c r="G90" s="143">
+      <c r="G94" s="114">
         <v>6.2990000000000004</v>
       </c>
-      <c r="H90" s="91">
+      <c r="H94" s="66">
         <v>530</v>
       </c>
-      <c r="I90" s="92">
+      <c r="I94" s="67">
         <v>200</v>
       </c>
-      <c r="J90" s="93">
+      <c r="J94" s="68">
         <v>1993</v>
       </c>
-      <c r="K90" s="92">
+      <c r="K94" s="67">
         <v>2024</v>
       </c>
-      <c r="L90" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="M90" s="94" t="s">
+      <c r="L94" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="M94" s="69" t="s">
         <v>172</v>
       </c>
-      <c r="N90" s="24" t="s">
+      <c r="N94" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="O90" s="25"/>
-      <c r="P90" s="131" t="s">
+      <c r="O94" s="17"/>
+      <c r="P94" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
-      <c r="A91" s="90" t="s">
+    <row r="95" spans="1:16" ht="16">
+      <c r="A95" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="B91" s="90" t="s">
+      <c r="B95" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="C91" s="90">
+      <c r="C95" s="65">
         <v>3</v>
       </c>
-      <c r="D91" s="90" t="s">
+      <c r="D95" s="65" t="s">
         <v>174</v>
       </c>
-      <c r="E91" s="90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F91" s="143">
+      <c r="E95" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="114">
         <v>46.966999999999999</v>
       </c>
-      <c r="G91" s="143">
+      <c r="G95" s="114">
         <v>6.0110000000000001</v>
       </c>
-      <c r="H91" s="91">
+      <c r="H95" s="66">
         <v>420</v>
       </c>
-      <c r="I91" s="92">
+      <c r="I95" s="67">
         <v>170</v>
       </c>
-      <c r="J91" s="93">
+      <c r="J95" s="68">
         <v>1976</v>
       </c>
-      <c r="K91" s="92">
+      <c r="K95" s="67">
         <v>2024</v>
       </c>
-      <c r="L91" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="M91" s="94" t="s">
+      <c r="L95" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="M95" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="N91" s="24" t="s">
+      <c r="N95" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O91" s="25"/>
-      <c r="P91" s="131" t="s">
+      <c r="O95" s="17"/>
+      <c r="P95" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
-      <c r="A92" s="90" t="s">
+    <row r="96" spans="1:16" ht="16">
+      <c r="A96" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="B92" s="90" t="s">
+      <c r="B96" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="C92" s="90">
+      <c r="C96" s="65">
         <v>4</v>
       </c>
-      <c r="D92" s="90" t="s">
+      <c r="D96" s="65" t="s">
         <v>176</v>
       </c>
-      <c r="E92" s="90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F92" s="143">
+      <c r="E96" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="114">
         <v>46.978000000000002</v>
       </c>
-      <c r="G92" s="143">
+      <c r="G96" s="114">
         <v>6.0019999999999998</v>
       </c>
-      <c r="H92" s="91">
+      <c r="H96" s="66">
         <v>375</v>
       </c>
-      <c r="I92" s="92">
+      <c r="I96" s="67">
         <v>13</v>
       </c>
-      <c r="J92" s="93">
+      <c r="J96" s="68">
         <v>1969</v>
       </c>
-      <c r="K92" s="92">
+      <c r="K96" s="67">
         <v>2024</v>
       </c>
-      <c r="L92" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="M92" s="94" t="s">
+      <c r="L96" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="M96" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="N92" s="24" t="s">
+      <c r="N96" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O92" s="25"/>
-      <c r="P92" s="131" t="s">
+      <c r="O96" s="17"/>
+      <c r="P96" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
-      <c r="A93" s="95" t="s">
+    <row r="97" spans="1:16" ht="16">
+      <c r="A97" s="70" t="s">
         <v>177</v>
       </c>
-      <c r="B93" s="95" t="s">
+      <c r="B97" s="70" t="s">
         <v>178</v>
       </c>
-      <c r="C93" s="95">
+      <c r="C97" s="70">
         <v>1</v>
       </c>
-      <c r="D93" s="95" t="s">
+      <c r="D97" s="70" t="s">
         <v>179</v>
       </c>
-      <c r="E93" s="95" t="s">
-        <v>19</v>
-      </c>
-      <c r="F93" s="139">
+      <c r="E97" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" s="110">
         <v>35.332999999999998</v>
       </c>
-      <c r="G93" s="139">
+      <c r="G97" s="110">
         <v>25.047000000000001</v>
       </c>
-      <c r="H93" s="96">
-        <v>19</v>
-      </c>
-      <c r="I93" s="97">
+      <c r="H97" s="71">
+        <v>19</v>
+      </c>
+      <c r="I97" s="72">
         <v>305</v>
       </c>
-      <c r="J93" s="98">
+      <c r="J97" s="73">
         <v>1999</v>
       </c>
-      <c r="K93" s="97">
+      <c r="K97" s="72">
         <v>2001</v>
       </c>
-      <c r="L93" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="M93" s="99" t="s">
+      <c r="L97" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M97" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="N93" s="24" t="s">
+      <c r="N97" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O93" s="25"/>
-      <c r="P93" s="131" t="s">
+      <c r="O97" s="17"/>
+      <c r="P97" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
-      <c r="A94" s="95" t="s">
+    <row r="98" spans="1:16" ht="16">
+      <c r="A98" s="70" t="s">
         <v>177</v>
       </c>
-      <c r="B94" s="95" t="s">
+      <c r="B98" s="70" t="s">
         <v>181</v>
       </c>
-      <c r="C94" s="95">
+      <c r="C98" s="70">
         <v>2</v>
       </c>
-      <c r="D94" s="95" t="s">
+      <c r="D98" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="E94" s="95" t="s">
-        <v>19</v>
-      </c>
-      <c r="F94" s="139">
+      <c r="E98" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="110">
         <v>39.923999999999999</v>
       </c>
-      <c r="G94" s="139">
+      <c r="G98" s="110">
         <v>20.192</v>
       </c>
-      <c r="H94" s="96">
+      <c r="H98" s="71">
         <v>170</v>
       </c>
-      <c r="I94" s="97">
+      <c r="I98" s="72">
         <v>400</v>
       </c>
-      <c r="J94" s="98">
+      <c r="J98" s="73">
         <v>1968</v>
       </c>
-      <c r="K94" s="97">
+      <c r="K98" s="72">
         <v>1973</v>
       </c>
-      <c r="L94" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="M94" s="100" t="s">
+      <c r="L98" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M98" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="N94" s="24" t="s">
+      <c r="N98" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="O94" s="25"/>
-      <c r="P94" s="133" t="s">
+      <c r="O98" s="17"/>
+      <c r="P98" s="104" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
-      <c r="A95" s="95" t="s">
+    <row r="99" spans="1:16" ht="16">
+      <c r="A99" s="70" t="s">
         <v>185</v>
       </c>
-      <c r="B95" s="95" t="s">
+      <c r="B99" s="70" t="s">
         <v>181</v>
       </c>
-      <c r="C95" s="95">
+      <c r="C99" s="70">
         <v>3</v>
       </c>
-      <c r="D95" s="95" t="s">
+      <c r="D99" s="70" t="s">
         <v>186</v>
       </c>
-      <c r="E95" s="95" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" s="139">
+      <c r="E99" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" s="110">
         <v>41.651000000000003</v>
       </c>
-      <c r="G95" s="139">
+      <c r="G99" s="110">
         <v>20.068999999999999</v>
       </c>
-      <c r="H95" s="96">
+      <c r="H99" s="71">
         <v>290</v>
       </c>
-      <c r="I95" s="97">
+      <c r="I99" s="72">
         <v>10</v>
       </c>
-      <c r="J95" s="98">
+      <c r="J99" s="73">
         <v>1966</v>
       </c>
-      <c r="K95" s="97">
+      <c r="K99" s="72">
         <v>1986</v>
       </c>
-      <c r="L95" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="M95" s="100" t="s">
+      <c r="L99" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M99" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="N95" s="24" t="s">
+      <c r="N99" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="O95" s="25"/>
-      <c r="P95" s="133" t="s">
+      <c r="O99" s="17"/>
+      <c r="P99" s="104" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
-      <c r="A96" s="65" t="s">
+    <row r="100" spans="1:16" ht="16">
+      <c r="A100" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="65" t="s">
+      <c r="B100" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="65">
+      <c r="C100" s="53">
         <v>1</v>
       </c>
-      <c r="D96" s="65" t="s">
+      <c r="D100" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="E96" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F96" s="140">
+      <c r="E100" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" s="111">
         <v>33.613</v>
       </c>
-      <c r="G96" s="140">
+      <c r="G100" s="111">
         <v>36.146999999999998</v>
       </c>
-      <c r="H96" s="67">
+      <c r="H100" s="54">
         <v>887</v>
       </c>
-      <c r="I96" s="103"/>
-      <c r="J96" s="71">
+      <c r="I100" s="78"/>
+      <c r="J100" s="57">
         <v>1987</v>
       </c>
-      <c r="K96" s="70">
+      <c r="K100" s="55">
         <v>2005</v>
       </c>
-      <c r="L96" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="M96" s="104" t="s">
+      <c r="L100" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M100" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="N96" s="24" t="s">
+      <c r="N100" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O96" s="25"/>
-      <c r="P96" s="131" t="s">
+      <c r="O100" s="17"/>
+      <c r="P100" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
-      <c r="A97" s="65" t="s">
+    <row r="101" spans="1:16" ht="16">
+      <c r="A101" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B97" s="65" t="s">
+      <c r="B101" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="C97" s="65">
+      <c r="C101" s="53">
         <v>2</v>
       </c>
-      <c r="D97" s="65" t="s">
+      <c r="D101" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="E97" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F97" s="140">
+      <c r="E101" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" s="111">
         <v>33.618000000000002</v>
       </c>
-      <c r="G97" s="140">
+      <c r="G101" s="111">
         <v>36.180999999999997</v>
       </c>
-      <c r="H97" s="67">
+      <c r="H101" s="54">
         <v>853</v>
       </c>
-      <c r="I97" s="103"/>
-      <c r="J97" s="71">
+      <c r="I101" s="78"/>
+      <c r="J101" s="57">
         <v>1987</v>
       </c>
-      <c r="K97" s="70">
+      <c r="K101" s="55">
         <v>2005</v>
       </c>
-      <c r="L97" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="M97" s="105" t="s">
+      <c r="L101" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M101" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="N97" s="24" t="s">
+      <c r="N101" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O97" s="25"/>
-      <c r="P97" s="131" t="s">
+      <c r="O101" s="17"/>
+      <c r="P101" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
-      <c r="A98" s="65" t="s">
+    <row r="102" spans="1:16" ht="16">
+      <c r="A102" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B98" s="65" t="s">
+      <c r="B102" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="C98" s="65">
+      <c r="C102" s="53">
         <v>3</v>
       </c>
-      <c r="D98" s="65" t="s">
+      <c r="D102" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="E98" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F98" s="140">
+      <c r="E102" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="111">
         <v>33.247999999999998</v>
       </c>
-      <c r="G98" s="140">
+      <c r="G102" s="111">
         <v>35.695</v>
       </c>
-      <c r="H98" s="67">
+      <c r="H102" s="54">
         <v>390</v>
       </c>
-      <c r="I98" s="106">
+      <c r="I102" s="78">
         <v>120</v>
       </c>
-      <c r="J98" s="71">
+      <c r="J102" s="57">
         <v>1989</v>
       </c>
-      <c r="K98" s="70">
+      <c r="K102" s="55">
         <v>1999</v>
       </c>
-      <c r="L98" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="M98" s="105" t="s">
+      <c r="L102" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M102" s="80" t="s">
         <v>203</v>
       </c>
-      <c r="N98" s="24" t="s">
+      <c r="N102" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O98" s="61" t="s">
+      <c r="O102" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="P98" s="131" t="s">
+      <c r="P102" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
-      <c r="A99" s="65" t="s">
+    <row r="103" spans="1:16" ht="16">
+      <c r="A103" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B99" s="65" t="s">
+      <c r="B103" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="C99" s="65">
+      <c r="C103" s="53">
         <v>4</v>
       </c>
-      <c r="D99" s="65" t="s">
+      <c r="D103" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="E99" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F99" s="140">
+      <c r="E103" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F103" s="111">
         <v>33.249000000000002</v>
       </c>
-      <c r="G99" s="140">
+      <c r="G103" s="111">
         <v>35.652999999999999</v>
       </c>
-      <c r="H99" s="67">
+      <c r="H103" s="54">
         <v>195</v>
       </c>
-      <c r="I99" s="106">
+      <c r="I103" s="78">
         <v>290</v>
       </c>
-      <c r="J99" s="71">
+      <c r="J103" s="57">
         <v>1989</v>
       </c>
-      <c r="K99" s="70">
+      <c r="K103" s="55">
         <v>1999</v>
       </c>
-      <c r="L99" s="70" t="s">
-        <v>20</v>
-      </c>
-      <c r="M99" s="104" t="s">
+      <c r="L103" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M103" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="N99" s="24" t="s">
+      <c r="N103" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O99" s="61" t="s">
+      <c r="O103" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="P99" s="131" t="s">
+      <c r="P103" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
-      <c r="A100" s="65" t="s">
+    <row r="104" spans="1:16" ht="16">
+      <c r="A104" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B100" s="65" t="s">
+      <c r="B104" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="C100" s="65">
+      <c r="C104" s="53">
         <v>5</v>
       </c>
-      <c r="D100" s="65" t="s">
+      <c r="D104" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="E100" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F100" s="140">
+      <c r="E104" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" s="111">
         <v>34.01</v>
       </c>
-      <c r="G100" s="140">
+      <c r="G104" s="111">
         <v>35.828000000000003</v>
       </c>
-      <c r="H100" s="67">
+      <c r="H104" s="54">
         <v>1390</v>
       </c>
-      <c r="I100" s="70">
+      <c r="I104" s="55">
         <v>15</v>
       </c>
-      <c r="J100" s="71">
+      <c r="J104" s="57">
         <v>2014</v>
       </c>
-      <c r="K100" s="70">
+      <c r="K104" s="55">
         <v>2018</v>
       </c>
-      <c r="L100" s="70" t="s">
+      <c r="L104" s="55" t="s">
         <v>362</v>
       </c>
-      <c r="M100" s="104" t="s">
+      <c r="M104" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="N100" s="24" t="s">
+      <c r="N104" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O100" s="25"/>
-      <c r="P100" s="131" t="s">
+      <c r="O104" s="17"/>
+      <c r="P104" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
-      <c r="A101" s="65" t="s">
+    <row r="105" spans="1:16" ht="16">
+      <c r="A105" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B101" s="65" t="s">
+      <c r="B105" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="C101" s="65">
+      <c r="C105" s="53">
         <v>6</v>
       </c>
-      <c r="D101" s="65" t="s">
+      <c r="D105" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="E101" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F101" s="140">
+      <c r="E105" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" s="111">
         <v>33.944000000000003</v>
       </c>
-      <c r="G101" s="140">
+      <c r="G105" s="111">
         <v>35.637999999999998</v>
       </c>
-      <c r="H101" s="67">
+      <c r="H105" s="54">
         <v>56</v>
       </c>
-      <c r="I101" s="68"/>
-      <c r="J101" s="71">
+      <c r="I105" s="55"/>
+      <c r="J105" s="57">
         <v>2014</v>
       </c>
-      <c r="K101" s="70">
+      <c r="K105" s="55">
         <v>2018</v>
       </c>
-      <c r="L101" s="70" t="s">
+      <c r="L105" s="55" t="s">
         <v>362</v>
       </c>
-      <c r="M101" s="104" t="s">
+      <c r="M105" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="N101" s="24" t="s">
+      <c r="N105" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O101" s="25"/>
-      <c r="P101" s="131" t="s">
+      <c r="O105" s="17"/>
+      <c r="P105" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
-      <c r="A102" s="10" t="s">
+    <row r="106" spans="1:16" ht="16">
+      <c r="A106" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B106" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C102" s="107">
+      <c r="C106" s="81">
         <v>1</v>
       </c>
-      <c r="D102" s="107" t="s">
+      <c r="D106" s="81" t="s">
         <v>212</v>
       </c>
-      <c r="E102" s="107" t="s">
-        <v>19</v>
-      </c>
-      <c r="F102" s="108">
+      <c r="E106" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" s="82">
         <v>42.651800000000001</v>
       </c>
-      <c r="G102" s="108">
+      <c r="G106" s="82">
         <v>1.52E-2</v>
       </c>
-      <c r="H102" s="109">
+      <c r="H106" s="83">
         <v>2000</v>
       </c>
-      <c r="I102" s="110">
+      <c r="I106" s="84">
         <v>14.483000000000001</v>
       </c>
-      <c r="J102" s="111">
+      <c r="J106" s="85">
         <v>2018</v>
       </c>
-      <c r="K102" s="12">
+      <c r="K106" s="12">
         <v>2025</v>
       </c>
-      <c r="L102" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M102" s="112" t="s">
+      <c r="L106" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M106" s="86" t="s">
         <v>213</v>
       </c>
-      <c r="N102" s="24" t="s">
+      <c r="N106" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O102" s="61" t="s">
+      <c r="O106" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="P102" s="133" t="s">
+      <c r="P106" s="104" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
-      <c r="A103" s="107" t="s">
+    <row r="107" spans="1:16" ht="16">
+      <c r="A107" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="107" t="s">
+      <c r="B107" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C103" s="107">
+      <c r="C107" s="81">
         <v>2</v>
       </c>
-      <c r="D103" s="107" t="s">
+      <c r="D107" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="E103" s="107" t="s">
-        <v>19</v>
-      </c>
-      <c r="F103" s="108">
+      <c r="E107" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" s="82">
         <v>42.890999999999998</v>
       </c>
-      <c r="G103" s="108">
+      <c r="G107" s="82">
         <v>1.927</v>
       </c>
-      <c r="H103" s="109">
+      <c r="H107" s="83">
         <v>100</v>
       </c>
-      <c r="I103" s="110">
+      <c r="I107" s="84">
         <v>125</v>
       </c>
-      <c r="J103" s="111">
+      <c r="J107" s="85">
         <v>2019</v>
       </c>
-      <c r="K103" s="12">
+      <c r="K107" s="12">
         <v>2024</v>
       </c>
-      <c r="L103" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M103" s="94" t="s">
+      <c r="L107" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M107" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="N103" s="24" t="s">
+      <c r="N107" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O103" s="25"/>
-      <c r="P103" s="133" t="s">
+      <c r="O107" s="17"/>
+      <c r="P107" s="104" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
-      <c r="A104" s="107" t="s">
+    <row r="108" spans="1:16" ht="16">
+      <c r="A108" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="B104" s="107" t="s">
+      <c r="B108" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C104" s="107">
+      <c r="C108" s="81">
         <v>3</v>
       </c>
-      <c r="D104" s="107" t="s">
+      <c r="D108" s="81" t="s">
         <v>215</v>
       </c>
-      <c r="E104" s="107" t="s">
-        <v>19</v>
-      </c>
-      <c r="F104" s="108">
+      <c r="E108" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" s="82">
         <v>42.954999999999998</v>
       </c>
-      <c r="G104" s="108">
+      <c r="G108" s="82">
         <v>1.0309999999999999</v>
       </c>
-      <c r="H104" s="109">
+      <c r="H108" s="83">
         <v>450</v>
       </c>
-      <c r="I104" s="110">
+      <c r="I108" s="84">
         <v>13</v>
       </c>
-      <c r="J104" s="111">
+      <c r="J108" s="85">
         <v>2020</v>
       </c>
-      <c r="K104" s="12">
+      <c r="K108" s="12">
         <v>2024</v>
       </c>
-      <c r="L104" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M104" s="94" t="s">
+      <c r="L108" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M108" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="N104" s="24" t="s">
+      <c r="N108" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O104" s="25"/>
-      <c r="P104" s="133" t="s">
+      <c r="O108" s="17"/>
+      <c r="P108" s="104" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
-      <c r="A105" s="107" t="s">
+    <row r="109" spans="1:16" ht="16">
+      <c r="A109" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="B105" s="107" t="s">
+      <c r="B109" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C105" s="107">
+      <c r="C109" s="81">
         <v>4</v>
       </c>
-      <c r="D105" s="107" t="s">
+      <c r="D109" s="81" t="s">
         <v>217</v>
       </c>
-      <c r="E105" s="107" t="s">
-        <v>19</v>
-      </c>
-      <c r="F105" s="108">
+      <c r="E109" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" s="82">
         <v>42.99</v>
       </c>
-      <c r="G105" s="108">
+      <c r="G109" s="82">
         <v>1.048</v>
       </c>
-      <c r="H105" s="109">
+      <c r="H109" s="83">
         <v>500</v>
       </c>
-      <c r="I105" s="110">
+      <c r="I109" s="84">
         <v>11</v>
       </c>
-      <c r="J105" s="111">
+      <c r="J109" s="85">
         <v>2009</v>
       </c>
-      <c r="K105" s="12">
+      <c r="K109" s="12">
         <v>2024</v>
       </c>
-      <c r="L105" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M105" s="94" t="s">
+      <c r="L109" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M109" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="N105" s="24" t="s">
+      <c r="N109" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O105" s="25"/>
-      <c r="P105" s="133" t="s">
+      <c r="O109" s="17"/>
+      <c r="P109" s="104" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
-      <c r="A106" s="113" t="s">
+    <row r="110" spans="1:16" ht="16">
+      <c r="A110" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="B106" s="113" t="s">
+      <c r="B110" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="C106" s="113">
+      <c r="C110" s="87">
         <v>1</v>
       </c>
-      <c r="D106" s="113" t="s">
+      <c r="D110" s="87" t="s">
         <v>220</v>
       </c>
-      <c r="E106" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F106" s="144">
+      <c r="E110" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" s="115">
         <v>37.113</v>
       </c>
-      <c r="G106" s="144">
+      <c r="G110" s="115">
         <v>32.140999999999998</v>
       </c>
-      <c r="H106" s="114">
+      <c r="H110" s="88">
         <v>1100</v>
       </c>
-      <c r="I106" s="115">
+      <c r="I110" s="89">
         <v>85</v>
       </c>
-      <c r="J106" s="116">
+      <c r="J110" s="90">
         <v>2003</v>
       </c>
-      <c r="K106" s="115">
+      <c r="K110" s="89">
         <v>2019</v>
       </c>
-      <c r="L106" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="M106" s="117" t="s">
+      <c r="L110" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="M110" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="N106" s="24" t="s">
+      <c r="N110" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O106" s="61" t="s">
+      <c r="O110" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="P106" s="131" t="s">
+      <c r="P110" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
-      <c r="A107" s="113" t="s">
+    <row r="111" spans="1:16" ht="16">
+      <c r="A111" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="B107" s="113" t="s">
+      <c r="B111" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="C107" s="113">
+      <c r="C111" s="87">
         <v>2</v>
       </c>
-      <c r="D107" s="113" t="s">
+      <c r="D111" s="87" t="s">
         <v>223</v>
       </c>
-      <c r="E107" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F107" s="144">
+      <c r="E111" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" s="115">
         <v>37.094000000000001</v>
       </c>
-      <c r="G107" s="144">
+      <c r="G111" s="115">
         <v>30.581</v>
       </c>
-      <c r="H107" s="115">
+      <c r="H111" s="89">
         <v>300</v>
       </c>
-      <c r="I107" s="115">
+      <c r="I111" s="89">
         <v>2000</v>
       </c>
-      <c r="J107" s="115">
+      <c r="J111" s="89">
         <v>2003</v>
       </c>
-      <c r="K107" s="115">
+      <c r="K111" s="89">
         <v>2017</v>
       </c>
-      <c r="L107" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="M107" s="118" t="s">
+      <c r="L111" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="M111" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="N107" s="24" t="s">
+      <c r="N111" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O107" s="61" t="s">
+      <c r="O111" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="P107" s="131" t="s">
+      <c r="P111" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
-      <c r="A108" s="113" t="s">
+    <row r="112" spans="1:16" ht="16">
+      <c r="A112" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="B108" s="113" t="s">
+      <c r="B112" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="C108" s="113">
+      <c r="C112" s="87">
         <v>3</v>
       </c>
-      <c r="D108" s="113" t="s">
+      <c r="D112" s="87" t="s">
         <v>224</v>
       </c>
-      <c r="E108" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F108" s="144">
+      <c r="E112" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="115">
         <v>37.302</v>
       </c>
-      <c r="G108" s="144">
+      <c r="G112" s="115">
         <v>31.942</v>
       </c>
-      <c r="H108" s="115">
+      <c r="H112" s="89">
         <v>1099</v>
       </c>
-      <c r="I108" s="115">
+      <c r="I112" s="89">
         <v>70</v>
       </c>
-      <c r="J108" s="115">
+      <c r="J112" s="89">
         <v>2014</v>
       </c>
-      <c r="K108" s="115">
+      <c r="K112" s="89">
         <v>2025</v>
       </c>
-      <c r="L108" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="M108" s="113" t="s">
+      <c r="L112" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="M112" s="87" t="s">
         <v>225</v>
       </c>
-      <c r="N108" s="24" t="s">
+      <c r="N112" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O108" s="61"/>
-      <c r="P108" s="131" t="s">
+      <c r="O112" s="17"/>
+      <c r="P112" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
-      <c r="A109" s="113" t="s">
+    <row r="113" spans="1:16" ht="16">
+      <c r="A113" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="113" t="s">
+      <c r="B113" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="C109" s="113">
+      <c r="C113" s="87">
         <v>4</v>
       </c>
-      <c r="D109" s="113" t="s">
+      <c r="D113" s="87" t="s">
         <v>226</v>
       </c>
-      <c r="E109" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F109" s="144">
+      <c r="E113" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" s="115">
         <v>37.468000000000004</v>
       </c>
-      <c r="G109" s="144">
+      <c r="G113" s="115">
         <v>34.863</v>
       </c>
-      <c r="H109" s="115">
+      <c r="H113" s="89">
         <v>840</v>
       </c>
-      <c r="I109" s="115">
+      <c r="I113" s="89">
         <v>140</v>
       </c>
-      <c r="J109" s="115">
+      <c r="J113" s="89">
         <v>2011</v>
       </c>
-      <c r="K109" s="115">
+      <c r="K113" s="89">
         <v>2024</v>
       </c>
-      <c r="L109" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="M109" s="119" t="s">
+      <c r="L113" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="M113" s="93" t="s">
         <v>227</v>
       </c>
-      <c r="N109" s="24" t="s">
+      <c r="N113" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O109" s="61" t="s">
+      <c r="O113" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="P109" s="131" t="s">
+      <c r="P113" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
-      <c r="A110" s="113" t="s">
+    <row r="114" spans="1:16" ht="16">
+      <c r="A114" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="B110" s="113" t="s">
+      <c r="B114" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="C110" s="113">
+      <c r="C114" s="87">
         <v>5</v>
       </c>
-      <c r="D110" s="113" t="s">
+      <c r="D114" s="87" t="s">
         <v>228</v>
       </c>
-      <c r="E110" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F110" s="144">
+      <c r="E114" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" s="115">
         <v>37.771000000000001</v>
       </c>
-      <c r="G110" s="144">
+      <c r="G114" s="115">
         <v>35.396000000000001</v>
       </c>
-      <c r="H110" s="115">
+      <c r="H114" s="89">
         <v>660</v>
       </c>
-      <c r="I110" s="115">
+      <c r="I114" s="89">
         <v>350</v>
       </c>
-      <c r="J110" s="115">
+      <c r="J114" s="89">
         <v>2011</v>
       </c>
-      <c r="K110" s="115">
+      <c r="K114" s="89">
         <v>2017</v>
       </c>
-      <c r="L110" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="M110" s="119" t="s">
+      <c r="L114" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="M114" s="93" t="s">
         <v>229</v>
       </c>
-      <c r="N110" s="24" t="s">
+      <c r="N114" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O110" s="61" t="s">
+      <c r="O114" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="P110" s="131" t="s">
+      <c r="P114" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
-      <c r="A111" s="113" t="s">
+    <row r="115" spans="1:16" ht="16">
+      <c r="A115" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="B111" s="113" t="s">
+      <c r="B115" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="C111" s="113">
+      <c r="C115" s="87">
         <v>6</v>
       </c>
-      <c r="D111" s="113" t="s">
+      <c r="D115" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="E111" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" s="144">
+      <c r="E115" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" s="115">
         <v>38.814999999999998</v>
       </c>
-      <c r="G111" s="144">
+      <c r="G115" s="115">
         <v>35.863999999999997</v>
       </c>
-      <c r="H111" s="115">
+      <c r="H115" s="89">
         <v>1536</v>
       </c>
-      <c r="I111" s="115">
+      <c r="I115" s="89">
         <v>10</v>
       </c>
-      <c r="J111" s="115">
+      <c r="J115" s="89">
         <v>2002</v>
       </c>
-      <c r="K111" s="115">
+      <c r="K115" s="89">
         <v>2019</v>
       </c>
-      <c r="L111" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="M111" s="119" t="s">
+      <c r="L115" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="M115" s="93" t="s">
         <v>231</v>
       </c>
-      <c r="N111" s="24" t="s">
+      <c r="N115" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="O111" s="61" t="s">
+      <c r="O115" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="P111" s="131" t="s">
+      <c r="P115" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
-      <c r="A112" s="120" t="s">
+    <row r="116" spans="1:16" ht="16">
+      <c r="A116" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B112" s="120" t="s">
+      <c r="B116" s="94" t="s">
         <v>233</v>
       </c>
-      <c r="C112" s="120">
+      <c r="C116" s="94">
         <v>1</v>
       </c>
-      <c r="D112" s="120" t="s">
+      <c r="D116" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="E112" s="120"/>
-      <c r="F112" s="145">
+      <c r="E116" s="94"/>
+      <c r="F116" s="116">
         <v>31.375</v>
       </c>
-      <c r="G112" s="146">
+      <c r="G116" s="117">
         <v>49.84</v>
       </c>
-      <c r="H112" s="121">
+      <c r="H116" s="95">
         <v>490</v>
       </c>
-      <c r="I112" s="122"/>
-      <c r="J112" s="123">
+      <c r="I116" s="96"/>
+      <c r="J116" s="97">
         <v>2003</v>
       </c>
-      <c r="K112" s="124">
+      <c r="K116" s="98">
         <v>2011</v>
       </c>
-      <c r="L112" s="124" t="s">
-        <v>20</v>
-      </c>
-      <c r="M112" s="125" t="s">
+      <c r="L116" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="M116" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="N112" s="24" t="s">
+      <c r="N116" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O112" s="61"/>
-      <c r="P112" s="131" t="s">
+      <c r="O116" s="17"/>
+      <c r="P116" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
-      <c r="A113" s="120" t="s">
+    <row r="117" spans="1:16" ht="16">
+      <c r="A117" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B113" s="120" t="s">
+      <c r="B117" s="94" t="s">
         <v>233</v>
       </c>
-      <c r="C113" s="120">
+      <c r="C117" s="94">
         <v>2</v>
       </c>
-      <c r="D113" s="120" t="s">
+      <c r="D117" s="94" t="s">
         <v>236</v>
       </c>
-      <c r="E113" s="120"/>
-      <c r="F113" s="145">
+      <c r="E117" s="94"/>
+      <c r="F117" s="116">
         <v>31.256</v>
       </c>
-      <c r="G113" s="146">
+      <c r="G117" s="117">
         <v>49.968000000000004</v>
       </c>
-      <c r="H113" s="121">
+      <c r="H117" s="95">
         <v>675</v>
       </c>
-      <c r="I113" s="122"/>
-      <c r="J113" s="123">
+      <c r="I117" s="96"/>
+      <c r="J117" s="97">
         <v>2010</v>
       </c>
-      <c r="K113" s="124">
+      <c r="K117" s="98">
         <v>2017</v>
       </c>
-      <c r="L113" s="124" t="s">
-        <v>20</v>
-      </c>
-      <c r="M113" s="125" t="s">
+      <c r="L117" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="M117" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="N113" s="24" t="s">
+      <c r="N117" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O113" s="61"/>
-      <c r="P113" s="131" t="s">
+      <c r="O117" s="17"/>
+      <c r="P117" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
-      <c r="A114" s="120" t="s">
+    <row r="118" spans="1:16" ht="16">
+      <c r="A118" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B114" s="120" t="s">
+      <c r="B118" s="94" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="120">
+      <c r="C118" s="94">
         <v>3</v>
       </c>
-      <c r="D114" s="120" t="s">
+      <c r="D118" s="94" t="s">
         <v>237</v>
       </c>
-      <c r="E114" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F114" s="145">
+      <c r="E118" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F118" s="116">
         <v>34.39</v>
       </c>
-      <c r="G114" s="145">
+      <c r="G118" s="116">
         <v>47.436999999999998</v>
       </c>
-      <c r="H114" s="124">
+      <c r="H118" s="98">
         <v>1290</v>
       </c>
-      <c r="I114" s="126"/>
-      <c r="J114" s="124">
+      <c r="I118" s="98"/>
+      <c r="J118" s="98">
         <v>1970</v>
       </c>
-      <c r="K114" s="124">
+      <c r="K118" s="98">
         <v>2009</v>
       </c>
-      <c r="L114" s="124" t="s">
+      <c r="L118" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="M114" s="125" t="s">
+      <c r="M118" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="N114" s="24" t="s">
+      <c r="N118" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O114" s="127"/>
-      <c r="P114" s="131" t="s">
+      <c r="O118" s="100"/>
+      <c r="P118" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
-      <c r="A115" s="120" t="s">
+    <row r="119" spans="1:16" ht="16">
+      <c r="A119" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B115" s="120" t="s">
+      <c r="B119" s="94" t="s">
         <v>233</v>
       </c>
-      <c r="C115" s="120">
+      <c r="C119" s="94">
         <v>4</v>
       </c>
-      <c r="D115" s="120" t="s">
+      <c r="D119" s="94" t="s">
         <v>238</v>
       </c>
-      <c r="E115" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F115" s="145">
+      <c r="E119" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" s="116">
         <v>32.500999999999998</v>
       </c>
-      <c r="G115" s="145">
+      <c r="G119" s="116">
         <v>50.215000000000003</v>
       </c>
-      <c r="H115" s="124">
+      <c r="H119" s="98">
         <v>2220</v>
       </c>
-      <c r="I115" s="126"/>
-      <c r="J115" s="124">
+      <c r="I119" s="98"/>
+      <c r="J119" s="98">
         <v>1998</v>
       </c>
-      <c r="K115" s="124">
+      <c r="K119" s="98">
         <v>2013</v>
       </c>
-      <c r="L115" s="124" t="s">
+      <c r="L119" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="M115" s="125" t="s">
+      <c r="M119" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="N115" s="24" t="s">
+      <c r="N119" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O115" s="127"/>
-      <c r="P115" s="131" t="s">
+      <c r="O119" s="100"/>
+      <c r="P119" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
-      <c r="A116" s="120" t="s">
+    <row r="120" spans="1:16" ht="16">
+      <c r="A120" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="120" t="s">
+      <c r="B120" s="94" t="s">
         <v>233</v>
       </c>
-      <c r="C116" s="120">
+      <c r="C120" s="94">
         <v>5</v>
       </c>
-      <c r="D116" s="120" t="s">
+      <c r="D120" s="94" t="s">
         <v>239</v>
       </c>
-      <c r="E116" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F116" s="145">
+      <c r="E120" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120" s="116">
         <v>32.216999999999999</v>
       </c>
-      <c r="G116" s="145">
+      <c r="G120" s="116">
         <v>50.543999999999997</v>
       </c>
-      <c r="H116" s="124">
+      <c r="H120" s="98">
         <v>2016</v>
       </c>
-      <c r="I116" s="122"/>
-      <c r="J116" s="124">
+      <c r="I120" s="96"/>
+      <c r="J120" s="98">
         <v>1998</v>
       </c>
-      <c r="K116" s="124">
+      <c r="K120" s="98">
         <v>2014</v>
       </c>
-      <c r="L116" s="124" t="s">
+      <c r="L120" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="M116" s="125" t="s">
+      <c r="M120" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="N116" s="24" t="s">
+      <c r="N120" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O116" s="127"/>
-      <c r="P116" s="131" t="s">
+      <c r="O120" s="100"/>
+      <c r="P120" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
-      <c r="A117" s="120" t="s">
+    <row r="121" spans="1:16" ht="16">
+      <c r="A121" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B117" s="120" t="s">
+      <c r="B121" s="94" t="s">
         <v>233</v>
       </c>
-      <c r="C117" s="120">
+      <c r="C121" s="94">
         <v>6</v>
       </c>
-      <c r="D117" s="120" t="s">
+      <c r="D121" s="94" t="s">
         <v>240</v>
       </c>
-      <c r="E117" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F117" s="145">
+      <c r="E121" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" s="116">
         <v>29.783000000000001</v>
       </c>
-      <c r="G117" s="146">
+      <c r="G121" s="117">
         <v>51.582999999999998</v>
       </c>
-      <c r="H117" s="121">
+      <c r="H121" s="95">
         <v>820</v>
       </c>
-      <c r="I117" s="122"/>
-      <c r="J117" s="123">
+      <c r="I121" s="96"/>
+      <c r="J121" s="97">
         <v>1984</v>
       </c>
-      <c r="K117" s="124">
+      <c r="K121" s="98">
         <v>2000</v>
       </c>
-      <c r="L117" s="124" t="s">
+      <c r="L121" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="M117" s="125" t="s">
+      <c r="M121" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="N117" s="24" t="s">
+      <c r="N121" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="O117" s="127"/>
-      <c r="P117" s="131" t="s">
+      <c r="O121" s="100"/>
+      <c r="P121" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
-      <c r="A118" s="120" t="s">
+    <row r="122" spans="1:16" ht="16">
+      <c r="A122" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B118" s="120" t="s">
+      <c r="B122" s="94" t="s">
         <v>242</v>
       </c>
-      <c r="C118" s="120">
+      <c r="C122" s="94">
         <v>7</v>
       </c>
-      <c r="D118" s="120" t="s">
+      <c r="D122" s="94" t="s">
         <v>243</v>
       </c>
-      <c r="E118" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F118" s="145">
+      <c r="E122" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F122" s="116">
         <v>35.6</v>
       </c>
-      <c r="G118" s="146">
+      <c r="G122" s="117">
         <v>45.4</v>
       </c>
-      <c r="H118" s="121">
+      <c r="H122" s="95">
         <v>1625</v>
       </c>
-      <c r="I118" s="122"/>
-      <c r="J118" s="123">
+      <c r="I122" s="96"/>
+      <c r="J122" s="97">
         <v>2002</v>
       </c>
-      <c r="K118" s="124">
+      <c r="K122" s="98">
         <v>2003</v>
       </c>
-      <c r="L118" s="124" t="s">
-        <v>20</v>
-      </c>
-      <c r="M118" s="125" t="s">
+      <c r="L122" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="M122" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="N118" s="24" t="s">
+      <c r="N122" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O118" s="127"/>
-      <c r="P118" s="134" t="s">
+      <c r="O122" s="100"/>
+      <c r="P122" s="105" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
-      <c r="A119" s="120" t="s">
+    <row r="123" spans="1:16" ht="16">
+      <c r="A123" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="B119" s="120" t="s">
+      <c r="B123" s="94" t="s">
         <v>242</v>
       </c>
-      <c r="C119" s="120">
+      <c r="C123" s="94">
         <v>8</v>
       </c>
-      <c r="D119" s="120" t="s">
+      <c r="D123" s="94" t="s">
         <v>244</v>
       </c>
-      <c r="E119" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F119" s="145">
+      <c r="E123" s="94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" s="116">
         <v>35.380000000000003</v>
       </c>
-      <c r="G119" s="146">
+      <c r="G123" s="117">
         <v>45.83</v>
       </c>
-      <c r="H119" s="121">
+      <c r="H123" s="95">
         <v>515</v>
       </c>
-      <c r="I119" s="122"/>
-      <c r="J119" s="123">
+      <c r="I123" s="96"/>
+      <c r="J123" s="97">
         <v>2004</v>
       </c>
-      <c r="K119" s="124">
+      <c r="K123" s="98">
         <v>2006</v>
       </c>
-      <c r="L119" s="124" t="s">
-        <v>20</v>
-      </c>
-      <c r="M119" s="125" t="s">
+      <c r="L123" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="M123" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="N119" s="24" t="s">
+      <c r="N123" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O119" s="127"/>
-      <c r="P119" s="132" t="s">
+      <c r="O123" s="100"/>
+      <c r="P123" s="104" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="14.25">
-      <c r="D120" s="128"/>
-    </row>
-    <row r="121" spans="1:16" ht="14.25">
-      <c r="D121" s="129"/>
-      <c r="E121" s="130"/>
-      <c r="F121" s="129"/>
-      <c r="G121" s="130"/>
-      <c r="H121" s="130"/>
-      <c r="I121" s="130"/>
-      <c r="J121" s="130"/>
-      <c r="K121" s="129"/>
-      <c r="L121" s="129"/>
-      <c r="M121" s="130"/>
-      <c r="N121" s="129"/>
+    <row r="124" spans="1:16" ht="14">
+      <c r="D124" s="101"/>
+    </row>
+    <row r="125" spans="1:16" ht="14">
+      <c r="D125" s="102"/>
+      <c r="E125" s="103"/>
+      <c r="F125" s="102"/>
+      <c r="G125" s="103"/>
+      <c r="H125" s="103"/>
+      <c r="I125" s="103"/>
+      <c r="J125" s="103"/>
+      <c r="K125" s="102"/>
+      <c r="L125" s="102"/>
+      <c r="M125" s="103"/>
+      <c r="N125" s="102"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M111" r:id="rId1"/>
-    <hyperlink ref="M110" r:id="rId2"/>
-    <hyperlink ref="M109" r:id="rId3"/>
-    <hyperlink ref="M107" r:id="rId4"/>
-    <hyperlink ref="M106" r:id="rId5"/>
-    <hyperlink ref="M102" r:id="rId6"/>
-    <hyperlink ref="M88" r:id="rId7"/>
-    <hyperlink ref="M87" r:id="rId8"/>
-    <hyperlink ref="M86" r:id="rId9"/>
-    <hyperlink ref="M85" r:id="rId10"/>
-    <hyperlink ref="M84" r:id="rId11"/>
-    <hyperlink ref="M83" r:id="rId12"/>
-    <hyperlink ref="M82" r:id="rId13"/>
-    <hyperlink ref="M81" r:id="rId14"/>
-    <hyperlink ref="M80" r:id="rId15"/>
-    <hyperlink ref="M79" r:id="rId16"/>
-    <hyperlink ref="M78" r:id="rId17"/>
-    <hyperlink ref="M77" r:id="rId18"/>
-    <hyperlink ref="M76" r:id="rId19"/>
-    <hyperlink ref="M74" r:id="rId20"/>
-    <hyperlink ref="M73" r:id="rId21"/>
-    <hyperlink ref="M72" r:id="rId22"/>
-    <hyperlink ref="M71" r:id="rId23"/>
-    <hyperlink ref="M70" r:id="rId24"/>
-    <hyperlink ref="M69" r:id="rId25"/>
-    <hyperlink ref="M68" r:id="rId26"/>
-    <hyperlink ref="M59" r:id="rId27"/>
-    <hyperlink ref="M58" r:id="rId28"/>
-    <hyperlink ref="M57" r:id="rId29"/>
-    <hyperlink ref="M56" r:id="rId30"/>
-    <hyperlink ref="M52" r:id="rId31"/>
-    <hyperlink ref="M51" r:id="rId32"/>
-    <hyperlink ref="M47" r:id="rId33"/>
-    <hyperlink ref="M45" r:id="rId34"/>
-    <hyperlink ref="M44" r:id="rId35"/>
-    <hyperlink ref="M43" r:id="rId36"/>
-    <hyperlink ref="M42" r:id="rId37"/>
-    <hyperlink ref="M41" r:id="rId38"/>
-    <hyperlink ref="M40" r:id="rId39"/>
-    <hyperlink ref="M39" r:id="rId40"/>
-    <hyperlink ref="M38" r:id="rId41"/>
-    <hyperlink ref="M37" r:id="rId42"/>
-    <hyperlink ref="M36" r:id="rId43"/>
-    <hyperlink ref="M35" r:id="rId44"/>
-    <hyperlink ref="M34" r:id="rId45"/>
-    <hyperlink ref="M33" r:id="rId46"/>
-    <hyperlink ref="M32" r:id="rId47"/>
-    <hyperlink ref="M31" r:id="rId48"/>
-    <hyperlink ref="M30" r:id="rId49"/>
-    <hyperlink ref="M29" r:id="rId50"/>
-    <hyperlink ref="M28" r:id="rId51"/>
-    <hyperlink ref="M27" r:id="rId52"/>
-    <hyperlink ref="M26" r:id="rId53"/>
-    <hyperlink ref="M25" r:id="rId54"/>
-    <hyperlink ref="M24" r:id="rId55"/>
-    <hyperlink ref="M23" r:id="rId56"/>
-    <hyperlink ref="M22" r:id="rId57"/>
-    <hyperlink ref="M21" r:id="rId58"/>
-    <hyperlink ref="M20" r:id="rId59"/>
-    <hyperlink ref="M19" r:id="rId60"/>
-    <hyperlink ref="M18" r:id="rId61"/>
-    <hyperlink ref="M17" r:id="rId62"/>
-    <hyperlink ref="M16" r:id="rId63"/>
-    <hyperlink ref="M15" r:id="rId64"/>
-    <hyperlink ref="M14" r:id="rId65"/>
-    <hyperlink ref="M13" r:id="rId66"/>
-    <hyperlink ref="M12" r:id="rId67"/>
-    <hyperlink ref="M11" r:id="rId68"/>
-    <hyperlink ref="M10" r:id="rId69"/>
-    <hyperlink ref="M9" r:id="rId70"/>
-    <hyperlink ref="M8" r:id="rId71"/>
-    <hyperlink ref="M7" r:id="rId72"/>
-    <hyperlink ref="M6" r:id="rId73"/>
-    <hyperlink ref="M5" r:id="rId74"/>
-    <hyperlink ref="M4" r:id="rId75"/>
-    <hyperlink ref="M3" r:id="rId76"/>
-    <hyperlink ref="M2" r:id="rId77"/>
+    <hyperlink ref="M115" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M114" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M113" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M111" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M110" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M106" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M92" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M91" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="M90" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M89" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="M88" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M87" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="M86" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M85" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="M84" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M83" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M82" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M77" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="M76" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="M74" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M73" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M72" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M71" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M70" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="M69" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M68" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="M59" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="M58" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="M57" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="M56" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="M52" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="M51" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="M47" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="M45" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="M44" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M43" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="M42" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="M41" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="M39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M38" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="M37" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="M36" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="M35" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="M34" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="M33" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="M32" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M31" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="M30" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="M29" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="M28" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="M27" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="M26" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M25" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="M24" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="M23" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="M22" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="M21" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="M20" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="M19" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="M18" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="M17" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="M16" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="M15" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="M14" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="M13" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="M12" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="M11" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="M10" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="M9" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="M8" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="M7" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="M6" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="M5" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="M4" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="M3" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="M2" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Kameraman_metadata.xlsx
+++ b/Kameraman_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/selimcalli/Documents/onemli belgeler/04-PROJELER/EU PROJECT/02_DATA/Mediterranean/00_ALL_SPRING_LIST/02_discharge_edited/01_Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E755788D-1259-A649-9FA3-453A52692AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085E5FCA-463B-4E41-AB36-810BE931ABCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="382">
   <si>
     <t>Region</t>
   </si>
@@ -529,9 +529,6 @@
   </si>
   <si>
     <t>Open data, Serbian open license</t>
-  </si>
-  <si>
-    <t>Carpathians/Bohemian</t>
   </si>
   <si>
     <t>Czechia</t>
@@ -1369,6 +1366,51 @@
   <si>
     <t>Kis-Tohonya</t>
   </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Abator</t>
+  </si>
+  <si>
+    <t>Ovid</t>
+  </si>
+  <si>
+    <t>Muncel</t>
+  </si>
+  <si>
+    <t>National Institute for Meteorology and Hidrology</t>
+  </si>
+  <si>
+    <t>General Directorate of Water Management, Hungary</t>
+  </si>
+  <si>
+    <t>Istvan GaborHatvani, Zoltan Kern</t>
+  </si>
+  <si>
+    <t>Virgil Dragusin</t>
+  </si>
+  <si>
+    <t>CAR_09_HU</t>
+  </si>
+  <si>
+    <t>CAR_10_HU</t>
+  </si>
+  <si>
+    <t>CAR_11_HU</t>
+  </si>
+  <si>
+    <t>CAR_12_HU</t>
+  </si>
+  <si>
+    <t>CAR_13_RO</t>
+  </si>
+  <si>
+    <t>CAR_14_RO</t>
+  </si>
+  <si>
+    <t>CAR_15_RO</t>
+  </si>
 </sst>
 </file>
 
@@ -1381,7 +1423,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1581,8 +1623,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1699,7 +1748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1838,7 +1893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1947,16 +2002,10 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2083,23 +2132,51 @@
     <xf numFmtId="166" fontId="3" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2319,7 +2396,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -2398,10 +2475,10 @@
       <c r="E2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="106">
+      <c r="F2" s="104">
         <v>47.36</v>
       </c>
-      <c r="G2" s="106">
+      <c r="G2" s="104">
         <v>10.172000000000001</v>
       </c>
       <c r="H2" s="12">
@@ -2446,10 +2523,10 @@
       <c r="E3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="106">
+      <c r="F3" s="104">
         <v>47.670999999999999</v>
       </c>
-      <c r="G3" s="106">
+      <c r="G3" s="104">
         <v>12.188000000000001</v>
       </c>
       <c r="H3" s="12">
@@ -2475,7 +2552,7 @@
         <v>23</v>
       </c>
       <c r="P3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1">
@@ -2494,10 +2571,10 @@
       <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="106">
+      <c r="F4" s="104">
         <v>47.807000000000002</v>
       </c>
-      <c r="G4" s="106">
+      <c r="G4" s="104">
         <v>14.096</v>
       </c>
       <c r="H4" s="12">
@@ -2523,7 +2600,7 @@
         <v>23</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1">
@@ -2542,10 +2619,10 @@
       <c r="E5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="106">
+      <c r="F5" s="104">
         <v>47.545000000000002</v>
       </c>
-      <c r="G5" s="106">
+      <c r="G5" s="104">
         <v>13.332000000000001</v>
       </c>
       <c r="H5" s="12">
@@ -2571,7 +2648,7 @@
         <v>23</v>
       </c>
       <c r="P5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1">
@@ -2588,10 +2665,10 @@
         <v>29</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="106">
+      <c r="F6" s="104">
         <v>47.316000000000003</v>
       </c>
-      <c r="G6" s="106">
+      <c r="G6" s="104">
         <v>10.497999999999999</v>
       </c>
       <c r="H6" s="12">
@@ -2617,7 +2694,7 @@
         <v>23</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1">
@@ -2636,10 +2713,10 @@
       <c r="E7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="106">
+      <c r="F7" s="104">
         <v>47.530999999999999</v>
       </c>
-      <c r="G7" s="106">
+      <c r="G7" s="104">
         <v>14.609</v>
       </c>
       <c r="H7" s="12">
@@ -2665,7 +2742,7 @@
         <v>23</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1">
@@ -2684,10 +2761,10 @@
       <c r="E8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="106">
+      <c r="F8" s="104">
         <v>46.743000000000002</v>
       </c>
-      <c r="G8" s="106">
+      <c r="G8" s="104">
         <v>13.331</v>
       </c>
       <c r="H8" s="12">
@@ -2713,7 +2790,7 @@
         <v>23</v>
       </c>
       <c r="P8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1">
@@ -2732,10 +2809,10 @@
       <c r="E9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="106">
+      <c r="F9" s="104">
         <v>46.984999999999999</v>
       </c>
-      <c r="G9" s="106">
+      <c r="G9" s="104">
         <v>9.9320000000000004</v>
       </c>
       <c r="H9" s="12">
@@ -2761,7 +2838,7 @@
         <v>23</v>
       </c>
       <c r="P9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1">
@@ -2780,10 +2857,10 @@
       <c r="E10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F10" s="104">
         <v>47.383000000000003</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="104">
         <v>10.047000000000001</v>
       </c>
       <c r="H10" s="12">
@@ -2809,7 +2886,7 @@
         <v>23</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1">
@@ -2828,10 +2905,10 @@
       <c r="E11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="106">
+      <c r="F11" s="104">
         <v>47.601999999999997</v>
       </c>
-      <c r="G11" s="106">
+      <c r="G11" s="104">
         <v>13.138</v>
       </c>
       <c r="H11" s="12">
@@ -2857,7 +2934,7 @@
         <v>23</v>
       </c>
       <c r="P11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1">
@@ -2876,10 +2953,10 @@
       <c r="E12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="106">
+      <c r="F12" s="104">
         <v>47.908999999999999</v>
       </c>
-      <c r="G12" s="106">
+      <c r="G12" s="104">
         <v>15.202999999999999</v>
       </c>
       <c r="H12" s="12">
@@ -2905,7 +2982,7 @@
         <v>23</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1">
@@ -2924,10 +3001,10 @@
       <c r="E13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="106">
+      <c r="F13" s="104">
         <v>47.21</v>
       </c>
-      <c r="G13" s="106">
+      <c r="G13" s="104">
         <v>15.348000000000001</v>
       </c>
       <c r="H13" s="12">
@@ -2953,7 +3030,7 @@
         <v>23</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1">
@@ -2972,10 +3049,10 @@
       <c r="E14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="104">
         <v>47.3</v>
       </c>
-      <c r="G14" s="106">
+      <c r="G14" s="104">
         <v>10.722</v>
       </c>
       <c r="H14" s="12">
@@ -3001,7 +3078,7 @@
         <v>23</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.75" customHeight="1">
@@ -3020,10 +3097,10 @@
       <c r="E15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="106">
+      <c r="F15" s="104">
         <v>47.546999999999997</v>
       </c>
-      <c r="G15" s="106">
+      <c r="G15" s="104">
         <v>13.659000000000001</v>
       </c>
       <c r="H15" s="12">
@@ -3049,7 +3126,7 @@
         <v>23</v>
       </c>
       <c r="P15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" customHeight="1">
@@ -3068,10 +3145,10 @@
       <c r="E16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="106">
+      <c r="F16" s="104">
         <v>47.786000000000001</v>
       </c>
-      <c r="G16" s="106">
+      <c r="G16" s="104">
         <v>13.734</v>
       </c>
       <c r="H16" s="12">
@@ -3097,7 +3174,7 @@
         <v>23</v>
       </c>
       <c r="P16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15.75" customHeight="1">
@@ -3116,10 +3193,10 @@
       <c r="E17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="106">
+      <c r="F17" s="104">
         <v>46.725000000000001</v>
       </c>
-      <c r="G17" s="106">
+      <c r="G17" s="104">
         <v>13.042999999999999</v>
       </c>
       <c r="H17" s="12">
@@ -3145,7 +3222,7 @@
         <v>23</v>
       </c>
       <c r="P17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="15.75" customHeight="1">
@@ -3164,10 +3241,10 @@
       <c r="E18" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="106">
+      <c r="F18" s="104">
         <v>47.253</v>
       </c>
-      <c r="G18" s="106">
+      <c r="G18" s="104">
         <v>13.414</v>
       </c>
       <c r="H18" s="12">
@@ -3193,7 +3270,7 @@
         <v>23</v>
       </c>
       <c r="P18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15.75" customHeight="1">
@@ -3212,10 +3289,10 @@
       <c r="E19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="106">
+      <c r="F19" s="104">
         <v>46.951999999999998</v>
       </c>
-      <c r="G19" s="106">
+      <c r="G19" s="104">
         <v>9.9109999999999996</v>
       </c>
       <c r="H19" s="12">
@@ -3241,7 +3318,7 @@
         <v>23</v>
       </c>
       <c r="P19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15.75" customHeight="1">
@@ -3260,10 +3337,10 @@
       <c r="E20" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="106">
+      <c r="F20" s="104">
         <v>47.564</v>
       </c>
-      <c r="G20" s="106">
+      <c r="G20" s="104">
         <v>13.826000000000001</v>
       </c>
       <c r="H20" s="12">
@@ -3289,7 +3366,7 @@
         <v>23</v>
       </c>
       <c r="P20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1">
@@ -3308,10 +3385,10 @@
       <c r="E21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="106">
+      <c r="F21" s="104">
         <v>46.832999999999998</v>
       </c>
-      <c r="G21" s="106">
+      <c r="G21" s="104">
         <v>13.769</v>
       </c>
       <c r="H21" s="12">
@@ -3337,7 +3414,7 @@
         <v>23</v>
       </c>
       <c r="P21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1">
@@ -3356,10 +3433,10 @@
       <c r="E22" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="106">
+      <c r="F22" s="104">
         <v>47.704999999999998</v>
       </c>
-      <c r="G22" s="106">
+      <c r="G22" s="104">
         <v>15.324999999999999</v>
       </c>
       <c r="H22" s="12">
@@ -3385,7 +3462,7 @@
         <v>23</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1">
@@ -3404,10 +3481,10 @@
       <c r="E23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="106">
+      <c r="F23" s="104">
         <v>47.692999999999998</v>
       </c>
-      <c r="G23" s="106">
+      <c r="G23" s="104">
         <v>14.276</v>
       </c>
       <c r="H23" s="12">
@@ -3433,7 +3510,7 @@
         <v>23</v>
       </c>
       <c r="P23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1">
@@ -3452,10 +3529,10 @@
       <c r="E24" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="106">
+      <c r="F24" s="104">
         <v>47.036000000000001</v>
       </c>
-      <c r="G24" s="106">
+      <c r="G24" s="104">
         <v>14.374000000000001</v>
       </c>
       <c r="H24" s="12">
@@ -3481,7 +3558,7 @@
         <v>23</v>
       </c>
       <c r="P24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1">
@@ -3500,10 +3577,10 @@
       <c r="E25" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="106">
+      <c r="F25" s="104">
         <v>47.43</v>
       </c>
-      <c r="G25" s="106">
+      <c r="G25" s="104">
         <v>12.693</v>
       </c>
       <c r="H25" s="12">
@@ -3529,7 +3606,7 @@
         <v>23</v>
       </c>
       <c r="P25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15.75" customHeight="1">
@@ -3548,10 +3625,10 @@
       <c r="E26" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="106">
+      <c r="F26" s="104">
         <v>47.843000000000004</v>
       </c>
-      <c r="G26" s="106">
+      <c r="G26" s="104">
         <v>14.879</v>
       </c>
       <c r="H26" s="12">
@@ -3577,7 +3654,7 @@
         <v>23</v>
       </c>
       <c r="P26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="16">
@@ -3596,10 +3673,10 @@
       <c r="E27" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="106">
+      <c r="F27" s="104">
         <v>47.755000000000003</v>
       </c>
-      <c r="G27" s="106">
+      <c r="G27" s="104">
         <v>14.315</v>
       </c>
       <c r="H27" s="12">
@@ -3625,7 +3702,7 @@
         <v>23</v>
       </c>
       <c r="P27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="16">
@@ -3644,10 +3721,10 @@
       <c r="E28" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F28" s="106">
+      <c r="F28" s="104">
         <v>47.546999999999997</v>
       </c>
-      <c r="G28" s="106">
+      <c r="G28" s="104">
         <v>13.867000000000001</v>
       </c>
       <c r="H28" s="12">
@@ -3673,7 +3750,7 @@
         <v>23</v>
       </c>
       <c r="P28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="16">
@@ -3692,10 +3769,10 @@
       <c r="E29" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="106">
+      <c r="F29" s="104">
         <v>47.582999999999998</v>
       </c>
-      <c r="G29" s="106">
+      <c r="G29" s="104">
         <v>14.031000000000001</v>
       </c>
       <c r="H29" s="12">
@@ -3721,7 +3798,7 @@
         <v>23</v>
       </c>
       <c r="P29" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="16">
@@ -3740,10 +3817,10 @@
       <c r="E30" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="106">
+      <c r="F30" s="104">
         <v>47.433999999999997</v>
       </c>
-      <c r="G30" s="106">
+      <c r="G30" s="104">
         <v>12.58</v>
       </c>
       <c r="H30" s="12">
@@ -3769,7 +3846,7 @@
         <v>23</v>
       </c>
       <c r="P30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="16">
@@ -3788,10 +3865,10 @@
       <c r="E31" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="106">
+      <c r="F31" s="104">
         <v>47.609000000000002</v>
       </c>
-      <c r="G31" s="106">
+      <c r="G31" s="104">
         <v>14.849</v>
       </c>
       <c r="H31" s="12">
@@ -3817,7 +3894,7 @@
         <v>23</v>
       </c>
       <c r="P31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="16">
@@ -3836,10 +3913,10 @@
       <c r="E32" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="106">
+      <c r="F32" s="104">
         <v>47.374000000000002</v>
       </c>
-      <c r="G32" s="106">
+      <c r="G32" s="104">
         <v>11.005000000000001</v>
       </c>
       <c r="H32" s="12">
@@ -3865,7 +3942,7 @@
         <v>23</v>
       </c>
       <c r="P32" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="16">
@@ -3884,10 +3961,10 @@
       <c r="E33" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F33" s="106">
+      <c r="F33" s="104">
         <v>47.566000000000003</v>
       </c>
-      <c r="G33" s="106">
+      <c r="G33" s="104">
         <v>13.118</v>
       </c>
       <c r="H33" s="12">
@@ -3913,7 +3990,7 @@
         <v>23</v>
       </c>
       <c r="P33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16">
@@ -3932,10 +4009,10 @@
       <c r="E34" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="106">
+      <c r="F34" s="104">
         <v>47.426000000000002</v>
       </c>
-      <c r="G34" s="106">
+      <c r="G34" s="104">
         <v>11.483000000000001</v>
       </c>
       <c r="H34" s="12">
@@ -3961,7 +4038,7 @@
         <v>23</v>
       </c>
       <c r="P34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="16">
@@ -3980,10 +4057,10 @@
       <c r="E35" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="106">
+      <c r="F35" s="104">
         <v>47.683</v>
       </c>
-      <c r="G35" s="106">
+      <c r="G35" s="104">
         <v>15.567</v>
       </c>
       <c r="H35" s="12">
@@ -4009,7 +4086,7 @@
         <v>23</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="16">
@@ -4028,10 +4105,10 @@
       <c r="E36" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="106">
+      <c r="F36" s="104">
         <v>47.814</v>
       </c>
-      <c r="G36" s="106">
+      <c r="G36" s="104">
         <v>14.768000000000001</v>
       </c>
       <c r="H36" s="12">
@@ -4057,7 +4134,7 @@
         <v>23</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="16">
@@ -4076,10 +4153,10 @@
       <c r="E37" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="106">
+      <c r="F37" s="104">
         <v>47.825000000000003</v>
       </c>
-      <c r="G37" s="106">
+      <c r="G37" s="104">
         <v>14.353</v>
       </c>
       <c r="H37" s="12">
@@ -4105,7 +4182,7 @@
         <v>23</v>
       </c>
       <c r="P37" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="16">
@@ -4124,10 +4201,10 @@
       <c r="E38" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F38" s="106">
+      <c r="F38" s="104">
         <v>47.787999999999997</v>
       </c>
-      <c r="G38" s="106">
+      <c r="G38" s="104">
         <v>14.206</v>
       </c>
       <c r="H38" s="12">
@@ -4153,7 +4230,7 @@
         <v>23</v>
       </c>
       <c r="P38" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="16">
@@ -4172,10 +4249,10 @@
       <c r="E39" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F39" s="106">
+      <c r="F39" s="104">
         <v>47.731000000000002</v>
       </c>
-      <c r="G39" s="106">
+      <c r="G39" s="104">
         <v>15.488</v>
       </c>
       <c r="H39" s="12">
@@ -4201,7 +4278,7 @@
         <v>23</v>
       </c>
       <c r="P39" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="16">
@@ -4220,10 +4297,10 @@
       <c r="E40" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="106">
+      <c r="F40" s="104">
         <v>46.63</v>
       </c>
-      <c r="G40" s="106">
+      <c r="G40" s="104">
         <v>13.804</v>
       </c>
       <c r="H40" s="12">
@@ -4249,7 +4326,7 @@
         <v>23</v>
       </c>
       <c r="P40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="16">
@@ -4268,10 +4345,10 @@
       <c r="E41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F41" s="106">
+      <c r="F41" s="104">
         <v>47.335000000000001</v>
       </c>
-      <c r="G41" s="106">
+      <c r="G41" s="104">
         <v>10.927</v>
       </c>
       <c r="H41" s="12">
@@ -4297,7 +4374,7 @@
         <v>23</v>
       </c>
       <c r="P41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="16">
@@ -4316,10 +4393,10 @@
       <c r="E42" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="106">
+      <c r="F42" s="104">
         <v>47.545000000000002</v>
       </c>
-      <c r="G42" s="106">
+      <c r="G42" s="104">
         <v>13.608000000000001</v>
       </c>
       <c r="H42" s="12">
@@ -4345,7 +4422,7 @@
         <v>23</v>
       </c>
       <c r="P42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="16">
@@ -4364,10 +4441,10 @@
       <c r="E43" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="106">
+      <c r="F43" s="104">
         <v>47.732999999999997</v>
       </c>
-      <c r="G43" s="106">
+      <c r="G43" s="104">
         <v>15.647</v>
       </c>
       <c r="H43" s="12">
@@ -4393,7 +4470,7 @@
         <v>23</v>
       </c>
       <c r="P43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="16">
@@ -4412,10 +4489,10 @@
       <c r="E44" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F44" s="106">
+      <c r="F44" s="104">
         <v>47.582000000000001</v>
       </c>
-      <c r="G44" s="106">
+      <c r="G44" s="104">
         <v>14.827999999999999</v>
       </c>
       <c r="H44" s="12">
@@ -4441,7 +4518,7 @@
         <v>23</v>
       </c>
       <c r="P44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="16">
@@ -4458,10 +4535,10 @@
         <v>68</v>
       </c>
       <c r="E45" s="10"/>
-      <c r="F45" s="106">
+      <c r="F45" s="104">
         <v>47.326000000000001</v>
       </c>
-      <c r="G45" s="106">
+      <c r="G45" s="104">
         <v>9.9779999999999998</v>
       </c>
       <c r="H45" s="12">
@@ -4487,7 +4564,7 @@
         <v>23</v>
       </c>
       <c r="P45" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="16">
@@ -4506,10 +4583,10 @@
       <c r="E46" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F46" s="106">
+      <c r="F46" s="104">
         <v>44.76</v>
       </c>
-      <c r="G46" s="106">
+      <c r="G46" s="104">
         <v>5.8879999999999999</v>
       </c>
       <c r="H46" s="12">
@@ -4534,8 +4611,8 @@
         <v>72</v>
       </c>
       <c r="O46" s="17"/>
-      <c r="P46" s="104" t="s">
-        <v>341</v>
+      <c r="P46" s="102" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="16">
@@ -4554,10 +4631,10 @@
       <c r="E47" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F47" s="106">
+      <c r="F47" s="104">
         <v>46.223999999999997</v>
       </c>
-      <c r="G47" s="106">
+      <c r="G47" s="104">
         <v>14.617000000000001</v>
       </c>
       <c r="H47" s="12">
@@ -4579,8 +4656,8 @@
       <c r="N47" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="P47" s="104" t="s">
-        <v>342</v>
+      <c r="P47" s="102" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="16">
@@ -4597,10 +4674,10 @@
         <v>77</v>
       </c>
       <c r="E48" s="10"/>
-      <c r="F48" s="106">
+      <c r="F48" s="104">
         <v>46.292999999999999</v>
       </c>
-      <c r="G48" s="106">
+      <c r="G48" s="104">
         <v>13.797000000000001</v>
       </c>
       <c r="H48" s="12">
@@ -4623,8 +4700,8 @@
         <v>76</v>
       </c>
       <c r="O48" s="24"/>
-      <c r="P48" s="104" t="s">
-        <v>343</v>
+      <c r="P48" s="102" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="16">
@@ -4641,10 +4718,10 @@
         <v>79</v>
       </c>
       <c r="E49" s="10"/>
-      <c r="F49" s="106">
+      <c r="F49" s="104">
         <v>46.411999999999999</v>
       </c>
-      <c r="G49" s="106">
+      <c r="G49" s="104">
         <v>13.724</v>
       </c>
       <c r="H49" s="12">
@@ -4667,8 +4744,8 @@
         <v>76</v>
       </c>
       <c r="O49" s="24"/>
-      <c r="P49" s="104" t="s">
-        <v>344</v>
+      <c r="P49" s="102" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="16">
@@ -4685,10 +4762,10 @@
         <v>80</v>
       </c>
       <c r="E50" s="10"/>
-      <c r="F50" s="106">
+      <c r="F50" s="104">
         <v>46.259</v>
       </c>
-      <c r="G50" s="106">
+      <c r="G50" s="104">
         <v>13.725</v>
       </c>
       <c r="H50" s="12">
@@ -4711,8 +4788,8 @@
         <v>76</v>
       </c>
       <c r="O50" s="24"/>
-      <c r="P50" s="104" t="s">
-        <v>345</v>
+      <c r="P50" s="102" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="16">
@@ -4729,10 +4806,10 @@
         <v>82</v>
       </c>
       <c r="E51" s="10"/>
-      <c r="F51" s="106">
+      <c r="F51" s="104">
         <v>47.539000000000001</v>
       </c>
-      <c r="G51" s="106">
+      <c r="G51" s="104">
         <v>10.772</v>
       </c>
       <c r="H51" s="12">
@@ -4755,8 +4832,8 @@
         <v>84</v>
       </c>
       <c r="O51" s="24"/>
-      <c r="P51" s="104" t="s">
-        <v>346</v>
+      <c r="P51" s="102" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="16">
@@ -4775,10 +4852,10 @@
       <c r="E52" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F52" s="107">
+      <c r="F52" s="105">
         <v>42.89</v>
       </c>
-      <c r="G52" s="107">
+      <c r="G52" s="105">
         <v>13.723000000000001</v>
       </c>
       <c r="H52" s="27">
@@ -4802,7 +4879,7 @@
         <v>90</v>
       </c>
       <c r="P52" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="16">
@@ -4821,10 +4898,10 @@
       <c r="E53" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F53" s="107">
+      <c r="F53" s="105">
         <v>42.942</v>
       </c>
-      <c r="G53" s="107">
+      <c r="G53" s="105">
         <v>13.202</v>
       </c>
       <c r="H53" s="27">
@@ -4850,7 +4927,7 @@
         <v>94</v>
       </c>
       <c r="P53" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="16">
@@ -4869,10 +4946,10 @@
       <c r="E54" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="107">
+      <c r="F54" s="105">
         <v>42.582000000000001</v>
       </c>
-      <c r="G54" s="107">
+      <c r="G54" s="105">
         <v>12.813000000000001</v>
       </c>
       <c r="H54" s="32">
@@ -4894,7 +4971,7 @@
         <v>96</v>
       </c>
       <c r="P54" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="16">
@@ -4913,10 +4990,10 @@
       <c r="E55" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F55" s="107">
+      <c r="F55" s="105">
         <v>42.959000000000003</v>
       </c>
-      <c r="G55" s="107">
+      <c r="G55" s="105">
         <v>12.861000000000001</v>
       </c>
       <c r="H55" s="32">
@@ -4938,7 +5015,7 @@
         <v>96</v>
       </c>
       <c r="P55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="16">
@@ -4957,10 +5034,10 @@
       <c r="E56" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F56" s="107">
+      <c r="F56" s="105">
         <v>43.353999999999999</v>
       </c>
-      <c r="G56" s="107">
+      <c r="G56" s="105">
         <v>12.73</v>
       </c>
       <c r="H56" s="32">
@@ -4984,7 +5061,7 @@
       </c>
       <c r="O56" s="30"/>
       <c r="P56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="16">
@@ -5003,10 +5080,10 @@
       <c r="E57" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F57" s="107">
+      <c r="F57" s="105">
         <v>43.103000000000002</v>
       </c>
-      <c r="G57" s="107">
+      <c r="G57" s="105">
         <v>12.826000000000001</v>
       </c>
       <c r="H57" s="32">
@@ -5030,7 +5107,7 @@
       </c>
       <c r="O57" s="30"/>
       <c r="P57" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="16">
@@ -5049,10 +5126,10 @@
       <c r="E58" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F58" s="107">
+      <c r="F58" s="105">
         <v>43.19</v>
       </c>
-      <c r="G58" s="107">
+      <c r="G58" s="105">
         <v>12.804</v>
       </c>
       <c r="H58" s="32">
@@ -5076,7 +5153,7 @@
       </c>
       <c r="O58" s="30"/>
       <c r="P58" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="16">
@@ -5095,10 +5172,10 @@
       <c r="E59" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F59" s="107">
+      <c r="F59" s="105">
         <v>43.109000000000002</v>
       </c>
-      <c r="G59" s="107">
+      <c r="G59" s="105">
         <v>12.856</v>
       </c>
       <c r="H59" s="32">
@@ -5122,7 +5199,7 @@
       </c>
       <c r="O59" s="30"/>
       <c r="P59" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="16">
@@ -5141,10 +5218,10 @@
       <c r="E60" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="F60" s="108">
+      <c r="F60" s="106">
         <v>35.417000000000002</v>
       </c>
-      <c r="G60" s="108">
+      <c r="G60" s="106">
         <v>7.9640000000000004</v>
       </c>
       <c r="H60" s="36">
@@ -5170,7 +5247,7 @@
       </c>
       <c r="O60" s="17"/>
       <c r="P60" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="17">
@@ -5187,10 +5264,10 @@
         <v>111</v>
       </c>
       <c r="E61" s="41"/>
-      <c r="F61" s="109">
+      <c r="F61" s="107">
         <v>34.15</v>
       </c>
-      <c r="G61" s="109">
+      <c r="G61" s="107">
         <v>-4.04</v>
       </c>
       <c r="H61" s="42">
@@ -5214,191 +5291,191 @@
       </c>
       <c r="O61" s="9"/>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="16">
-      <c r="A62" s="70" t="s">
+      <c r="A62" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="B62" s="70" t="s">
-        <v>188</v>
-      </c>
-      <c r="C62" s="70">
+      <c r="C62" s="68">
         <v>1</v>
       </c>
-      <c r="D62" s="70" t="s">
+      <c r="D62" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="E62" s="68"/>
+      <c r="F62" s="108">
+        <v>41.854999999999997</v>
+      </c>
+      <c r="G62" s="108">
+        <v>23.427</v>
+      </c>
+      <c r="H62" s="75">
+        <v>942</v>
+      </c>
+      <c r="I62" s="70" t="s">
         <v>192</v>
       </c>
-      <c r="E62" s="70"/>
-      <c r="F62" s="110">
-        <v>41.854999999999997</v>
-      </c>
-      <c r="G62" s="110">
-        <v>23.427</v>
-      </c>
-      <c r="H62" s="77">
-        <v>942</v>
-      </c>
-      <c r="I62" s="72" t="s">
+      <c r="J62" s="71">
+        <v>1963</v>
+      </c>
+      <c r="K62" s="70">
+        <v>2018</v>
+      </c>
+      <c r="L62" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62" s="74" t="s">
         <v>193</v>
       </c>
-      <c r="J62" s="73">
-        <v>1963</v>
-      </c>
-      <c r="K62" s="72">
-        <v>2018</v>
-      </c>
-      <c r="L62" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M62" s="76" t="s">
-        <v>194</v>
-      </c>
       <c r="N62" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O62" s="17"/>
       <c r="P62" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="16">
-      <c r="A63" s="70" t="s">
+      <c r="A63" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="B63" s="70" t="s">
-        <v>188</v>
-      </c>
-      <c r="C63" s="70">
+      <c r="C63" s="68">
         <v>2</v>
       </c>
-      <c r="D63" s="70" t="s">
+      <c r="D63" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" s="68"/>
+      <c r="F63" s="108">
+        <v>41.853999999999999</v>
+      </c>
+      <c r="G63" s="108">
+        <v>23.436</v>
+      </c>
+      <c r="H63" s="75">
+        <v>912</v>
+      </c>
+      <c r="I63" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="E63" s="70"/>
-      <c r="F63" s="110">
-        <v>41.853999999999999</v>
-      </c>
-      <c r="G63" s="110">
-        <v>23.436</v>
-      </c>
-      <c r="H63" s="77">
-        <v>912</v>
-      </c>
-      <c r="I63" s="72" t="s">
-        <v>196</v>
-      </c>
-      <c r="J63" s="73">
+      <c r="J63" s="71">
         <v>1963</v>
       </c>
-      <c r="K63" s="72">
+      <c r="K63" s="70">
         <v>2018</v>
       </c>
-      <c r="L63" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M63" s="76" t="s">
-        <v>194</v>
+      <c r="L63" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="74" t="s">
+        <v>193</v>
       </c>
       <c r="N63" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O63" s="17"/>
       <c r="P63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="16">
-      <c r="A64" s="70" t="s">
+      <c r="A64" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="B64" s="70" t="s">
+      <c r="C64" s="68">
+        <v>3</v>
+      </c>
+      <c r="D64" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="C64" s="70">
-        <v>3</v>
-      </c>
-      <c r="D64" s="70" t="s">
+      <c r="E64" s="68"/>
+      <c r="F64" s="108">
+        <v>41.706000000000003</v>
+      </c>
+      <c r="G64" s="108">
+        <v>24.466000000000001</v>
+      </c>
+      <c r="H64" s="69">
+        <v>800</v>
+      </c>
+      <c r="I64" s="70">
+        <v>170</v>
+      </c>
+      <c r="J64" s="71">
+        <v>2000</v>
+      </c>
+      <c r="K64" s="70">
+        <v>2020</v>
+      </c>
+      <c r="L64" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64" s="74" t="s">
         <v>189</v>
       </c>
-      <c r="E64" s="70"/>
-      <c r="F64" s="110">
-        <v>41.706000000000003</v>
-      </c>
-      <c r="G64" s="110">
-        <v>24.466000000000001</v>
-      </c>
-      <c r="H64" s="71">
-        <v>800</v>
-      </c>
-      <c r="I64" s="72">
-        <v>170</v>
-      </c>
-      <c r="J64" s="73">
+      <c r="N64" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="O64" s="17"/>
+      <c r="P64" s="102" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="16">
+      <c r="A65" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" s="68">
+        <v>4</v>
+      </c>
+      <c r="D65" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="E65" s="68"/>
+      <c r="F65" s="108">
+        <v>41.616</v>
+      </c>
+      <c r="G65" s="108">
+        <v>24.492999999999999</v>
+      </c>
+      <c r="H65" s="69">
+        <v>1357</v>
+      </c>
+      <c r="I65" s="70">
+        <v>45</v>
+      </c>
+      <c r="J65" s="71">
         <v>2000</v>
       </c>
-      <c r="K64" s="72">
-        <v>2020</v>
-      </c>
-      <c r="L64" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M64" s="76" t="s">
-        <v>190</v>
-      </c>
-      <c r="N64" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="O64" s="17"/>
-      <c r="P64" s="104" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="16">
-      <c r="A65" s="70" t="s">
-        <v>187</v>
-      </c>
-      <c r="B65" s="70" t="s">
-        <v>188</v>
-      </c>
-      <c r="C65" s="70">
-        <v>4</v>
-      </c>
-      <c r="D65" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="E65" s="70"/>
-      <c r="F65" s="110">
-        <v>41.616</v>
-      </c>
-      <c r="G65" s="110">
-        <v>24.492999999999999</v>
-      </c>
-      <c r="H65" s="71">
-        <v>1357</v>
-      </c>
-      <c r="I65" s="72">
-        <v>45</v>
-      </c>
-      <c r="J65" s="73">
-        <v>2000</v>
-      </c>
-      <c r="K65" s="72">
+      <c r="K65" s="70">
         <v>2009</v>
       </c>
-      <c r="L65" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M65" s="76" t="s">
-        <v>190</v>
+      <c r="L65" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M65" s="74" t="s">
+        <v>189</v>
       </c>
       <c r="N65" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O65" s="17"/>
       <c r="P65" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="16">
@@ -5444,7 +5521,7 @@
       </c>
       <c r="O66" s="17"/>
       <c r="P66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="16">
@@ -5490,7 +5567,7 @@
       </c>
       <c r="O67" s="17"/>
       <c r="P67" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="16">
@@ -5540,7 +5617,7 @@
         <v>121</v>
       </c>
       <c r="P68" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="16">
@@ -5590,45 +5667,45 @@
         <v>121</v>
       </c>
       <c r="P69" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="16">
-      <c r="A70" s="53" t="s">
+      <c r="A70" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B70" s="53" t="s">
+      <c r="B70" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="C70" s="53">
+      <c r="C70" s="119">
         <v>1</v>
       </c>
-      <c r="D70" s="53" t="s">
+      <c r="D70" s="119" t="s">
         <v>126</v>
       </c>
-      <c r="E70" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" s="111">
+      <c r="E70" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" s="120">
         <v>48.86</v>
       </c>
-      <c r="G70" s="111">
+      <c r="G70" s="120">
         <v>19.527000000000001</v>
       </c>
-      <c r="H70" s="54">
+      <c r="H70" s="121">
         <v>600</v>
       </c>
-      <c r="I70" s="55"/>
-      <c r="J70" s="56">
+      <c r="I70" s="122"/>
+      <c r="J70" s="123">
         <v>2016</v>
       </c>
-      <c r="K70" s="55">
+      <c r="K70" s="122">
         <v>2024</v>
       </c>
-      <c r="L70" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="M70" s="58" t="s">
+      <c r="L70" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70" s="125" t="s">
         <v>127</v>
       </c>
       <c r="N70" s="20" t="s">
@@ -5638,45 +5715,45 @@
         <v>129</v>
       </c>
       <c r="P70" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="16">
-      <c r="A71" s="53" t="s">
+      <c r="A71" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B71" s="53" t="s">
+      <c r="B71" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="C71" s="53">
+      <c r="C71" s="119">
         <v>2</v>
       </c>
-      <c r="D71" s="53" t="s">
+      <c r="D71" s="119" t="s">
         <v>130</v>
       </c>
-      <c r="E71" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" s="111">
+      <c r="E71" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="120">
         <v>48.929000000000002</v>
       </c>
-      <c r="G71" s="111">
+      <c r="G71" s="120">
         <v>20.123999999999999</v>
       </c>
-      <c r="H71" s="54">
+      <c r="H71" s="121">
         <v>990</v>
       </c>
-      <c r="I71" s="55"/>
-      <c r="J71" s="57">
+      <c r="I71" s="122"/>
+      <c r="J71" s="124">
         <v>2016</v>
       </c>
-      <c r="K71" s="55">
+      <c r="K71" s="122">
         <v>2024</v>
       </c>
-      <c r="L71" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="M71" s="58" t="s">
+      <c r="L71" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="M71" s="125" t="s">
         <v>127</v>
       </c>
       <c r="N71" s="20" t="s">
@@ -5686,45 +5763,45 @@
         <v>129</v>
       </c>
       <c r="P71" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="16">
-      <c r="A72" s="53" t="s">
+      <c r="A72" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B72" s="53" t="s">
+      <c r="B72" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="C72" s="53">
+      <c r="C72" s="119">
         <v>3</v>
       </c>
-      <c r="D72" s="53" t="s">
+      <c r="D72" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="E72" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" s="111">
+      <c r="E72" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="120">
         <v>49.252000000000002</v>
       </c>
-      <c r="G72" s="111">
+      <c r="G72" s="120">
         <v>20.103000000000002</v>
       </c>
-      <c r="H72" s="54">
+      <c r="H72" s="121">
         <v>995</v>
       </c>
-      <c r="I72" s="55"/>
-      <c r="J72" s="57">
+      <c r="I72" s="122"/>
+      <c r="J72" s="124">
         <v>2016</v>
       </c>
-      <c r="K72" s="55">
+      <c r="K72" s="122">
         <v>2024</v>
       </c>
-      <c r="L72" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="M72" s="58" t="s">
+      <c r="L72" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="M72" s="125" t="s">
         <v>127</v>
       </c>
       <c r="N72" s="20" t="s">
@@ -5734,45 +5811,45 @@
         <v>129</v>
       </c>
       <c r="P72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="16">
-      <c r="A73" s="53" t="s">
+      <c r="A73" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B73" s="53" t="s">
+      <c r="B73" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="C73" s="53">
+      <c r="C73" s="119">
         <v>4</v>
       </c>
-      <c r="D73" s="53" t="s">
+      <c r="D73" s="119" t="s">
         <v>132</v>
       </c>
-      <c r="E73" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" s="111">
+      <c r="E73" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" s="120">
         <v>48.756999999999998</v>
       </c>
-      <c r="G73" s="111">
+      <c r="G73" s="120">
         <v>20.07</v>
       </c>
-      <c r="H73" s="54">
+      <c r="H73" s="121">
         <v>430</v>
       </c>
-      <c r="I73" s="55"/>
-      <c r="J73" s="57">
+      <c r="I73" s="122"/>
+      <c r="J73" s="124">
         <v>2016</v>
       </c>
-      <c r="K73" s="57">
+      <c r="K73" s="124">
         <v>2024</v>
       </c>
-      <c r="L73" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="M73" s="58" t="s">
+      <c r="L73" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="M73" s="125" t="s">
         <v>127</v>
       </c>
       <c r="N73" s="20" t="s">
@@ -5782,45 +5859,45 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="16">
-      <c r="A74" s="53" t="s">
+      <c r="A74" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B74" s="53" t="s">
+      <c r="B74" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="C74" s="53">
+      <c r="C74" s="119">
         <v>5</v>
       </c>
-      <c r="D74" s="53" t="s">
+      <c r="D74" s="119" t="s">
         <v>133</v>
       </c>
-      <c r="E74" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" s="111">
+      <c r="E74" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="120">
         <v>48.561999999999998</v>
       </c>
-      <c r="G74" s="111">
+      <c r="G74" s="120">
         <v>20.465</v>
       </c>
-      <c r="H74" s="54">
+      <c r="H74" s="121">
         <v>250</v>
       </c>
-      <c r="I74" s="55"/>
-      <c r="J74" s="57">
+      <c r="I74" s="122"/>
+      <c r="J74" s="124">
         <v>2016</v>
       </c>
-      <c r="K74" s="57">
+      <c r="K74" s="124">
         <v>2024</v>
       </c>
-      <c r="L74" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M74" s="58" t="s">
+      <c r="L74" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M74" s="125" t="s">
         <v>127</v>
       </c>
       <c r="N74" s="20" t="s">
@@ -5830,45 +5907,45 @@
         <v>129</v>
       </c>
       <c r="P74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="16">
-      <c r="A75" s="53" t="s">
+      <c r="A75" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B75" s="53" t="s">
+      <c r="B75" s="119" t="s">
         <v>134</v>
       </c>
-      <c r="C75" s="53">
+      <c r="C75" s="119">
         <v>6</v>
       </c>
-      <c r="D75" s="53" t="s">
+      <c r="D75" s="119" t="s">
         <v>135</v>
       </c>
-      <c r="E75" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" s="111">
+      <c r="E75" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="120">
         <v>43.96</v>
       </c>
-      <c r="G75" s="111">
+      <c r="G75" s="120">
         <v>21.62</v>
       </c>
-      <c r="H75" s="54">
+      <c r="H75" s="121">
         <v>560</v>
       </c>
-      <c r="I75" s="55"/>
-      <c r="J75" s="57">
+      <c r="I75" s="122"/>
+      <c r="J75" s="124">
         <v>1988</v>
       </c>
-      <c r="K75" s="55">
+      <c r="K75" s="122">
         <v>1991</v>
       </c>
-      <c r="L75" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M75" s="31" t="s">
+      <c r="L75" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M75" s="126" t="s">
         <v>117</v>
       </c>
       <c r="N75" s="20" t="s">
@@ -5876,45 +5953,45 @@
       </c>
       <c r="O75" s="30"/>
       <c r="P75" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="16">
-      <c r="A76" s="53" t="s">
+      <c r="A76" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B76" s="53" t="s">
+      <c r="B76" s="119" t="s">
         <v>134</v>
       </c>
-      <c r="C76" s="53">
+      <c r="C76" s="119">
         <v>7</v>
       </c>
-      <c r="D76" s="53" t="s">
+      <c r="D76" s="119" t="s">
         <v>136</v>
       </c>
-      <c r="E76" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" s="111">
+      <c r="E76" s="119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" s="120">
         <v>44.192</v>
       </c>
-      <c r="G76" s="111">
+      <c r="G76" s="120">
         <v>21.783999999999999</v>
       </c>
-      <c r="H76" s="54">
+      <c r="H76" s="121">
         <v>320</v>
       </c>
-      <c r="I76" s="55"/>
-      <c r="J76" s="57">
+      <c r="I76" s="122"/>
+      <c r="J76" s="124">
         <v>1991</v>
       </c>
-      <c r="K76" s="55">
+      <c r="K76" s="122">
         <v>1999</v>
       </c>
-      <c r="L76" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M76" s="34" t="s">
+      <c r="L76" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M76" s="127" t="s">
         <v>137</v>
       </c>
       <c r="N76" s="20" t="s">
@@ -5922,2236 +5999,2402 @@
       </c>
       <c r="O76" s="30"/>
       <c r="P76" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="16">
-      <c r="A77" s="53" t="s">
+      <c r="A77" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="119" t="s">
         <v>139</v>
       </c>
-      <c r="B77" s="53" t="s">
+      <c r="C77" s="119">
+        <v>8</v>
+      </c>
+      <c r="D77" s="128" t="s">
         <v>140</v>
       </c>
-      <c r="C77" s="53">
-        <v>8</v>
-      </c>
-      <c r="D77" s="119" t="s">
+      <c r="E77" s="128" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="129">
+        <v>49.332999999999998</v>
+      </c>
+      <c r="G77" s="129">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="H77" s="130">
+        <v>300</v>
+      </c>
+      <c r="I77" s="122">
+        <v>153</v>
+      </c>
+      <c r="J77" s="124">
+        <v>1980</v>
+      </c>
+      <c r="K77" s="122">
+        <v>2023</v>
+      </c>
+      <c r="L77" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M77" s="127" t="s">
         <v>141</v>
-      </c>
-      <c r="E77" s="119" t="s">
-        <v>19</v>
-      </c>
-      <c r="F77" s="120">
-        <v>49.332999999999998</v>
-      </c>
-      <c r="G77" s="120">
-        <v>16.649999999999999</v>
-      </c>
-      <c r="H77" s="59">
-        <v>300</v>
-      </c>
-      <c r="I77" s="55">
-        <v>153</v>
-      </c>
-      <c r="J77" s="57">
-        <v>1980</v>
-      </c>
-      <c r="K77" s="55">
-        <v>2023</v>
-      </c>
-      <c r="L77" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M77" s="34" t="s">
-        <v>142</v>
       </c>
       <c r="N77" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O77" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="P77" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="16">
+      <c r="A78" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B78" s="119" t="s">
+        <v>362</v>
+      </c>
+      <c r="C78" s="131">
+        <v>9</v>
+      </c>
+      <c r="D78" s="132" t="s">
+        <v>363</v>
+      </c>
+      <c r="E78" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" s="134">
+        <v>48.557000000000002</v>
+      </c>
+      <c r="G78" s="134">
+        <v>20.763999999999999</v>
+      </c>
+      <c r="H78" s="121">
+        <v>173</v>
+      </c>
+      <c r="I78" s="122"/>
+      <c r="J78" s="124">
+        <v>1969</v>
+      </c>
+      <c r="K78" s="122">
+        <v>2024</v>
+      </c>
+      <c r="L78" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78" s="135" t="s">
+        <v>372</v>
+      </c>
+      <c r="N78" s="20"/>
+      <c r="O78" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="P78" s="118" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="16">
+      <c r="A79" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B79" s="119" t="s">
+        <v>362</v>
+      </c>
+      <c r="C79" s="131">
+        <v>10</v>
+      </c>
+      <c r="D79" s="132" t="s">
+        <v>364</v>
+      </c>
+      <c r="E79" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="134">
+        <v>48.487000000000002</v>
+      </c>
+      <c r="G79" s="134">
+        <v>20.550999999999998</v>
+      </c>
+      <c r="H79" s="121">
+        <v>236</v>
+      </c>
+      <c r="I79" s="122"/>
+      <c r="J79" s="124">
+        <v>1964</v>
+      </c>
+      <c r="K79" s="122">
+        <v>2024</v>
+      </c>
+      <c r="L79" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M79" s="135" t="s">
+        <v>372</v>
+      </c>
+      <c r="N79" s="20"/>
+      <c r="O79" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="P79" s="118" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="16">
+      <c r="A80" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" s="119" t="s">
+        <v>362</v>
+      </c>
+      <c r="C80" s="131">
+        <v>11</v>
+      </c>
+      <c r="D80" s="132" t="s">
+        <v>365</v>
+      </c>
+      <c r="E80" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="136">
+        <v>48.521999999999998</v>
+      </c>
+      <c r="G80" s="136">
+        <v>20.545999999999999</v>
+      </c>
+      <c r="H80" s="121">
+        <v>462</v>
+      </c>
+      <c r="I80" s="122"/>
+      <c r="J80" s="124">
+        <v>1965</v>
+      </c>
+      <c r="K80" s="122">
+        <v>2023</v>
+      </c>
+      <c r="L80" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M80" s="135" t="s">
+        <v>372</v>
+      </c>
+      <c r="N80" s="20"/>
+      <c r="O80" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="P80" s="118" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="16">
+      <c r="A81" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" s="119" t="s">
+        <v>362</v>
+      </c>
+      <c r="C81" s="131">
+        <v>12</v>
+      </c>
+      <c r="D81" s="132" t="s">
+        <v>366</v>
+      </c>
+      <c r="E81" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="136">
+        <v>48.494999999999997</v>
+      </c>
+      <c r="G81" s="136">
+        <v>20.538</v>
+      </c>
+      <c r="H81" s="121">
+        <v>262</v>
+      </c>
+      <c r="I81" s="122"/>
+      <c r="J81" s="124">
+        <v>1960</v>
+      </c>
+      <c r="K81" s="122">
+        <v>2024</v>
+      </c>
+      <c r="L81" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" s="135" t="s">
+        <v>372</v>
+      </c>
+      <c r="N81" s="20"/>
+      <c r="O81" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="P81" s="118" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="16">
+      <c r="A82" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B82" s="119" t="s">
+        <v>367</v>
+      </c>
+      <c r="C82" s="131">
+        <v>13</v>
+      </c>
+      <c r="D82" s="132" t="s">
+        <v>368</v>
+      </c>
+      <c r="E82" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="137">
+        <v>45</v>
+      </c>
+      <c r="G82" s="137">
+        <v>22.8</v>
+      </c>
+      <c r="H82" s="121">
+        <v>284</v>
+      </c>
+      <c r="I82" s="122"/>
+      <c r="J82" s="124">
+        <v>1977</v>
+      </c>
+      <c r="K82" s="122">
+        <v>1986</v>
+      </c>
+      <c r="L82" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82" s="138" t="s">
+        <v>371</v>
+      </c>
+      <c r="N82" s="20"/>
+      <c r="O82" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="P82" s="118" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="16">
+      <c r="A83" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B83" s="119" t="s">
+        <v>367</v>
+      </c>
+      <c r="C83" s="131">
+        <v>14</v>
+      </c>
+      <c r="D83" s="132" t="s">
+        <v>369</v>
+      </c>
+      <c r="E83" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="136">
+        <v>45.01</v>
+      </c>
+      <c r="G83" s="136">
+        <v>22.82</v>
+      </c>
+      <c r="H83" s="121">
+        <v>290</v>
+      </c>
+      <c r="I83" s="122"/>
+      <c r="J83" s="124">
+        <v>1979</v>
+      </c>
+      <c r="K83" s="122">
+        <v>1987</v>
+      </c>
+      <c r="L83" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83" s="138" t="s">
+        <v>371</v>
+      </c>
+      <c r="N83" s="20"/>
+      <c r="O83" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="P83" s="118" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="16">
+      <c r="A84" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="119" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="131">
+        <v>15</v>
+      </c>
+      <c r="D84" s="132" t="s">
+        <v>370</v>
+      </c>
+      <c r="E84" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="136">
+        <v>45.01</v>
+      </c>
+      <c r="G84" s="136">
+        <v>22.81</v>
+      </c>
+      <c r="H84" s="121">
+        <v>290</v>
+      </c>
+      <c r="I84" s="122"/>
+      <c r="J84" s="124">
+        <v>1977</v>
+      </c>
+      <c r="K84" s="122">
+        <v>1987</v>
+      </c>
+      <c r="L84" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84" s="138" t="s">
+        <v>371</v>
+      </c>
+      <c r="N84" s="20"/>
+      <c r="O84" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="P84" s="118" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="16">
+      <c r="A85" s="58" t="s">
         <v>143</v>
       </c>
-      <c r="P77" t="s">
+      <c r="B85" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C85" s="58">
+        <v>1</v>
+      </c>
+      <c r="D85" s="116" t="s">
+        <v>145</v>
+      </c>
+      <c r="E85" s="116" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="117">
+        <v>43.826999999999998</v>
+      </c>
+      <c r="G85" s="117">
+        <v>18.271000000000001</v>
+      </c>
+      <c r="H85" s="59">
+        <v>497</v>
+      </c>
+      <c r="I85" s="60"/>
+      <c r="J85" s="61">
+        <v>2007</v>
+      </c>
+      <c r="K85" s="60">
+        <v>2019</v>
+      </c>
+      <c r="L85" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M85" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="N85" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O85" s="30"/>
+      <c r="P85" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="16">
-      <c r="A78" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="B78" s="53" t="s">
-        <v>363</v>
-      </c>
-      <c r="C78" s="118">
+    <row r="86" spans="1:16" ht="16">
+      <c r="A86" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B86" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C86" s="58">
+        <v>2</v>
+      </c>
+      <c r="D86" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="E86" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="110">
+        <v>43.774000000000001</v>
+      </c>
+      <c r="G86" s="110">
+        <v>17.023</v>
+      </c>
+      <c r="H86" s="59">
+        <v>738</v>
+      </c>
+      <c r="I86" s="60"/>
+      <c r="J86" s="61">
+        <v>2004</v>
+      </c>
+      <c r="K86" s="60">
+        <v>2019</v>
+      </c>
+      <c r="L86" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M86" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="N86" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O86" s="30"/>
+      <c r="P86" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="16">
+      <c r="A87" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B87" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C87" s="58">
+        <v>3</v>
+      </c>
+      <c r="D87" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="E87" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="110">
+        <v>43.808</v>
+      </c>
+      <c r="G87" s="110">
+        <v>17.007000000000001</v>
+      </c>
+      <c r="H87" s="59">
+        <v>721</v>
+      </c>
+      <c r="I87" s="60"/>
+      <c r="J87" s="61">
+        <v>2007</v>
+      </c>
+      <c r="K87" s="60">
+        <v>2019</v>
+      </c>
+      <c r="L87" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M87" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="N87" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O87" s="30"/>
+      <c r="P87" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="16">
+      <c r="A88" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B88" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C88" s="58">
+        <v>4</v>
+      </c>
+      <c r="D88" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="E88" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="110">
+        <v>45.828000000000003</v>
+      </c>
+      <c r="G88" s="110">
+        <v>14.260999999999999</v>
+      </c>
+      <c r="H88" s="59">
+        <v>450</v>
+      </c>
+      <c r="I88" s="60"/>
+      <c r="J88" s="61">
+        <v>1936</v>
+      </c>
+      <c r="K88" s="60">
+        <v>2023</v>
+      </c>
+      <c r="L88" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M88" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N88" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="O88" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P88" s="102" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="16">
+      <c r="A89" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C89" s="58">
+        <v>5</v>
+      </c>
+      <c r="D89" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="E89" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" s="110">
+        <v>45.899000000000001</v>
+      </c>
+      <c r="G89" s="110">
+        <v>13.909000000000001</v>
+      </c>
+      <c r="H89" s="59">
+        <v>183</v>
+      </c>
+      <c r="I89" s="60"/>
+      <c r="J89" s="61">
+        <v>1970</v>
+      </c>
+      <c r="K89" s="60">
+        <v>2023</v>
+      </c>
+      <c r="L89" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M89" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N89" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="O89" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P89" s="102" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="16">
+      <c r="A90" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B90" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C90" s="58">
+        <v>6</v>
+      </c>
+      <c r="D90" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="E90" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" s="110">
+        <v>45.43</v>
+      </c>
+      <c r="G90" s="110">
+        <v>13.89</v>
+      </c>
+      <c r="H90" s="59">
+        <v>400</v>
+      </c>
+      <c r="I90" s="60"/>
+      <c r="J90" s="61">
+        <v>2015</v>
+      </c>
+      <c r="K90" s="60">
+        <v>2023</v>
+      </c>
+      <c r="L90" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M90" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N90" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="O90" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P90" s="102" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="16">
+      <c r="A91" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B91" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C91" s="58">
+        <v>7</v>
+      </c>
+      <c r="D91" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="E91" s="58"/>
+      <c r="F91" s="110">
+        <v>44.042000000000002</v>
+      </c>
+      <c r="G91" s="110">
+        <v>16.234999999999999</v>
+      </c>
+      <c r="H91" s="59">
+        <v>250</v>
+      </c>
+      <c r="I91" s="60"/>
+      <c r="J91" s="61">
+        <v>1998</v>
+      </c>
+      <c r="K91" s="60">
+        <v>2015</v>
+      </c>
+      <c r="L91" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="N91" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="O91" s="24"/>
+      <c r="P91" s="102" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="16">
+      <c r="A92" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B92" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C92" s="58">
+        <v>8</v>
+      </c>
+      <c r="D92" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="E92" s="58"/>
+      <c r="F92" s="110">
+        <v>44.203000000000003</v>
+      </c>
+      <c r="G92" s="110">
+        <v>16.082999999999998</v>
+      </c>
+      <c r="H92" s="59">
+        <v>325</v>
+      </c>
+      <c r="I92" s="60"/>
+      <c r="J92" s="61">
+        <v>2001</v>
+      </c>
+      <c r="K92" s="60">
+        <v>2015</v>
+      </c>
+      <c r="L92" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M92" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="N92" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="O92" s="24"/>
+      <c r="P92" s="102" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="16">
+      <c r="A93" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B93" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C93" s="58">
         <v>9</v>
       </c>
-      <c r="D78" s="126" t="s">
-        <v>364</v>
-      </c>
-      <c r="E78" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="F78" s="124">
-        <v>48.557000000000002</v>
-      </c>
-      <c r="G78" s="124">
-        <v>20.763999999999999</v>
-      </c>
-      <c r="H78" s="54">
-        <v>173</v>
-      </c>
-      <c r="I78" s="55"/>
-      <c r="J78" s="57">
-        <v>1969</v>
-      </c>
-      <c r="K78" s="55">
+      <c r="D93" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="E93" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" s="110">
+        <v>43.509</v>
+      </c>
+      <c r="G93" s="110">
+        <v>17.096</v>
+      </c>
+      <c r="H93" s="59">
+        <v>410</v>
+      </c>
+      <c r="I93" s="60"/>
+      <c r="J93" s="61">
+        <v>2001</v>
+      </c>
+      <c r="K93" s="60">
+        <v>2023</v>
+      </c>
+      <c r="L93" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M93" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="N93" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O93" s="24"/>
+      <c r="P93" s="102" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="16">
+      <c r="A94" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B94" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C94" s="58">
+        <v>10</v>
+      </c>
+      <c r="D94" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="E94" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="111">
+        <v>45.554000000000002</v>
+      </c>
+      <c r="G94" s="110">
+        <v>17.337</v>
+      </c>
+      <c r="H94" s="59">
+        <v>234</v>
+      </c>
+      <c r="I94" s="60"/>
+      <c r="J94" s="61">
+        <v>2001</v>
+      </c>
+      <c r="K94" s="60">
+        <v>2023</v>
+      </c>
+      <c r="L94" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M94" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="N94" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O94" s="24"/>
+      <c r="P94" s="102" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="16">
+      <c r="A95" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="B95" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C95" s="58">
+        <v>11</v>
+      </c>
+      <c r="D95" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="E95" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="110">
+        <v>44.838999999999999</v>
+      </c>
+      <c r="G95" s="110">
+        <v>15.603</v>
+      </c>
+      <c r="H95" s="59">
+        <v>687</v>
+      </c>
+      <c r="I95" s="60"/>
+      <c r="J95" s="61">
+        <v>1996</v>
+      </c>
+      <c r="K95" s="60">
+        <v>2023</v>
+      </c>
+      <c r="L95" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M95" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="N95" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O95" s="24"/>
+      <c r="P95" s="102" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="16">
+      <c r="A96" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B96" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C96" s="63">
+        <v>1</v>
+      </c>
+      <c r="D96" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E96" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="112">
+        <v>46.704999999999998</v>
+      </c>
+      <c r="G96" s="112">
+        <v>6.2089999999999996</v>
+      </c>
+      <c r="H96" s="64">
+        <v>945</v>
+      </c>
+      <c r="I96" s="65">
+        <v>55</v>
+      </c>
+      <c r="J96" s="66">
+        <v>2009</v>
+      </c>
+      <c r="K96" s="65">
         <v>2024</v>
       </c>
-      <c r="L78" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M78" s="34"/>
-      <c r="N78" s="20"/>
-      <c r="O78" s="30"/>
-    </row>
-    <row r="79" spans="1:16" ht="16">
-      <c r="A79" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="B79" s="53" t="s">
-        <v>363</v>
-      </c>
-      <c r="C79" s="118">
-        <v>10</v>
-      </c>
-      <c r="D79" s="126" t="s">
-        <v>365</v>
-      </c>
-      <c r="E79" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="F79" s="124">
-        <v>48.487000000000002</v>
-      </c>
-      <c r="G79" s="124">
-        <v>20.550999999999998</v>
-      </c>
-      <c r="H79" s="54">
-        <v>236</v>
-      </c>
-      <c r="I79" s="55"/>
-      <c r="J79" s="57">
-        <v>1964</v>
-      </c>
-      <c r="K79" s="55">
-        <v>2024</v>
-      </c>
-      <c r="L79" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M79" s="34"/>
-      <c r="N79" s="20"/>
-      <c r="O79" s="30"/>
-    </row>
-    <row r="80" spans="1:16" ht="16">
-      <c r="A80" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="B80" s="53" t="s">
-        <v>363</v>
-      </c>
-      <c r="C80" s="118">
-        <v>11</v>
-      </c>
-      <c r="D80" s="126" t="s">
-        <v>366</v>
-      </c>
-      <c r="E80" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" s="125">
-        <v>48.521999999999998</v>
-      </c>
-      <c r="G80" s="125">
-        <v>20.545999999999999</v>
-      </c>
-      <c r="H80" s="54">
-        <v>462</v>
-      </c>
-      <c r="I80" s="55"/>
-      <c r="J80" s="57">
-        <v>1965</v>
-      </c>
-      <c r="K80" s="55">
-        <v>2023</v>
-      </c>
-      <c r="L80" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M80" s="34"/>
-      <c r="N80" s="20"/>
-      <c r="O80" s="30"/>
-    </row>
-    <row r="81" spans="1:16" ht="16">
-      <c r="A81" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="B81" s="53" t="s">
-        <v>363</v>
-      </c>
-      <c r="C81" s="118">
-        <v>12</v>
-      </c>
-      <c r="D81" s="126" t="s">
-        <v>367</v>
-      </c>
-      <c r="E81" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="F81" s="125">
-        <v>48.494999999999997</v>
-      </c>
-      <c r="G81" s="125">
-        <v>20.538</v>
-      </c>
-      <c r="H81" s="54">
-        <v>262</v>
-      </c>
-      <c r="I81" s="55"/>
-      <c r="J81" s="57">
-        <v>1960</v>
-      </c>
-      <c r="K81" s="55">
-        <v>2024</v>
-      </c>
-      <c r="L81" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M81" s="34"/>
-      <c r="N81" s="20"/>
-      <c r="O81" s="30"/>
-    </row>
-    <row r="82" spans="1:16" ht="16">
-      <c r="A82" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B82" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="C82" s="60">
-        <v>1</v>
-      </c>
-      <c r="D82" s="121" t="s">
-        <v>146</v>
-      </c>
-      <c r="E82" s="121" t="s">
-        <v>19</v>
-      </c>
-      <c r="F82" s="122">
-        <v>43.826999999999998</v>
-      </c>
-      <c r="G82" s="122">
-        <v>18.271000000000001</v>
-      </c>
-      <c r="H82" s="61">
-        <v>497</v>
-      </c>
-      <c r="I82" s="62"/>
-      <c r="J82" s="63">
-        <v>2007</v>
-      </c>
-      <c r="K82" s="62">
-        <v>2019</v>
-      </c>
-      <c r="L82" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M82" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="N82" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O82" s="30"/>
-      <c r="P82" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" ht="16">
-      <c r="A83" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B83" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="C83" s="60">
-        <v>2</v>
-      </c>
-      <c r="D83" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="E83" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" s="112">
-        <v>43.774000000000001</v>
-      </c>
-      <c r="G83" s="112">
-        <v>17.023</v>
-      </c>
-      <c r="H83" s="61">
-        <v>738</v>
-      </c>
-      <c r="I83" s="62"/>
-      <c r="J83" s="63">
-        <v>2004</v>
-      </c>
-      <c r="K83" s="62">
-        <v>2019</v>
-      </c>
-      <c r="L83" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M83" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="N83" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O83" s="30"/>
-      <c r="P83" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="16">
-      <c r="A84" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B84" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="C84" s="60">
-        <v>3</v>
-      </c>
-      <c r="D84" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E84" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F84" s="112">
-        <v>43.808</v>
-      </c>
-      <c r="G84" s="112">
-        <v>17.007000000000001</v>
-      </c>
-      <c r="H84" s="61">
-        <v>721</v>
-      </c>
-      <c r="I84" s="62"/>
-      <c r="J84" s="63">
-        <v>2007</v>
-      </c>
-      <c r="K84" s="62">
-        <v>2019</v>
-      </c>
-      <c r="L84" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M84" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="N84" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O84" s="30"/>
-      <c r="P84" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="16">
-      <c r="A85" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B85" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="C85" s="60">
-        <v>4</v>
-      </c>
-      <c r="D85" s="60" t="s">
-        <v>153</v>
-      </c>
-      <c r="E85" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F85" s="112">
-        <v>45.828000000000003</v>
-      </c>
-      <c r="G85" s="112">
-        <v>14.260999999999999</v>
-      </c>
-      <c r="H85" s="61">
-        <v>450</v>
-      </c>
-      <c r="I85" s="62"/>
-      <c r="J85" s="63">
-        <v>1936</v>
-      </c>
-      <c r="K85" s="62">
-        <v>2023</v>
-      </c>
-      <c r="L85" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M85" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="N85" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="O85" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="P85" s="104" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="16">
-      <c r="A86" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B86" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="C86" s="60">
-        <v>5</v>
-      </c>
-      <c r="D86" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="E86" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" s="112">
-        <v>45.899000000000001</v>
-      </c>
-      <c r="G86" s="112">
-        <v>13.909000000000001</v>
-      </c>
-      <c r="H86" s="61">
-        <v>183</v>
-      </c>
-      <c r="I86" s="62"/>
-      <c r="J86" s="63">
-        <v>1970</v>
-      </c>
-      <c r="K86" s="62">
-        <v>2023</v>
-      </c>
-      <c r="L86" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M86" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="N86" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="O86" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="P86" s="104" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="16">
-      <c r="A87" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B87" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="C87" s="60">
-        <v>6</v>
-      </c>
-      <c r="D87" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="E87" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="112">
-        <v>45.43</v>
-      </c>
-      <c r="G87" s="112">
-        <v>13.89</v>
-      </c>
-      <c r="H87" s="61">
-        <v>400</v>
-      </c>
-      <c r="I87" s="62"/>
-      <c r="J87" s="63">
-        <v>2015</v>
-      </c>
-      <c r="K87" s="62">
-        <v>2023</v>
-      </c>
-      <c r="L87" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M87" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="N87" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="O87" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="P87" s="104" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" ht="16">
-      <c r="A88" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B88" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="C88" s="60">
-        <v>7</v>
-      </c>
-      <c r="D88" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="E88" s="60"/>
-      <c r="F88" s="112">
-        <v>44.042000000000002</v>
-      </c>
-      <c r="G88" s="112">
-        <v>16.234999999999999</v>
-      </c>
-      <c r="H88" s="61">
-        <v>250</v>
-      </c>
-      <c r="I88" s="62"/>
-      <c r="J88" s="63">
-        <v>1998</v>
-      </c>
-      <c r="K88" s="62">
-        <v>2015</v>
-      </c>
-      <c r="L88" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M88" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="N88" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="O88" s="24"/>
-      <c r="P88" s="104" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="16">
-      <c r="A89" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B89" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89" s="60">
-        <v>8</v>
-      </c>
-      <c r="D89" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="E89" s="60"/>
-      <c r="F89" s="112">
-        <v>44.203000000000003</v>
-      </c>
-      <c r="G89" s="112">
-        <v>16.082999999999998</v>
-      </c>
-      <c r="H89" s="61">
-        <v>325</v>
-      </c>
-      <c r="I89" s="62"/>
-      <c r="J89" s="63">
-        <v>2001</v>
-      </c>
-      <c r="K89" s="62">
-        <v>2015</v>
-      </c>
-      <c r="L89" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M89" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="N89" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="O89" s="24"/>
-      <c r="P89" s="104" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="16">
-      <c r="A90" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B90" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="C90" s="60">
-        <v>9</v>
-      </c>
-      <c r="D90" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="E90" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" s="112">
-        <v>43.509</v>
-      </c>
-      <c r="G90" s="112">
-        <v>17.096</v>
-      </c>
-      <c r="H90" s="61">
-        <v>410</v>
-      </c>
-      <c r="I90" s="62"/>
-      <c r="J90" s="63">
-        <v>2001</v>
-      </c>
-      <c r="K90" s="62">
-        <v>2023</v>
-      </c>
-      <c r="L90" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M90" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="N90" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O90" s="24"/>
-      <c r="P90" s="104" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="16">
-      <c r="A91" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B91" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="C91" s="60">
-        <v>10</v>
-      </c>
-      <c r="D91" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="E91" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F91" s="113">
-        <v>45.554000000000002</v>
-      </c>
-      <c r="G91" s="112">
-        <v>17.337</v>
-      </c>
-      <c r="H91" s="61">
-        <v>234</v>
-      </c>
-      <c r="I91" s="62"/>
-      <c r="J91" s="63">
-        <v>2001</v>
-      </c>
-      <c r="K91" s="62">
-        <v>2023</v>
-      </c>
-      <c r="L91" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M91" s="58" t="s">
-        <v>165</v>
-      </c>
-      <c r="N91" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O91" s="24"/>
-      <c r="P91" s="104" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="16">
-      <c r="A92" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B92" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="C92" s="60">
-        <v>11</v>
-      </c>
-      <c r="D92" s="60" t="s">
-        <v>166</v>
-      </c>
-      <c r="E92" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F92" s="112">
-        <v>44.838999999999999</v>
-      </c>
-      <c r="G92" s="112">
-        <v>15.603</v>
-      </c>
-      <c r="H92" s="61">
-        <v>687</v>
-      </c>
-      <c r="I92" s="62"/>
-      <c r="J92" s="63">
-        <v>1996</v>
-      </c>
-      <c r="K92" s="62">
-        <v>2023</v>
-      </c>
-      <c r="L92" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M92" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="N92" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O92" s="24"/>
-      <c r="P92" s="104" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="16">
-      <c r="A93" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="B93" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="C93" s="65">
-        <v>1</v>
-      </c>
-      <c r="D93" s="65" t="s">
+      <c r="L96" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="M96" s="67" t="s">
         <v>169</v>
-      </c>
-      <c r="E93" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F93" s="114">
-        <v>46.704999999999998</v>
-      </c>
-      <c r="G93" s="114">
-        <v>6.2089999999999996</v>
-      </c>
-      <c r="H93" s="66">
-        <v>945</v>
-      </c>
-      <c r="I93" s="67">
-        <v>55</v>
-      </c>
-      <c r="J93" s="68">
-        <v>2009</v>
-      </c>
-      <c r="K93" s="67">
-        <v>2024</v>
-      </c>
-      <c r="L93" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="M93" s="69" t="s">
-        <v>170</v>
-      </c>
-      <c r="N93" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O93" s="17"/>
-      <c r="P93" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" ht="16">
-      <c r="A94" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="B94" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94" s="65">
-        <v>2</v>
-      </c>
-      <c r="D94" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="E94" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F94" s="114">
-        <v>47.011000000000003</v>
-      </c>
-      <c r="G94" s="114">
-        <v>6.2990000000000004</v>
-      </c>
-      <c r="H94" s="66">
-        <v>530</v>
-      </c>
-      <c r="I94" s="67">
-        <v>200</v>
-      </c>
-      <c r="J94" s="68">
-        <v>1993</v>
-      </c>
-      <c r="K94" s="67">
-        <v>2024</v>
-      </c>
-      <c r="L94" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="M94" s="69" t="s">
-        <v>172</v>
-      </c>
-      <c r="N94" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="O94" s="17"/>
-      <c r="P94" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="16">
-      <c r="A95" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="B95" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="C95" s="65">
-        <v>3</v>
-      </c>
-      <c r="D95" s="65" t="s">
-        <v>174</v>
-      </c>
-      <c r="E95" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" s="114">
-        <v>46.966999999999999</v>
-      </c>
-      <c r="G95" s="114">
-        <v>6.0110000000000001</v>
-      </c>
-      <c r="H95" s="66">
-        <v>420</v>
-      </c>
-      <c r="I95" s="67">
-        <v>170</v>
-      </c>
-      <c r="J95" s="68">
-        <v>1976</v>
-      </c>
-      <c r="K95" s="67">
-        <v>2024</v>
-      </c>
-      <c r="L95" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="M95" s="69" t="s">
-        <v>175</v>
-      </c>
-      <c r="N95" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O95" s="17"/>
-      <c r="P95" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="16">
-      <c r="A96" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="B96" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="C96" s="65">
-        <v>4</v>
-      </c>
-      <c r="D96" s="65" t="s">
-        <v>176</v>
-      </c>
-      <c r="E96" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F96" s="114">
-        <v>46.978000000000002</v>
-      </c>
-      <c r="G96" s="114">
-        <v>6.0019999999999998</v>
-      </c>
-      <c r="H96" s="66">
-        <v>375</v>
-      </c>
-      <c r="I96" s="67">
-        <v>13</v>
-      </c>
-      <c r="J96" s="68">
-        <v>1969</v>
-      </c>
-      <c r="K96" s="67">
-        <v>2024</v>
-      </c>
-      <c r="L96" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="M96" s="69" t="s">
-        <v>175</v>
       </c>
       <c r="N96" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O96" s="17"/>
       <c r="P96" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="16">
-      <c r="A97" s="70" t="s">
-        <v>177</v>
-      </c>
-      <c r="B97" s="70" t="s">
-        <v>178</v>
-      </c>
-      <c r="C97" s="70">
-        <v>1</v>
-      </c>
-      <c r="D97" s="70" t="s">
-        <v>179</v>
-      </c>
-      <c r="E97" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="F97" s="110">
-        <v>35.332999999999998</v>
-      </c>
-      <c r="G97" s="110">
-        <v>25.047000000000001</v>
-      </c>
-      <c r="H97" s="71">
-        <v>19</v>
-      </c>
-      <c r="I97" s="72">
-        <v>305</v>
-      </c>
-      <c r="J97" s="73">
-        <v>1999</v>
-      </c>
-      <c r="K97" s="72">
-        <v>2001</v>
-      </c>
-      <c r="L97" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M97" s="74" t="s">
-        <v>180</v>
+      <c r="A97" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C97" s="63">
+        <v>2</v>
+      </c>
+      <c r="D97" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="E97" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" s="112">
+        <v>47.011000000000003</v>
+      </c>
+      <c r="G97" s="112">
+        <v>6.2990000000000004</v>
+      </c>
+      <c r="H97" s="64">
+        <v>530</v>
+      </c>
+      <c r="I97" s="65">
+        <v>200</v>
+      </c>
+      <c r="J97" s="66">
+        <v>1993</v>
+      </c>
+      <c r="K97" s="65">
+        <v>2024</v>
+      </c>
+      <c r="L97" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="M97" s="67" t="s">
+        <v>171</v>
       </c>
       <c r="N97" s="20" t="s">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="O97" s="17"/>
       <c r="P97" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="16">
-      <c r="A98" s="70" t="s">
+      <c r="A98" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B98" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C98" s="63">
+        <v>3</v>
+      </c>
+      <c r="D98" s="63" t="s">
+        <v>173</v>
+      </c>
+      <c r="E98" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="112">
+        <v>46.966999999999999</v>
+      </c>
+      <c r="G98" s="112">
+        <v>6.0110000000000001</v>
+      </c>
+      <c r="H98" s="64">
+        <v>420</v>
+      </c>
+      <c r="I98" s="65">
+        <v>170</v>
+      </c>
+      <c r="J98" s="66">
+        <v>1976</v>
+      </c>
+      <c r="K98" s="65">
+        <v>2024</v>
+      </c>
+      <c r="L98" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="M98" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="N98" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O98" s="17"/>
+      <c r="P98" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="16">
+      <c r="A99" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B99" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C99" s="63">
+        <v>4</v>
+      </c>
+      <c r="D99" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="E99" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" s="112">
+        <v>46.978000000000002</v>
+      </c>
+      <c r="G99" s="112">
+        <v>6.0019999999999998</v>
+      </c>
+      <c r="H99" s="64">
+        <v>375</v>
+      </c>
+      <c r="I99" s="65">
+        <v>13</v>
+      </c>
+      <c r="J99" s="66">
+        <v>1969</v>
+      </c>
+      <c r="K99" s="65">
+        <v>2024</v>
+      </c>
+      <c r="L99" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="M99" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="N99" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O99" s="17"/>
+      <c r="P99" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="16">
+      <c r="A100" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="B100" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="B98" s="70" t="s">
-        <v>181</v>
-      </c>
-      <c r="C98" s="70">
-        <v>2</v>
-      </c>
-      <c r="D98" s="70" t="s">
-        <v>182</v>
-      </c>
-      <c r="E98" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="F98" s="110">
-        <v>39.923999999999999</v>
-      </c>
-      <c r="G98" s="110">
-        <v>20.192</v>
-      </c>
-      <c r="H98" s="71">
-        <v>170</v>
-      </c>
-      <c r="I98" s="72">
-        <v>400</v>
-      </c>
-      <c r="J98" s="73">
-        <v>1968</v>
-      </c>
-      <c r="K98" s="72">
-        <v>1973</v>
-      </c>
-      <c r="L98" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M98" s="75" t="s">
-        <v>183</v>
-      </c>
-      <c r="N98" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="O98" s="17"/>
-      <c r="P98" s="104" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="16">
-      <c r="A99" s="70" t="s">
-        <v>185</v>
-      </c>
-      <c r="B99" s="70" t="s">
-        <v>181</v>
-      </c>
-      <c r="C99" s="70">
-        <v>3</v>
-      </c>
-      <c r="D99" s="70" t="s">
-        <v>186</v>
-      </c>
-      <c r="E99" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="F99" s="110">
-        <v>41.651000000000003</v>
-      </c>
-      <c r="G99" s="110">
-        <v>20.068999999999999</v>
-      </c>
-      <c r="H99" s="71">
-        <v>290</v>
-      </c>
-      <c r="I99" s="72">
-        <v>10</v>
-      </c>
-      <c r="J99" s="73">
-        <v>1966</v>
-      </c>
-      <c r="K99" s="72">
-        <v>1986</v>
-      </c>
-      <c r="L99" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M99" s="75" t="s">
-        <v>183</v>
-      </c>
-      <c r="N99" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="O99" s="17"/>
-      <c r="P99" s="104" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="16">
-      <c r="A100" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="B100" s="53" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="53">
+      <c r="C100" s="68">
         <v>1</v>
       </c>
-      <c r="D100" s="53" t="s">
-        <v>199</v>
-      </c>
-      <c r="E100" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F100" s="111">
-        <v>33.613</v>
-      </c>
-      <c r="G100" s="111">
-        <v>36.146999999999998</v>
-      </c>
-      <c r="H100" s="54">
-        <v>887</v>
-      </c>
-      <c r="I100" s="78"/>
-      <c r="J100" s="57">
-        <v>1987</v>
-      </c>
-      <c r="K100" s="55">
-        <v>2005</v>
-      </c>
-      <c r="L100" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M100" s="79" t="s">
-        <v>117</v>
+      <c r="D100" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="E100" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" s="108">
+        <v>35.332999999999998</v>
+      </c>
+      <c r="G100" s="108">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="H100" s="69">
+        <v>19</v>
+      </c>
+      <c r="I100" s="70">
+        <v>305</v>
+      </c>
+      <c r="J100" s="71">
+        <v>1999</v>
+      </c>
+      <c r="K100" s="70">
+        <v>2001</v>
+      </c>
+      <c r="L100" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M100" s="72" t="s">
+        <v>179</v>
       </c>
       <c r="N100" s="20" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="O100" s="17"/>
       <c r="P100" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="16">
-      <c r="A101" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="B101" s="53" t="s">
-        <v>198</v>
-      </c>
-      <c r="C101" s="53">
+      <c r="A101" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="C101" s="68">
         <v>2</v>
       </c>
-      <c r="D101" s="53" t="s">
-        <v>200</v>
-      </c>
-      <c r="E101" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F101" s="111">
-        <v>33.618000000000002</v>
-      </c>
-      <c r="G101" s="111">
-        <v>36.180999999999997</v>
-      </c>
-      <c r="H101" s="54">
-        <v>853</v>
-      </c>
-      <c r="I101" s="78"/>
-      <c r="J101" s="57">
-        <v>1987</v>
-      </c>
-      <c r="K101" s="55">
-        <v>2005</v>
-      </c>
-      <c r="L101" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M101" s="80" t="s">
-        <v>117</v>
+      <c r="D101" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E101" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" s="108">
+        <v>39.923999999999999</v>
+      </c>
+      <c r="G101" s="108">
+        <v>20.192</v>
+      </c>
+      <c r="H101" s="69">
+        <v>170</v>
+      </c>
+      <c r="I101" s="70">
+        <v>400</v>
+      </c>
+      <c r="J101" s="71">
+        <v>1968</v>
+      </c>
+      <c r="K101" s="70">
+        <v>1973</v>
+      </c>
+      <c r="L101" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M101" s="73" t="s">
+        <v>182</v>
       </c>
       <c r="N101" s="20" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="O101" s="17"/>
-      <c r="P101" t="s">
-        <v>323</v>
+      <c r="P101" s="102" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="16">
-      <c r="A102" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="B102" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="C102" s="53">
+      <c r="A102" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="B102" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="C102" s="68">
         <v>3</v>
       </c>
-      <c r="D102" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="E102" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F102" s="111">
-        <v>33.247999999999998</v>
-      </c>
-      <c r="G102" s="111">
-        <v>35.695</v>
-      </c>
-      <c r="H102" s="54">
-        <v>390</v>
-      </c>
-      <c r="I102" s="78">
-        <v>120</v>
-      </c>
-      <c r="J102" s="57">
-        <v>1989</v>
-      </c>
-      <c r="K102" s="55">
-        <v>1999</v>
-      </c>
-      <c r="L102" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M102" s="80" t="s">
-        <v>203</v>
+      <c r="D102" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="E102" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="108">
+        <v>41.651000000000003</v>
+      </c>
+      <c r="G102" s="108">
+        <v>20.068999999999999</v>
+      </c>
+      <c r="H102" s="69">
+        <v>290</v>
+      </c>
+      <c r="I102" s="70">
+        <v>10</v>
+      </c>
+      <c r="J102" s="71">
+        <v>1966</v>
+      </c>
+      <c r="K102" s="70">
+        <v>1986</v>
+      </c>
+      <c r="L102" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M102" s="73" t="s">
+        <v>182</v>
       </c>
       <c r="N102" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="O102" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="P102" t="s">
-        <v>324</v>
+        <v>183</v>
+      </c>
+      <c r="O102" s="17"/>
+      <c r="P102" s="102" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="16">
       <c r="A103" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="B103" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B103" s="53" t="s">
-        <v>201</v>
-      </c>
       <c r="C103" s="53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D103" s="53" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E103" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F103" s="111">
-        <v>33.249000000000002</v>
-      </c>
-      <c r="G103" s="111">
-        <v>35.652999999999999</v>
+      <c r="F103" s="109">
+        <v>33.613</v>
+      </c>
+      <c r="G103" s="109">
+        <v>36.146999999999998</v>
       </c>
       <c r="H103" s="54">
-        <v>195</v>
-      </c>
-      <c r="I103" s="78">
-        <v>290</v>
-      </c>
-      <c r="J103" s="57">
-        <v>1989</v>
+        <v>887</v>
+      </c>
+      <c r="I103" s="76"/>
+      <c r="J103" s="56">
+        <v>1987</v>
       </c>
       <c r="K103" s="55">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="L103" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="M103" s="79" t="s">
-        <v>206</v>
+      <c r="M103" s="77" t="s">
+        <v>117</v>
       </c>
       <c r="N103" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O103" s="17" t="s">
-        <v>204</v>
-      </c>
+      <c r="O103" s="17"/>
       <c r="P103" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="16">
       <c r="A104" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="B104" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="B104" s="53" t="s">
-        <v>207</v>
-      </c>
       <c r="C104" s="53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104" s="53" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E104" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F104" s="111">
-        <v>34.01</v>
-      </c>
-      <c r="G104" s="111">
-        <v>35.828000000000003</v>
+      <c r="F104" s="109">
+        <v>33.618000000000002</v>
+      </c>
+      <c r="G104" s="109">
+        <v>36.180999999999997</v>
       </c>
       <c r="H104" s="54">
-        <v>1390</v>
-      </c>
-      <c r="I104" s="55">
-        <v>15</v>
-      </c>
-      <c r="J104" s="57">
-        <v>2014</v>
+        <v>853</v>
+      </c>
+      <c r="I104" s="76"/>
+      <c r="J104" s="56">
+        <v>1987</v>
       </c>
       <c r="K104" s="55">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="L104" s="55" t="s">
-        <v>362</v>
-      </c>
-      <c r="M104" s="79" t="s">
-        <v>209</v>
+        <v>20</v>
+      </c>
+      <c r="M104" s="78" t="s">
+        <v>117</v>
       </c>
       <c r="N104" s="20" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="O104" s="17"/>
       <c r="P104" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="16">
       <c r="A105" s="53" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B105" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C105" s="53">
+        <v>3</v>
+      </c>
+      <c r="D105" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="E105" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" s="109">
+        <v>33.247999999999998</v>
+      </c>
+      <c r="G105" s="109">
+        <v>35.695</v>
+      </c>
+      <c r="H105" s="54">
+        <v>390</v>
+      </c>
+      <c r="I105" s="76">
+        <v>120</v>
+      </c>
+      <c r="J105" s="56">
+        <v>1989</v>
+      </c>
+      <c r="K105" s="55">
+        <v>1999</v>
+      </c>
+      <c r="L105" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M105" s="78" t="s">
+        <v>202</v>
+      </c>
+      <c r="N105" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="O105" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="P105" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="16">
+      <c r="A106" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="B106" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C106" s="53">
+        <v>4</v>
+      </c>
+      <c r="D106" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="E106" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" s="109">
+        <v>33.249000000000002</v>
+      </c>
+      <c r="G106" s="109">
+        <v>35.652999999999999</v>
+      </c>
+      <c r="H106" s="54">
+        <v>195</v>
+      </c>
+      <c r="I106" s="76">
+        <v>290</v>
+      </c>
+      <c r="J106" s="56">
+        <v>1989</v>
+      </c>
+      <c r="K106" s="55">
+        <v>1999</v>
+      </c>
+      <c r="L106" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M106" s="77" t="s">
+        <v>205</v>
+      </c>
+      <c r="N106" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="O106" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="P106" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="16">
+      <c r="A107" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="B107" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="C107" s="53">
+        <v>5</v>
+      </c>
+      <c r="D107" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="C105" s="53">
-        <v>6</v>
-      </c>
-      <c r="D105" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="E105" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F105" s="111">
-        <v>33.944000000000003</v>
-      </c>
-      <c r="G105" s="111">
-        <v>35.637999999999998</v>
-      </c>
-      <c r="H105" s="54">
-        <v>56</v>
-      </c>
-      <c r="I105" s="55"/>
-      <c r="J105" s="57">
+      <c r="E107" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" s="109">
+        <v>34.01</v>
+      </c>
+      <c r="G107" s="109">
+        <v>35.828000000000003</v>
+      </c>
+      <c r="H107" s="54">
+        <v>1390</v>
+      </c>
+      <c r="I107" s="55">
+        <v>15</v>
+      </c>
+      <c r="J107" s="56">
         <v>2014</v>
       </c>
-      <c r="K105" s="55">
+      <c r="K107" s="55">
         <v>2018</v>
       </c>
-      <c r="L105" s="55" t="s">
-        <v>362</v>
-      </c>
-      <c r="M105" s="79" t="s">
-        <v>209</v>
-      </c>
-      <c r="N105" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O105" s="17"/>
-      <c r="P105" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="16">
-      <c r="A106" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C106" s="81">
-        <v>1</v>
-      </c>
-      <c r="D106" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="E106" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F106" s="82">
-        <v>42.651800000000001</v>
-      </c>
-      <c r="G106" s="82">
-        <v>1.52E-2</v>
-      </c>
-      <c r="H106" s="83">
-        <v>2000</v>
-      </c>
-      <c r="I106" s="84">
-        <v>14.483000000000001</v>
-      </c>
-      <c r="J106" s="85">
-        <v>2018</v>
-      </c>
-      <c r="K106" s="12">
-        <v>2025</v>
-      </c>
-      <c r="L106" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M106" s="86" t="s">
-        <v>213</v>
-      </c>
-      <c r="N106" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O106" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="P106" s="104" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="16">
-      <c r="A107" s="81" t="s">
-        <v>211</v>
-      </c>
-      <c r="B107" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="C107" s="81">
-        <v>2</v>
-      </c>
-      <c r="D107" s="81" t="s">
-        <v>214</v>
-      </c>
-      <c r="E107" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F107" s="82">
-        <v>42.890999999999998</v>
-      </c>
-      <c r="G107" s="82">
-        <v>1.927</v>
-      </c>
-      <c r="H107" s="83">
-        <v>100</v>
-      </c>
-      <c r="I107" s="84">
-        <v>125</v>
-      </c>
-      <c r="J107" s="85">
-        <v>2019</v>
-      </c>
-      <c r="K107" s="12">
-        <v>2024</v>
-      </c>
-      <c r="L107" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M107" s="69" t="s">
-        <v>175</v>
+      <c r="L107" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="M107" s="77" t="s">
+        <v>208</v>
       </c>
       <c r="N107" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O107" s="17"/>
-      <c r="P107" s="104" t="s">
-        <v>358</v>
+      <c r="P107" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="16">
-      <c r="A108" s="81" t="s">
-        <v>211</v>
-      </c>
-      <c r="B108" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="C108" s="81">
-        <v>3</v>
-      </c>
-      <c r="D108" s="81" t="s">
-        <v>215</v>
-      </c>
-      <c r="E108" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F108" s="82">
-        <v>42.954999999999998</v>
-      </c>
-      <c r="G108" s="82">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="H108" s="83">
-        <v>450</v>
-      </c>
-      <c r="I108" s="84">
-        <v>13</v>
-      </c>
-      <c r="J108" s="85">
-        <v>2020</v>
-      </c>
-      <c r="K108" s="12">
-        <v>2024</v>
-      </c>
-      <c r="L108" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M108" s="69" t="s">
-        <v>216</v>
+      <c r="A108" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="B108" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="C108" s="53">
+        <v>6</v>
+      </c>
+      <c r="D108" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="E108" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" s="109">
+        <v>33.944000000000003</v>
+      </c>
+      <c r="G108" s="109">
+        <v>35.637999999999998</v>
+      </c>
+      <c r="H108" s="54">
+        <v>56</v>
+      </c>
+      <c r="I108" s="55"/>
+      <c r="J108" s="56">
+        <v>2014</v>
+      </c>
+      <c r="K108" s="55">
+        <v>2018</v>
+      </c>
+      <c r="L108" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="M108" s="77" t="s">
+        <v>208</v>
       </c>
       <c r="N108" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O108" s="17"/>
-      <c r="P108" s="104" t="s">
-        <v>359</v>
+      <c r="P108" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="16">
-      <c r="A109" s="81" t="s">
+      <c r="A109" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C109" s="79">
+        <v>1</v>
+      </c>
+      <c r="D109" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="B109" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="C109" s="81">
-        <v>4</v>
-      </c>
-      <c r="D109" s="81" t="s">
-        <v>217</v>
-      </c>
-      <c r="E109" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F109" s="82">
-        <v>42.99</v>
-      </c>
-      <c r="G109" s="82">
-        <v>1.048</v>
-      </c>
-      <c r="H109" s="83">
-        <v>500</v>
-      </c>
-      <c r="I109" s="84">
-        <v>11</v>
-      </c>
-      <c r="J109" s="85">
-        <v>2009</v>
+      <c r="E109" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" s="80">
+        <v>42.651800000000001</v>
+      </c>
+      <c r="G109" s="80">
+        <v>1.52E-2</v>
+      </c>
+      <c r="H109" s="81">
+        <v>2000</v>
+      </c>
+      <c r="I109" s="82">
+        <v>14.483000000000001</v>
+      </c>
+      <c r="J109" s="83">
+        <v>2018</v>
       </c>
       <c r="K109" s="12">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L109" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M109" s="69" t="s">
-        <v>216</v>
+      <c r="M109" s="84" t="s">
+        <v>212</v>
       </c>
       <c r="N109" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O109" s="17"/>
-      <c r="P109" s="104" t="s">
+      <c r="O109" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="P109" s="102" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="16">
+      <c r="A110" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B110" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C110" s="79">
+        <v>2</v>
+      </c>
+      <c r="D110" s="79" t="s">
+        <v>213</v>
+      </c>
+      <c r="E110" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" s="80">
+        <v>42.890999999999998</v>
+      </c>
+      <c r="G110" s="80">
+        <v>1.927</v>
+      </c>
+      <c r="H110" s="81">
+        <v>100</v>
+      </c>
+      <c r="I110" s="82">
+        <v>125</v>
+      </c>
+      <c r="J110" s="83">
+        <v>2019</v>
+      </c>
+      <c r="K110" s="12">
+        <v>2024</v>
+      </c>
+      <c r="L110" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M110" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="N110" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O110" s="17"/>
+      <c r="P110" s="102" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="16">
+      <c r="A111" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B111" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="79">
+        <v>3</v>
+      </c>
+      <c r="D111" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="E111" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" s="80">
+        <v>42.954999999999998</v>
+      </c>
+      <c r="G111" s="80">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="H111" s="81">
+        <v>450</v>
+      </c>
+      <c r="I111" s="82">
+        <v>13</v>
+      </c>
+      <c r="J111" s="83">
+        <v>2020</v>
+      </c>
+      <c r="K111" s="12">
+        <v>2024</v>
+      </c>
+      <c r="L111" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M111" s="67" t="s">
+        <v>215</v>
+      </c>
+      <c r="N111" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O111" s="17"/>
+      <c r="P111" s="102" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="16">
+      <c r="A112" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B112" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C112" s="79">
+        <v>4</v>
+      </c>
+      <c r="D112" s="79" t="s">
+        <v>216</v>
+      </c>
+      <c r="E112" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="80">
+        <v>42.99</v>
+      </c>
+      <c r="G112" s="80">
+        <v>1.048</v>
+      </c>
+      <c r="H112" s="81">
+        <v>500</v>
+      </c>
+      <c r="I112" s="82">
+        <v>11</v>
+      </c>
+      <c r="J112" s="83">
+        <v>2009</v>
+      </c>
+      <c r="K112" s="12">
+        <v>2024</v>
+      </c>
+      <c r="L112" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M112" s="67" t="s">
+        <v>215</v>
+      </c>
+      <c r="N112" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O112" s="17"/>
+      <c r="P112" s="102" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="16">
+      <c r="A113" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B113" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C113" s="85">
+        <v>1</v>
+      </c>
+      <c r="D113" s="85" t="s">
+        <v>219</v>
+      </c>
+      <c r="E113" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" s="113">
+        <v>37.113</v>
+      </c>
+      <c r="G113" s="113">
+        <v>32.140999999999998</v>
+      </c>
+      <c r="H113" s="86">
+        <v>1100</v>
+      </c>
+      <c r="I113" s="87">
+        <v>85</v>
+      </c>
+      <c r="J113" s="88">
+        <v>2003</v>
+      </c>
+      <c r="K113" s="87">
+        <v>2019</v>
+      </c>
+      <c r="L113" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M113" s="89" t="s">
+        <v>220</v>
+      </c>
+      <c r="N113" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O113" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P113" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="16">
-      <c r="A110" s="87" t="s">
+    <row r="114" spans="1:16" ht="16">
+      <c r="A114" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B114" s="85" t="s">
         <v>218</v>
       </c>
-      <c r="B110" s="87" t="s">
-        <v>219</v>
-      </c>
-      <c r="C110" s="87">
+      <c r="C114" s="85">
+        <v>2</v>
+      </c>
+      <c r="D114" s="85" t="s">
+        <v>222</v>
+      </c>
+      <c r="E114" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" s="113">
+        <v>37.094000000000001</v>
+      </c>
+      <c r="G114" s="113">
+        <v>30.581</v>
+      </c>
+      <c r="H114" s="87">
+        <v>300</v>
+      </c>
+      <c r="I114" s="87">
+        <v>2000</v>
+      </c>
+      <c r="J114" s="87">
+        <v>2003</v>
+      </c>
+      <c r="K114" s="87">
+        <v>2017</v>
+      </c>
+      <c r="L114" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M114" s="90" t="s">
+        <v>220</v>
+      </c>
+      <c r="N114" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O114" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P114" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="16">
+      <c r="A115" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B115" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C115" s="85">
+        <v>3</v>
+      </c>
+      <c r="D115" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="E115" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" s="113">
+        <v>37.302</v>
+      </c>
+      <c r="G115" s="113">
+        <v>31.942</v>
+      </c>
+      <c r="H115" s="87">
+        <v>1099</v>
+      </c>
+      <c r="I115" s="87">
+        <v>70</v>
+      </c>
+      <c r="J115" s="87">
+        <v>2014</v>
+      </c>
+      <c r="K115" s="87">
+        <v>2025</v>
+      </c>
+      <c r="L115" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M115" s="85" t="s">
+        <v>224</v>
+      </c>
+      <c r="N115" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O115" s="17"/>
+      <c r="P115" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="16">
+      <c r="A116" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B116" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" s="85">
+        <v>4</v>
+      </c>
+      <c r="D116" s="85" t="s">
+        <v>225</v>
+      </c>
+      <c r="E116" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116" s="113">
+        <v>37.468000000000004</v>
+      </c>
+      <c r="G116" s="113">
+        <v>34.863</v>
+      </c>
+      <c r="H116" s="87">
+        <v>840</v>
+      </c>
+      <c r="I116" s="87">
+        <v>140</v>
+      </c>
+      <c r="J116" s="87">
+        <v>2011</v>
+      </c>
+      <c r="K116" s="87">
+        <v>2024</v>
+      </c>
+      <c r="L116" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M116" s="91" t="s">
+        <v>226</v>
+      </c>
+      <c r="N116" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O116" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P116" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="16">
+      <c r="A117" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B117" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C117" s="85">
+        <v>5</v>
+      </c>
+      <c r="D117" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="E117" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F117" s="113">
+        <v>37.771000000000001</v>
+      </c>
+      <c r="G117" s="113">
+        <v>35.396000000000001</v>
+      </c>
+      <c r="H117" s="87">
+        <v>660</v>
+      </c>
+      <c r="I117" s="87">
+        <v>350</v>
+      </c>
+      <c r="J117" s="87">
+        <v>2011</v>
+      </c>
+      <c r="K117" s="87">
+        <v>2017</v>
+      </c>
+      <c r="L117" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M117" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="N117" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O117" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P117" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="16">
+      <c r="A118" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B118" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C118" s="85">
+        <v>6</v>
+      </c>
+      <c r="D118" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="E118" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F118" s="113">
+        <v>38.814999999999998</v>
+      </c>
+      <c r="G118" s="113">
+        <v>35.863999999999997</v>
+      </c>
+      <c r="H118" s="87">
+        <v>1536</v>
+      </c>
+      <c r="I118" s="87">
+        <v>10</v>
+      </c>
+      <c r="J118" s="87">
+        <v>2002</v>
+      </c>
+      <c r="K118" s="87">
+        <v>2019</v>
+      </c>
+      <c r="L118" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M118" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="N118" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O118" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P118" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="16">
+      <c r="A119" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B119" s="92" t="s">
+        <v>232</v>
+      </c>
+      <c r="C119" s="92">
         <v>1</v>
       </c>
-      <c r="D110" s="87" t="s">
-        <v>220</v>
-      </c>
-      <c r="E110" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F110" s="115">
-        <v>37.113</v>
-      </c>
-      <c r="G110" s="115">
-        <v>32.140999999999998</v>
-      </c>
-      <c r="H110" s="88">
-        <v>1100</v>
-      </c>
-      <c r="I110" s="89">
-        <v>85</v>
-      </c>
-      <c r="J110" s="90">
+      <c r="D119" s="92" t="s">
+        <v>233</v>
+      </c>
+      <c r="E119" s="92"/>
+      <c r="F119" s="114">
+        <v>31.375</v>
+      </c>
+      <c r="G119" s="115">
+        <v>49.84</v>
+      </c>
+      <c r="H119" s="93">
+        <v>490</v>
+      </c>
+      <c r="I119" s="94"/>
+      <c r="J119" s="95">
         <v>2003</v>
       </c>
-      <c r="K110" s="89">
-        <v>2019</v>
-      </c>
-      <c r="L110" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M110" s="91" t="s">
-        <v>221</v>
-      </c>
-      <c r="N110" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O110" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="P110" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="16">
-      <c r="A111" s="87" t="s">
-        <v>218</v>
-      </c>
-      <c r="B111" s="87" t="s">
-        <v>219</v>
-      </c>
-      <c r="C111" s="87">
-        <v>2</v>
-      </c>
-      <c r="D111" s="87" t="s">
-        <v>223</v>
-      </c>
-      <c r="E111" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" s="115">
-        <v>37.094000000000001</v>
-      </c>
-      <c r="G111" s="115">
-        <v>30.581</v>
-      </c>
-      <c r="H111" s="89">
-        <v>300</v>
-      </c>
-      <c r="I111" s="89">
-        <v>2000</v>
-      </c>
-      <c r="J111" s="89">
-        <v>2003</v>
-      </c>
-      <c r="K111" s="89">
-        <v>2017</v>
-      </c>
-      <c r="L111" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M111" s="92" t="s">
-        <v>221</v>
-      </c>
-      <c r="N111" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O111" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="P111" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="16">
-      <c r="A112" s="87" t="s">
-        <v>218</v>
-      </c>
-      <c r="B112" s="87" t="s">
-        <v>219</v>
-      </c>
-      <c r="C112" s="87">
-        <v>3</v>
-      </c>
-      <c r="D112" s="87" t="s">
-        <v>224</v>
-      </c>
-      <c r="E112" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F112" s="115">
-        <v>37.302</v>
-      </c>
-      <c r="G112" s="115">
-        <v>31.942</v>
-      </c>
-      <c r="H112" s="89">
-        <v>1099</v>
-      </c>
-      <c r="I112" s="89">
-        <v>70</v>
-      </c>
-      <c r="J112" s="89">
-        <v>2014</v>
-      </c>
-      <c r="K112" s="89">
-        <v>2025</v>
-      </c>
-      <c r="L112" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M112" s="87" t="s">
-        <v>225</v>
-      </c>
-      <c r="N112" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O112" s="17"/>
-      <c r="P112" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="16">
-      <c r="A113" s="87" t="s">
-        <v>218</v>
-      </c>
-      <c r="B113" s="87" t="s">
-        <v>219</v>
-      </c>
-      <c r="C113" s="87">
-        <v>4</v>
-      </c>
-      <c r="D113" s="87" t="s">
-        <v>226</v>
-      </c>
-      <c r="E113" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F113" s="115">
-        <v>37.468000000000004</v>
-      </c>
-      <c r="G113" s="115">
-        <v>34.863</v>
-      </c>
-      <c r="H113" s="89">
-        <v>840</v>
-      </c>
-      <c r="I113" s="89">
-        <v>140</v>
-      </c>
-      <c r="J113" s="89">
+      <c r="K119" s="96">
         <v>2011</v>
       </c>
-      <c r="K113" s="89">
-        <v>2024</v>
-      </c>
-      <c r="L113" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M113" s="93" t="s">
-        <v>227</v>
-      </c>
-      <c r="N113" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O113" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="P113" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="16">
-      <c r="A114" s="87" t="s">
-        <v>218</v>
-      </c>
-      <c r="B114" s="87" t="s">
-        <v>219</v>
-      </c>
-      <c r="C114" s="87">
-        <v>5</v>
-      </c>
-      <c r="D114" s="87" t="s">
-        <v>228</v>
-      </c>
-      <c r="E114" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F114" s="115">
-        <v>37.771000000000001</v>
-      </c>
-      <c r="G114" s="115">
-        <v>35.396000000000001</v>
-      </c>
-      <c r="H114" s="89">
-        <v>660</v>
-      </c>
-      <c r="I114" s="89">
-        <v>350</v>
-      </c>
-      <c r="J114" s="89">
-        <v>2011</v>
-      </c>
-      <c r="K114" s="89">
-        <v>2017</v>
-      </c>
-      <c r="L114" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M114" s="93" t="s">
-        <v>229</v>
-      </c>
-      <c r="N114" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O114" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="P114" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="16">
-      <c r="A115" s="87" t="s">
-        <v>218</v>
-      </c>
-      <c r="B115" s="87" t="s">
-        <v>219</v>
-      </c>
-      <c r="C115" s="87">
-        <v>6</v>
-      </c>
-      <c r="D115" s="87" t="s">
-        <v>230</v>
-      </c>
-      <c r="E115" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F115" s="115">
-        <v>38.814999999999998</v>
-      </c>
-      <c r="G115" s="115">
-        <v>35.863999999999997</v>
-      </c>
-      <c r="H115" s="89">
-        <v>1536</v>
-      </c>
-      <c r="I115" s="89">
-        <v>10</v>
-      </c>
-      <c r="J115" s="89">
-        <v>2002</v>
-      </c>
-      <c r="K115" s="89">
-        <v>2019</v>
-      </c>
-      <c r="L115" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="M115" s="93" t="s">
-        <v>231</v>
-      </c>
-      <c r="N115" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="O115" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="P115" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="16">
-      <c r="A116" s="94" t="s">
-        <v>232</v>
-      </c>
-      <c r="B116" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="C116" s="94">
-        <v>1</v>
-      </c>
-      <c r="D116" s="94" t="s">
+      <c r="L119" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M119" s="97" t="s">
         <v>234</v>
-      </c>
-      <c r="E116" s="94"/>
-      <c r="F116" s="116">
-        <v>31.375</v>
-      </c>
-      <c r="G116" s="117">
-        <v>49.84</v>
-      </c>
-      <c r="H116" s="95">
-        <v>490</v>
-      </c>
-      <c r="I116" s="96"/>
-      <c r="J116" s="97">
-        <v>2003</v>
-      </c>
-      <c r="K116" s="98">
-        <v>2011</v>
-      </c>
-      <c r="L116" s="98" t="s">
-        <v>20</v>
-      </c>
-      <c r="M116" s="99" t="s">
-        <v>235</v>
-      </c>
-      <c r="N116" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O116" s="17"/>
-      <c r="P116" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" ht="16">
-      <c r="A117" s="94" t="s">
-        <v>232</v>
-      </c>
-      <c r="B117" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="C117" s="94">
-        <v>2</v>
-      </c>
-      <c r="D117" s="94" t="s">
-        <v>236</v>
-      </c>
-      <c r="E117" s="94"/>
-      <c r="F117" s="116">
-        <v>31.256</v>
-      </c>
-      <c r="G117" s="117">
-        <v>49.968000000000004</v>
-      </c>
-      <c r="H117" s="95">
-        <v>675</v>
-      </c>
-      <c r="I117" s="96"/>
-      <c r="J117" s="97">
-        <v>2010</v>
-      </c>
-      <c r="K117" s="98">
-        <v>2017</v>
-      </c>
-      <c r="L117" s="98" t="s">
-        <v>20</v>
-      </c>
-      <c r="M117" s="99" t="s">
-        <v>235</v>
-      </c>
-      <c r="N117" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O117" s="17"/>
-      <c r="P117" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="16">
-      <c r="A118" s="94" t="s">
-        <v>232</v>
-      </c>
-      <c r="B118" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="C118" s="94">
-        <v>3</v>
-      </c>
-      <c r="D118" s="94" t="s">
-        <v>237</v>
-      </c>
-      <c r="E118" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F118" s="116">
-        <v>34.39</v>
-      </c>
-      <c r="G118" s="116">
-        <v>47.436999999999998</v>
-      </c>
-      <c r="H118" s="98">
-        <v>1290</v>
-      </c>
-      <c r="I118" s="98"/>
-      <c r="J118" s="98">
-        <v>1970</v>
-      </c>
-      <c r="K118" s="98">
-        <v>2009</v>
-      </c>
-      <c r="L118" s="98" t="s">
-        <v>112</v>
-      </c>
-      <c r="M118" s="99" t="s">
-        <v>235</v>
-      </c>
-      <c r="N118" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O118" s="100"/>
-      <c r="P118" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="16">
-      <c r="A119" s="94" t="s">
-        <v>232</v>
-      </c>
-      <c r="B119" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="C119" s="94">
-        <v>4</v>
-      </c>
-      <c r="D119" s="94" t="s">
-        <v>238</v>
-      </c>
-      <c r="E119" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F119" s="116">
-        <v>32.500999999999998</v>
-      </c>
-      <c r="G119" s="116">
-        <v>50.215000000000003</v>
-      </c>
-      <c r="H119" s="98">
-        <v>2220</v>
-      </c>
-      <c r="I119" s="98"/>
-      <c r="J119" s="98">
-        <v>1998</v>
-      </c>
-      <c r="K119" s="98">
-        <v>2013</v>
-      </c>
-      <c r="L119" s="98" t="s">
-        <v>112</v>
-      </c>
-      <c r="M119" s="99" t="s">
-        <v>235</v>
       </c>
       <c r="N119" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O119" s="100"/>
+      <c r="O119" s="17"/>
       <c r="P119" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="16">
-      <c r="A120" s="94" t="s">
+      <c r="A120" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B120" s="92" t="s">
         <v>232</v>
       </c>
-      <c r="B120" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="C120" s="94">
-        <v>5</v>
-      </c>
-      <c r="D120" s="94" t="s">
-        <v>239</v>
-      </c>
-      <c r="E120" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F120" s="116">
-        <v>32.216999999999999</v>
-      </c>
-      <c r="G120" s="116">
-        <v>50.543999999999997</v>
-      </c>
-      <c r="H120" s="98">
-        <v>2016</v>
-      </c>
-      <c r="I120" s="96"/>
-      <c r="J120" s="98">
-        <v>1998</v>
-      </c>
-      <c r="K120" s="98">
-        <v>2014</v>
-      </c>
-      <c r="L120" s="98" t="s">
-        <v>112</v>
-      </c>
-      <c r="M120" s="99" t="s">
+      <c r="C120" s="92">
+        <v>2</v>
+      </c>
+      <c r="D120" s="92" t="s">
         <v>235</v>
+      </c>
+      <c r="E120" s="92"/>
+      <c r="F120" s="114">
+        <v>31.256</v>
+      </c>
+      <c r="G120" s="115">
+        <v>49.968000000000004</v>
+      </c>
+      <c r="H120" s="93">
+        <v>675</v>
+      </c>
+      <c r="I120" s="94"/>
+      <c r="J120" s="95">
+        <v>2010</v>
+      </c>
+      <c r="K120" s="96">
+        <v>2017</v>
+      </c>
+      <c r="L120" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M120" s="97" t="s">
+        <v>234</v>
       </c>
       <c r="N120" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O120" s="100"/>
+      <c r="O120" s="17"/>
       <c r="P120" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="16">
-      <c r="A121" s="94" t="s">
+      <c r="A121" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B121" s="92" t="s">
         <v>232</v>
       </c>
-      <c r="B121" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="C121" s="94">
-        <v>6</v>
-      </c>
-      <c r="D121" s="94" t="s">
-        <v>240</v>
-      </c>
-      <c r="E121" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F121" s="116">
-        <v>29.783000000000001</v>
-      </c>
-      <c r="G121" s="117">
-        <v>51.582999999999998</v>
-      </c>
-      <c r="H121" s="95">
-        <v>820</v>
+      <c r="C121" s="92">
+        <v>3</v>
+      </c>
+      <c r="D121" s="92" t="s">
+        <v>236</v>
+      </c>
+      <c r="E121" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" s="114">
+        <v>34.39</v>
+      </c>
+      <c r="G121" s="114">
+        <v>47.436999999999998</v>
+      </c>
+      <c r="H121" s="96">
+        <v>1290</v>
       </c>
       <c r="I121" s="96"/>
-      <c r="J121" s="97">
-        <v>1984</v>
-      </c>
-      <c r="K121" s="98">
-        <v>2000</v>
-      </c>
-      <c r="L121" s="98" t="s">
+      <c r="J121" s="96">
+        <v>1970</v>
+      </c>
+      <c r="K121" s="96">
+        <v>2009</v>
+      </c>
+      <c r="L121" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="M121" s="99" t="s">
-        <v>235</v>
+      <c r="M121" s="97" t="s">
+        <v>234</v>
       </c>
       <c r="N121" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="O121" s="100"/>
+        <v>84</v>
+      </c>
+      <c r="O121" s="98"/>
       <c r="P121" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="16">
-      <c r="A122" s="94" t="s">
+      <c r="A122" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B122" s="92" t="s">
         <v>232</v>
       </c>
-      <c r="B122" s="94" t="s">
-        <v>242</v>
-      </c>
-      <c r="C122" s="94">
-        <v>7</v>
-      </c>
-      <c r="D122" s="94" t="s">
-        <v>243</v>
-      </c>
-      <c r="E122" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F122" s="116">
-        <v>35.6</v>
-      </c>
-      <c r="G122" s="117">
-        <v>45.4</v>
-      </c>
-      <c r="H122" s="95">
-        <v>1625</v>
+      <c r="C122" s="92">
+        <v>4</v>
+      </c>
+      <c r="D122" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="E122" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F122" s="114">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="G122" s="114">
+        <v>50.215000000000003</v>
+      </c>
+      <c r="H122" s="96">
+        <v>2220</v>
       </c>
       <c r="I122" s="96"/>
-      <c r="J122" s="97">
-        <v>2002</v>
-      </c>
-      <c r="K122" s="98">
-        <v>2003</v>
-      </c>
-      <c r="L122" s="98" t="s">
-        <v>20</v>
-      </c>
-      <c r="M122" s="99" t="s">
-        <v>117</v>
+      <c r="J122" s="96">
+        <v>1998</v>
+      </c>
+      <c r="K122" s="96">
+        <v>2013</v>
+      </c>
+      <c r="L122" s="96" t="s">
+        <v>112</v>
+      </c>
+      <c r="M122" s="97" t="s">
+        <v>234</v>
       </c>
       <c r="N122" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O122" s="100"/>
-      <c r="P122" s="105" t="s">
-        <v>360</v>
+      <c r="O122" s="98"/>
+      <c r="P122" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="16">
-      <c r="A123" s="94" t="s">
+      <c r="A123" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B123" s="92" t="s">
         <v>232</v>
       </c>
-      <c r="B123" s="94" t="s">
-        <v>242</v>
-      </c>
-      <c r="C123" s="94">
-        <v>8</v>
-      </c>
-      <c r="D123" s="94" t="s">
-        <v>244</v>
-      </c>
-      <c r="E123" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F123" s="116">
-        <v>35.380000000000003</v>
-      </c>
-      <c r="G123" s="117">
-        <v>45.83</v>
-      </c>
-      <c r="H123" s="95">
-        <v>515</v>
-      </c>
-      <c r="I123" s="96"/>
-      <c r="J123" s="97">
-        <v>2004</v>
-      </c>
-      <c r="K123" s="98">
-        <v>2006</v>
-      </c>
-      <c r="L123" s="98" t="s">
-        <v>20</v>
-      </c>
-      <c r="M123" s="99" t="s">
-        <v>117</v>
+      <c r="C123" s="92">
+        <v>5</v>
+      </c>
+      <c r="D123" s="92" t="s">
+        <v>238</v>
+      </c>
+      <c r="E123" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" s="114">
+        <v>32.216999999999999</v>
+      </c>
+      <c r="G123" s="114">
+        <v>50.543999999999997</v>
+      </c>
+      <c r="H123" s="96">
+        <v>2016</v>
+      </c>
+      <c r="I123" s="94"/>
+      <c r="J123" s="96">
+        <v>1998</v>
+      </c>
+      <c r="K123" s="96">
+        <v>2014</v>
+      </c>
+      <c r="L123" s="96" t="s">
+        <v>112</v>
+      </c>
+      <c r="M123" s="97" t="s">
+        <v>234</v>
       </c>
       <c r="N123" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O123" s="100"/>
-      <c r="P123" s="104" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="14">
-      <c r="D124" s="101"/>
-    </row>
-    <row r="125" spans="1:16" ht="14">
-      <c r="D125" s="102"/>
-      <c r="E125" s="103"/>
-      <c r="F125" s="102"/>
-      <c r="G125" s="103"/>
-      <c r="H125" s="103"/>
-      <c r="I125" s="103"/>
-      <c r="J125" s="103"/>
-      <c r="K125" s="102"/>
-      <c r="L125" s="102"/>
-      <c r="M125" s="103"/>
-      <c r="N125" s="102"/>
+      <c r="O123" s="98"/>
+      <c r="P123" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="16">
+      <c r="A124" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B124" s="92" t="s">
+        <v>232</v>
+      </c>
+      <c r="C124" s="92">
+        <v>6</v>
+      </c>
+      <c r="D124" s="92" t="s">
+        <v>239</v>
+      </c>
+      <c r="E124" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F124" s="114">
+        <v>29.783000000000001</v>
+      </c>
+      <c r="G124" s="115">
+        <v>51.582999999999998</v>
+      </c>
+      <c r="H124" s="93">
+        <v>820</v>
+      </c>
+      <c r="I124" s="94"/>
+      <c r="J124" s="95">
+        <v>1984</v>
+      </c>
+      <c r="K124" s="96">
+        <v>2000</v>
+      </c>
+      <c r="L124" s="96" t="s">
+        <v>112</v>
+      </c>
+      <c r="M124" s="97" t="s">
+        <v>234</v>
+      </c>
+      <c r="N124" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="O124" s="98"/>
+      <c r="P124" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="16">
+      <c r="A125" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B125" s="92" t="s">
+        <v>241</v>
+      </c>
+      <c r="C125" s="92">
+        <v>7</v>
+      </c>
+      <c r="D125" s="92" t="s">
+        <v>242</v>
+      </c>
+      <c r="E125" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F125" s="114">
+        <v>35.6</v>
+      </c>
+      <c r="G125" s="115">
+        <v>45.4</v>
+      </c>
+      <c r="H125" s="93">
+        <v>1625</v>
+      </c>
+      <c r="I125" s="94"/>
+      <c r="J125" s="95">
+        <v>2002</v>
+      </c>
+      <c r="K125" s="96">
+        <v>2003</v>
+      </c>
+      <c r="L125" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M125" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="N125" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O125" s="98"/>
+      <c r="P125" s="103" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="16">
+      <c r="A126" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B126" s="92" t="s">
+        <v>241</v>
+      </c>
+      <c r="C126" s="92">
+        <v>8</v>
+      </c>
+      <c r="D126" s="92" t="s">
+        <v>243</v>
+      </c>
+      <c r="E126" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" s="114">
+        <v>35.380000000000003</v>
+      </c>
+      <c r="G126" s="115">
+        <v>45.83</v>
+      </c>
+      <c r="H126" s="93">
+        <v>515</v>
+      </c>
+      <c r="I126" s="94"/>
+      <c r="J126" s="95">
+        <v>2004</v>
+      </c>
+      <c r="K126" s="96">
+        <v>2006</v>
+      </c>
+      <c r="L126" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M126" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="N126" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O126" s="98"/>
+      <c r="P126" s="102" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="14">
+      <c r="D127" s="99"/>
+    </row>
+    <row r="128" spans="1:16" ht="14">
+      <c r="D128" s="100"/>
+      <c r="E128" s="101"/>
+      <c r="F128" s="100"/>
+      <c r="G128" s="101"/>
+      <c r="H128" s="101"/>
+      <c r="I128" s="101"/>
+      <c r="J128" s="101"/>
+      <c r="K128" s="100"/>
+      <c r="L128" s="100"/>
+      <c r="M128" s="101"/>
+      <c r="N128" s="100"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M115" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M114" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="M113" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="M111" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="M110" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="M106" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M92" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="M91" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="M90" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="M89" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="M88" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="M87" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="M86" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="M85" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="M84" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="M83" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="M82" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M118" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M117" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M116" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M114" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M113" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M109" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M95" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M94" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="M93" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M92" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="M91" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M90" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="M89" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M88" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="M87" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M86" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M85" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="M77" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="M76" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
     <hyperlink ref="M74" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>

--- a/Kameraman_metadata.xlsx
+++ b/Kameraman_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/selimcalli/Documents/onemli belgeler/04-PROJELER/EU PROJECT/02_DATA/Mediterranean/00_ALL_SPRING_LIST/02_discharge_edited/01_Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085E5FCA-463B-4E41-AB36-810BE931ABCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9790331-F8FD-3647-8285-5303E56910EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="384">
   <si>
     <t>Region</t>
   </si>
@@ -1410,6 +1410,12 @@
   </si>
   <si>
     <t>CAR_15_RO</t>
+  </si>
+  <si>
+    <t>Fontmaure</t>
+  </si>
+  <si>
+    <t>eaufrance hydroportail (from Bernard Ladouche, JC Marechal, V Bailly-Comte)</t>
   </si>
 </sst>
 </file>
@@ -2396,7 +2402,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P128"/>
+  <dimension ref="A1:P129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -7699,53 +7705,49 @@
       </c>
     </row>
     <row r="113" spans="1:16" ht="16">
-      <c r="A113" s="85" t="s">
-        <v>217</v>
-      </c>
-      <c r="B113" s="85" t="s">
-        <v>218</v>
-      </c>
-      <c r="C113" s="85">
-        <v>1</v>
-      </c>
-      <c r="D113" s="85" t="s">
-        <v>219</v>
-      </c>
-      <c r="E113" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F113" s="113">
-        <v>37.113</v>
-      </c>
-      <c r="G113" s="113">
-        <v>32.140999999999998</v>
-      </c>
-      <c r="H113" s="86">
-        <v>1100</v>
-      </c>
-      <c r="I113" s="87">
-        <v>85</v>
-      </c>
-      <c r="J113" s="88">
-        <v>2003</v>
-      </c>
-      <c r="K113" s="87">
-        <v>2019</v>
-      </c>
-      <c r="L113" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="M113" s="89" t="s">
-        <v>220</v>
+      <c r="A113" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B113" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C113" s="79">
+        <v>5</v>
+      </c>
+      <c r="D113" s="79" t="s">
+        <v>382</v>
+      </c>
+      <c r="E113" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" s="80">
+        <v>42.843000000000004</v>
+      </c>
+      <c r="G113" s="80">
+        <v>2.2029999999999998</v>
+      </c>
+      <c r="H113" s="81">
+        <v>317</v>
+      </c>
+      <c r="I113" s="82"/>
+      <c r="J113" s="83">
+        <v>2010</v>
+      </c>
+      <c r="K113" s="12">
+        <v>2026</v>
+      </c>
+      <c r="L113" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M113" s="67" t="s">
+        <v>383</v>
       </c>
       <c r="N113" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="O113" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="P113" t="s">
-        <v>328</v>
+        <v>84</v>
+      </c>
+      <c r="O113" s="17"/>
+      <c r="P113" s="102" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="16">
@@ -7756,36 +7758,36 @@
         <v>218</v>
       </c>
       <c r="C114" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" s="85" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E114" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F114" s="113">
-        <v>37.094000000000001</v>
+        <v>37.113</v>
       </c>
       <c r="G114" s="113">
-        <v>30.581</v>
-      </c>
-      <c r="H114" s="87">
-        <v>300</v>
+        <v>32.140999999999998</v>
+      </c>
+      <c r="H114" s="86">
+        <v>1100</v>
       </c>
       <c r="I114" s="87">
-        <v>2000</v>
-      </c>
-      <c r="J114" s="87">
+        <v>85</v>
+      </c>
+      <c r="J114" s="88">
         <v>2003</v>
       </c>
       <c r="K114" s="87">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="L114" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M114" s="90" t="s">
+      <c r="M114" s="89" t="s">
         <v>220</v>
       </c>
       <c r="N114" s="20" t="s">
@@ -7795,7 +7797,7 @@
         <v>221</v>
       </c>
       <c r="P114" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="16">
@@ -7806,44 +7808,46 @@
         <v>218</v>
       </c>
       <c r="C115" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115" s="85" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E115" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F115" s="113">
-        <v>37.302</v>
+        <v>37.094000000000001</v>
       </c>
       <c r="G115" s="113">
-        <v>31.942</v>
+        <v>30.581</v>
       </c>
       <c r="H115" s="87">
-        <v>1099</v>
+        <v>300</v>
       </c>
       <c r="I115" s="87">
-        <v>70</v>
+        <v>2000</v>
       </c>
       <c r="J115" s="87">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="K115" s="87">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="L115" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M115" s="85" t="s">
-        <v>224</v>
+      <c r="M115" s="90" t="s">
+        <v>220</v>
       </c>
       <c r="N115" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="O115" s="17"/>
+      <c r="O115" s="17" t="s">
+        <v>221</v>
+      </c>
       <c r="P115" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="16">
@@ -7854,46 +7858,44 @@
         <v>218</v>
       </c>
       <c r="C116" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D116" s="85" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E116" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F116" s="113">
-        <v>37.468000000000004</v>
+        <v>37.302</v>
       </c>
       <c r="G116" s="113">
-        <v>34.863</v>
+        <v>31.942</v>
       </c>
       <c r="H116" s="87">
-        <v>840</v>
+        <v>1099</v>
       </c>
       <c r="I116" s="87">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="J116" s="87">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="K116" s="87">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L116" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M116" s="91" t="s">
-        <v>226</v>
+      <c r="M116" s="85" t="s">
+        <v>224</v>
       </c>
       <c r="N116" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="O116" s="17" t="s">
-        <v>221</v>
-      </c>
+      <c r="O116" s="17"/>
       <c r="P116" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="16">
@@ -7904,37 +7906,37 @@
         <v>218</v>
       </c>
       <c r="C117" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D117" s="85" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E117" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F117" s="113">
-        <v>37.771000000000001</v>
+        <v>37.468000000000004</v>
       </c>
       <c r="G117" s="113">
-        <v>35.396000000000001</v>
+        <v>34.863</v>
       </c>
       <c r="H117" s="87">
-        <v>660</v>
+        <v>840</v>
       </c>
       <c r="I117" s="87">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="J117" s="87">
         <v>2011</v>
       </c>
       <c r="K117" s="87">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="L117" s="87" t="s">
         <v>20</v>
       </c>
       <c r="M117" s="91" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N117" s="20" t="s">
         <v>147</v>
@@ -7943,7 +7945,7 @@
         <v>221</v>
       </c>
       <c r="P117" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="16">
@@ -7954,37 +7956,37 @@
         <v>218</v>
       </c>
       <c r="C118" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118" s="85" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E118" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F118" s="113">
-        <v>38.814999999999998</v>
+        <v>37.771000000000001</v>
       </c>
       <c r="G118" s="113">
-        <v>35.863999999999997</v>
+        <v>35.396000000000001</v>
       </c>
       <c r="H118" s="87">
-        <v>1536</v>
+        <v>660</v>
       </c>
       <c r="I118" s="87">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="J118" s="87">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="K118" s="87">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="L118" s="87" t="s">
         <v>20</v>
       </c>
       <c r="M118" s="91" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N118" s="20" t="s">
         <v>147</v>
@@ -7993,51 +7995,57 @@
         <v>221</v>
       </c>
       <c r="P118" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="16">
+      <c r="A119" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B119" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C119" s="85">
+        <v>6</v>
+      </c>
+      <c r="D119" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="E119" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" s="113">
+        <v>38.814999999999998</v>
+      </c>
+      <c r="G119" s="113">
+        <v>35.863999999999997</v>
+      </c>
+      <c r="H119" s="87">
+        <v>1536</v>
+      </c>
+      <c r="I119" s="87">
+        <v>10</v>
+      </c>
+      <c r="J119" s="87">
+        <v>2002</v>
+      </c>
+      <c r="K119" s="87">
+        <v>2019</v>
+      </c>
+      <c r="L119" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M119" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="N119" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O119" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P119" t="s">
         <v>333</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="16">
-      <c r="A119" s="92" t="s">
-        <v>231</v>
-      </c>
-      <c r="B119" s="92" t="s">
-        <v>232</v>
-      </c>
-      <c r="C119" s="92">
-        <v>1</v>
-      </c>
-      <c r="D119" s="92" t="s">
-        <v>233</v>
-      </c>
-      <c r="E119" s="92"/>
-      <c r="F119" s="114">
-        <v>31.375</v>
-      </c>
-      <c r="G119" s="115">
-        <v>49.84</v>
-      </c>
-      <c r="H119" s="93">
-        <v>490</v>
-      </c>
-      <c r="I119" s="94"/>
-      <c r="J119" s="95">
-        <v>2003</v>
-      </c>
-      <c r="K119" s="96">
-        <v>2011</v>
-      </c>
-      <c r="L119" s="96" t="s">
-        <v>20</v>
-      </c>
-      <c r="M119" s="97" t="s">
-        <v>234</v>
-      </c>
-      <c r="N119" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O119" s="17"/>
-      <c r="P119" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="16">
@@ -8048,27 +8056,27 @@
         <v>232</v>
       </c>
       <c r="C120" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" s="92" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E120" s="92"/>
       <c r="F120" s="114">
-        <v>31.256</v>
+        <v>31.375</v>
       </c>
       <c r="G120" s="115">
-        <v>49.968000000000004</v>
+        <v>49.84</v>
       </c>
       <c r="H120" s="93">
-        <v>675</v>
+        <v>490</v>
       </c>
       <c r="I120" s="94"/>
       <c r="J120" s="95">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="K120" s="96">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="L120" s="96" t="s">
         <v>20</v>
@@ -8081,7 +8089,7 @@
       </c>
       <c r="O120" s="17"/>
       <c r="P120" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="16">
@@ -8092,32 +8100,30 @@
         <v>232</v>
       </c>
       <c r="C121" s="92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="E121" s="92" t="s">
-        <v>19</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="E121" s="92"/>
       <c r="F121" s="114">
-        <v>34.39</v>
-      </c>
-      <c r="G121" s="114">
-        <v>47.436999999999998</v>
-      </c>
-      <c r="H121" s="96">
-        <v>1290</v>
-      </c>
-      <c r="I121" s="96"/>
-      <c r="J121" s="96">
-        <v>1970</v>
+        <v>31.256</v>
+      </c>
+      <c r="G121" s="115">
+        <v>49.968000000000004</v>
+      </c>
+      <c r="H121" s="93">
+        <v>675</v>
+      </c>
+      <c r="I121" s="94"/>
+      <c r="J121" s="95">
+        <v>2010</v>
       </c>
       <c r="K121" s="96">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="L121" s="96" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="M121" s="97" t="s">
         <v>234</v>
@@ -8125,9 +8131,9 @@
       <c r="N121" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O121" s="98"/>
+      <c r="O121" s="17"/>
       <c r="P121" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="16">
@@ -8138,29 +8144,29 @@
         <v>232</v>
       </c>
       <c r="C122" s="92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D122" s="92" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E122" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F122" s="114">
-        <v>32.500999999999998</v>
+        <v>34.39</v>
       </c>
       <c r="G122" s="114">
-        <v>50.215000000000003</v>
+        <v>47.436999999999998</v>
       </c>
       <c r="H122" s="96">
-        <v>2220</v>
+        <v>1290</v>
       </c>
       <c r="I122" s="96"/>
       <c r="J122" s="96">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="K122" s="96">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="L122" s="96" t="s">
         <v>112</v>
@@ -8173,7 +8179,7 @@
       </c>
       <c r="O122" s="98"/>
       <c r="P122" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="16">
@@ -8184,29 +8190,29 @@
         <v>232</v>
       </c>
       <c r="C123" s="92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D123" s="92" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E123" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F123" s="114">
-        <v>32.216999999999999</v>
+        <v>32.500999999999998</v>
       </c>
       <c r="G123" s="114">
-        <v>50.543999999999997</v>
+        <v>50.215000000000003</v>
       </c>
       <c r="H123" s="96">
-        <v>2016</v>
-      </c>
-      <c r="I123" s="94"/>
+        <v>2220</v>
+      </c>
+      <c r="I123" s="96"/>
       <c r="J123" s="96">
         <v>1998</v>
       </c>
       <c r="K123" s="96">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="L123" s="96" t="s">
         <v>112</v>
@@ -8219,7 +8225,7 @@
       </c>
       <c r="O123" s="98"/>
       <c r="P123" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="16">
@@ -8230,29 +8236,29 @@
         <v>232</v>
       </c>
       <c r="C124" s="92">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D124" s="92" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E124" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F124" s="114">
-        <v>29.783000000000001</v>
-      </c>
-      <c r="G124" s="115">
-        <v>51.582999999999998</v>
-      </c>
-      <c r="H124" s="93">
-        <v>820</v>
+        <v>32.216999999999999</v>
+      </c>
+      <c r="G124" s="114">
+        <v>50.543999999999997</v>
+      </c>
+      <c r="H124" s="96">
+        <v>2016</v>
       </c>
       <c r="I124" s="94"/>
-      <c r="J124" s="95">
-        <v>1984</v>
+      <c r="J124" s="96">
+        <v>1998</v>
       </c>
       <c r="K124" s="96">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="L124" s="96" t="s">
         <v>112</v>
@@ -8261,11 +8267,11 @@
         <v>234</v>
       </c>
       <c r="N124" s="20" t="s">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="O124" s="98"/>
       <c r="P124" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="125" spans="1:16" ht="16">
@@ -8273,45 +8279,45 @@
         <v>231</v>
       </c>
       <c r="B125" s="92" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C125" s="92">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D125" s="92" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E125" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F125" s="114">
-        <v>35.6</v>
+        <v>29.783000000000001</v>
       </c>
       <c r="G125" s="115">
-        <v>45.4</v>
+        <v>51.582999999999998</v>
       </c>
       <c r="H125" s="93">
-        <v>1625</v>
+        <v>820</v>
       </c>
       <c r="I125" s="94"/>
       <c r="J125" s="95">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="K125" s="96">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="L125" s="96" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="M125" s="97" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="N125" s="20" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="O125" s="98"/>
-      <c r="P125" s="103" t="s">
-        <v>359</v>
+      <c r="P125" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="16">
@@ -8322,29 +8328,29 @@
         <v>241</v>
       </c>
       <c r="C126" s="92">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D126" s="92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E126" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="114">
-        <v>35.380000000000003</v>
+        <v>35.6</v>
       </c>
       <c r="G126" s="115">
-        <v>45.83</v>
+        <v>45.4</v>
       </c>
       <c r="H126" s="93">
-        <v>515</v>
+        <v>1625</v>
       </c>
       <c r="I126" s="94"/>
       <c r="J126" s="95">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="K126" s="96">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="L126" s="96" t="s">
         <v>20</v>
@@ -8356,33 +8362,79 @@
         <v>84</v>
       </c>
       <c r="O126" s="98"/>
-      <c r="P126" s="102" t="s">
+      <c r="P126" s="103" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="16">
+      <c r="A127" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B127" s="92" t="s">
+        <v>241</v>
+      </c>
+      <c r="C127" s="92">
+        <v>8</v>
+      </c>
+      <c r="D127" s="92" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F127" s="114">
+        <v>35.380000000000003</v>
+      </c>
+      <c r="G127" s="115">
+        <v>45.83</v>
+      </c>
+      <c r="H127" s="93">
+        <v>515</v>
+      </c>
+      <c r="I127" s="94"/>
+      <c r="J127" s="95">
+        <v>2004</v>
+      </c>
+      <c r="K127" s="96">
+        <v>2006</v>
+      </c>
+      <c r="L127" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M127" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="N127" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O127" s="98"/>
+      <c r="P127" s="102" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="14">
-      <c r="D127" s="99"/>
-    </row>
     <row r="128" spans="1:16" ht="14">
-      <c r="D128" s="100"/>
-      <c r="E128" s="101"/>
-      <c r="F128" s="100"/>
-      <c r="G128" s="101"/>
-      <c r="H128" s="101"/>
-      <c r="I128" s="101"/>
-      <c r="J128" s="101"/>
-      <c r="K128" s="100"/>
-      <c r="L128" s="100"/>
-      <c r="M128" s="101"/>
-      <c r="N128" s="100"/>
+      <c r="D128" s="99"/>
+    </row>
+    <row r="129" spans="4:14" ht="14">
+      <c r="D129" s="100"/>
+      <c r="E129" s="101"/>
+      <c r="F129" s="100"/>
+      <c r="G129" s="101"/>
+      <c r="H129" s="101"/>
+      <c r="I129" s="101"/>
+      <c r="J129" s="101"/>
+      <c r="K129" s="100"/>
+      <c r="L129" s="100"/>
+      <c r="M129" s="101"/>
+      <c r="N129" s="100"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M118" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M117" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="M116" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="M114" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="M113" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M119" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M118" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M117" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M115" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M114" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="M109" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="M95" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="M94" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>

--- a/Kameraman_metadata.xlsx
+++ b/Kameraman_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/selimcalli/Documents/onemli belgeler/04-PROJELER/EU PROJECT/02_DATA/Mediterranean/00_ALL_SPRING_LIST/02_discharge_edited/01_Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9790331-F8FD-3647-8285-5303E56910EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A673F54F-BD93-B841-B1C9-F1A6C92CD72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="386">
   <si>
     <t>Region</t>
   </si>
@@ -1416,6 +1416,12 @@
   </si>
   <si>
     <t>eaufrance hydroportail (from Bernard Ladouche, JC Marechal, V Bailly-Comte)</t>
+  </si>
+  <si>
+    <t>Arbas</t>
+  </si>
+  <si>
+    <t>Plan de Pouts</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1905,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2183,6 +2189,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2402,7 +2411,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P129"/>
+  <dimension ref="A1:P131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -7535,8 +7544,8 @@
       <c r="H109" s="81">
         <v>2000</v>
       </c>
-      <c r="I109" s="82">
-        <v>14.483000000000001</v>
+      <c r="I109" s="139">
+        <v>14483</v>
       </c>
       <c r="J109" s="83">
         <v>2018</v>
@@ -7589,10 +7598,10 @@
         <v>125</v>
       </c>
       <c r="J110" s="83">
-        <v>2019</v>
+        <v>1965</v>
       </c>
       <c r="K110" s="12">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="L110" s="12" t="s">
         <v>20</v>
@@ -7637,10 +7646,10 @@
         <v>13</v>
       </c>
       <c r="J111" s="83">
-        <v>2020</v>
+        <v>1968</v>
       </c>
       <c r="K111" s="12">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="L111" s="12" t="s">
         <v>20</v>
@@ -7685,10 +7694,10 @@
         <v>11</v>
       </c>
       <c r="J112" s="83">
-        <v>2009</v>
+        <v>1969</v>
       </c>
       <c r="K112" s="12">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="L112" s="12" t="s">
         <v>20</v>
@@ -7731,7 +7740,7 @@
       </c>
       <c r="I113" s="82"/>
       <c r="J113" s="83">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="K113" s="12">
         <v>2026</v>
@@ -7751,103 +7760,93 @@
       </c>
     </row>
     <row r="114" spans="1:16" ht="16">
-      <c r="A114" s="85" t="s">
-        <v>217</v>
-      </c>
-      <c r="B114" s="85" t="s">
-        <v>218</v>
-      </c>
-      <c r="C114" s="85">
-        <v>1</v>
-      </c>
-      <c r="D114" s="85" t="s">
-        <v>219</v>
-      </c>
-      <c r="E114" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F114" s="113">
-        <v>37.113</v>
-      </c>
-      <c r="G114" s="113">
-        <v>32.140999999999998</v>
-      </c>
-      <c r="H114" s="86">
-        <v>1100</v>
-      </c>
-      <c r="I114" s="87">
-        <v>85</v>
-      </c>
-      <c r="J114" s="88">
-        <v>2003</v>
-      </c>
-      <c r="K114" s="87">
-        <v>2019</v>
-      </c>
-      <c r="L114" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="M114" s="89" t="s">
-        <v>220</v>
+      <c r="A114" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B114" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C114" s="79">
+        <v>6</v>
+      </c>
+      <c r="D114" s="79" t="s">
+        <v>384</v>
+      </c>
+      <c r="E114" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" s="80">
+        <v>42.984000000000002</v>
+      </c>
+      <c r="G114" s="80">
+        <v>0.9</v>
+      </c>
+      <c r="H114" s="81">
+        <v>435</v>
+      </c>
+      <c r="I114" s="82"/>
+      <c r="J114" s="83">
+        <v>2002</v>
+      </c>
+      <c r="K114" s="12">
+        <v>2026</v>
+      </c>
+      <c r="L114" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M114" s="67" t="s">
+        <v>215</v>
       </c>
       <c r="N114" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="O114" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="P114" t="s">
-        <v>328</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="O114" s="17"/>
+      <c r="P114" s="102"/>
     </row>
     <row r="115" spans="1:16" ht="16">
-      <c r="A115" s="85" t="s">
-        <v>217</v>
-      </c>
-      <c r="B115" s="85" t="s">
-        <v>218</v>
-      </c>
-      <c r="C115" s="85">
-        <v>2</v>
-      </c>
-      <c r="D115" s="85" t="s">
-        <v>222</v>
-      </c>
-      <c r="E115" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F115" s="113">
-        <v>37.094000000000001</v>
-      </c>
-      <c r="G115" s="113">
-        <v>30.581</v>
-      </c>
-      <c r="H115" s="87">
-        <v>300</v>
-      </c>
-      <c r="I115" s="87">
-        <v>2000</v>
-      </c>
-      <c r="J115" s="87">
-        <v>2003</v>
-      </c>
-      <c r="K115" s="87">
-        <v>2017</v>
-      </c>
-      <c r="L115" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="M115" s="90" t="s">
-        <v>220</v>
+      <c r="A115" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B115" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C115" s="79">
+        <v>7</v>
+      </c>
+      <c r="D115" s="79" t="s">
+        <v>385</v>
+      </c>
+      <c r="E115" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" s="80">
+        <v>43.031999999999996</v>
+      </c>
+      <c r="G115" s="80">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="H115" s="81">
+        <v>525</v>
+      </c>
+      <c r="I115" s="82"/>
+      <c r="J115" s="83">
+        <v>2002</v>
+      </c>
+      <c r="K115" s="12">
+        <v>2026</v>
+      </c>
+      <c r="L115" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M115" s="67" t="s">
+        <v>215</v>
       </c>
       <c r="N115" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="O115" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="P115" t="s">
-        <v>329</v>
+        <v>84</v>
+      </c>
+      <c r="O115" s="17"/>
+      <c r="P115" s="102" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="16">
@@ -7858,44 +7857,46 @@
         <v>218</v>
       </c>
       <c r="C116" s="85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116" s="85" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E116" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F116" s="113">
-        <v>37.302</v>
+        <v>37.113</v>
       </c>
       <c r="G116" s="113">
-        <v>31.942</v>
-      </c>
-      <c r="H116" s="87">
-        <v>1099</v>
+        <v>32.140999999999998</v>
+      </c>
+      <c r="H116" s="86">
+        <v>1100</v>
       </c>
       <c r="I116" s="87">
-        <v>70</v>
-      </c>
-      <c r="J116" s="87">
-        <v>2014</v>
+        <v>85</v>
+      </c>
+      <c r="J116" s="88">
+        <v>2003</v>
       </c>
       <c r="K116" s="87">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="L116" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M116" s="85" t="s">
-        <v>224</v>
+      <c r="M116" s="89" t="s">
+        <v>220</v>
       </c>
       <c r="N116" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="O116" s="17"/>
+      <c r="O116" s="17" t="s">
+        <v>221</v>
+      </c>
       <c r="P116" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="16">
@@ -7906,37 +7907,37 @@
         <v>218</v>
       </c>
       <c r="C117" s="85">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D117" s="85" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E117" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F117" s="113">
-        <v>37.468000000000004</v>
+        <v>37.094000000000001</v>
       </c>
       <c r="G117" s="113">
-        <v>34.863</v>
+        <v>30.581</v>
       </c>
       <c r="H117" s="87">
-        <v>840</v>
+        <v>300</v>
       </c>
       <c r="I117" s="87">
-        <v>140</v>
+        <v>2000</v>
       </c>
       <c r="J117" s="87">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="K117" s="87">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="L117" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M117" s="91" t="s">
-        <v>226</v>
+      <c r="M117" s="90" t="s">
+        <v>220</v>
       </c>
       <c r="N117" s="20" t="s">
         <v>147</v>
@@ -7945,7 +7946,7 @@
         <v>221</v>
       </c>
       <c r="P117" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="16">
@@ -7956,46 +7957,44 @@
         <v>218</v>
       </c>
       <c r="C118" s="85">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D118" s="85" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E118" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F118" s="113">
-        <v>37.771000000000001</v>
+        <v>37.302</v>
       </c>
       <c r="G118" s="113">
-        <v>35.396000000000001</v>
+        <v>31.942</v>
       </c>
       <c r="H118" s="87">
-        <v>660</v>
+        <v>1099</v>
       </c>
       <c r="I118" s="87">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="J118" s="87">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="K118" s="87">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="L118" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M118" s="91" t="s">
-        <v>228</v>
+      <c r="M118" s="85" t="s">
+        <v>224</v>
       </c>
       <c r="N118" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="O118" s="17" t="s">
-        <v>221</v>
-      </c>
+      <c r="O118" s="17"/>
       <c r="P118" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="16">
@@ -8006,37 +8005,37 @@
         <v>218</v>
       </c>
       <c r="C119" s="85">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D119" s="85" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E119" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F119" s="113">
-        <v>38.814999999999998</v>
+        <v>37.468000000000004</v>
       </c>
       <c r="G119" s="113">
-        <v>35.863999999999997</v>
+        <v>34.863</v>
       </c>
       <c r="H119" s="87">
-        <v>1536</v>
+        <v>840</v>
       </c>
       <c r="I119" s="87">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="J119" s="87">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="K119" s="87">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="L119" s="87" t="s">
         <v>20</v>
       </c>
       <c r="M119" s="91" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="N119" s="20" t="s">
         <v>147</v>
@@ -8045,95 +8044,107 @@
         <v>221</v>
       </c>
       <c r="P119" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="16">
+      <c r="A120" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B120" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C120" s="85">
+        <v>5</v>
+      </c>
+      <c r="D120" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="E120" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120" s="113">
+        <v>37.771000000000001</v>
+      </c>
+      <c r="G120" s="113">
+        <v>35.396000000000001</v>
+      </c>
+      <c r="H120" s="87">
+        <v>660</v>
+      </c>
+      <c r="I120" s="87">
+        <v>350</v>
+      </c>
+      <c r="J120" s="87">
+        <v>2011</v>
+      </c>
+      <c r="K120" s="87">
+        <v>2017</v>
+      </c>
+      <c r="L120" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M120" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="N120" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O120" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P120" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="16">
+      <c r="A121" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B121" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C121" s="85">
+        <v>6</v>
+      </c>
+      <c r="D121" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="E121" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" s="113">
+        <v>38.814999999999998</v>
+      </c>
+      <c r="G121" s="113">
+        <v>35.863999999999997</v>
+      </c>
+      <c r="H121" s="87">
+        <v>1536</v>
+      </c>
+      <c r="I121" s="87">
+        <v>10</v>
+      </c>
+      <c r="J121" s="87">
+        <v>2002</v>
+      </c>
+      <c r="K121" s="87">
+        <v>2019</v>
+      </c>
+      <c r="L121" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M121" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="N121" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O121" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P121" t="s">
         <v>333</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="16">
-      <c r="A120" s="92" t="s">
-        <v>231</v>
-      </c>
-      <c r="B120" s="92" t="s">
-        <v>232</v>
-      </c>
-      <c r="C120" s="92">
-        <v>1</v>
-      </c>
-      <c r="D120" s="92" t="s">
-        <v>233</v>
-      </c>
-      <c r="E120" s="92"/>
-      <c r="F120" s="114">
-        <v>31.375</v>
-      </c>
-      <c r="G120" s="115">
-        <v>49.84</v>
-      </c>
-      <c r="H120" s="93">
-        <v>490</v>
-      </c>
-      <c r="I120" s="94"/>
-      <c r="J120" s="95">
-        <v>2003</v>
-      </c>
-      <c r="K120" s="96">
-        <v>2011</v>
-      </c>
-      <c r="L120" s="96" t="s">
-        <v>20</v>
-      </c>
-      <c r="M120" s="97" t="s">
-        <v>234</v>
-      </c>
-      <c r="N120" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O120" s="17"/>
-      <c r="P120" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="16">
-      <c r="A121" s="92" t="s">
-        <v>231</v>
-      </c>
-      <c r="B121" s="92" t="s">
-        <v>232</v>
-      </c>
-      <c r="C121" s="92">
-        <v>2</v>
-      </c>
-      <c r="D121" s="92" t="s">
-        <v>235</v>
-      </c>
-      <c r="E121" s="92"/>
-      <c r="F121" s="114">
-        <v>31.256</v>
-      </c>
-      <c r="G121" s="115">
-        <v>49.968000000000004</v>
-      </c>
-      <c r="H121" s="93">
-        <v>675</v>
-      </c>
-      <c r="I121" s="94"/>
-      <c r="J121" s="95">
-        <v>2010</v>
-      </c>
-      <c r="K121" s="96">
-        <v>2017</v>
-      </c>
-      <c r="L121" s="96" t="s">
-        <v>20</v>
-      </c>
-      <c r="M121" s="97" t="s">
-        <v>234</v>
-      </c>
-      <c r="N121" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O121" s="17"/>
-      <c r="P121" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="16">
@@ -8144,32 +8155,30 @@
         <v>232</v>
       </c>
       <c r="C122" s="92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="E122" s="92" t="s">
-        <v>19</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="E122" s="92"/>
       <c r="F122" s="114">
-        <v>34.39</v>
-      </c>
-      <c r="G122" s="114">
-        <v>47.436999999999998</v>
-      </c>
-      <c r="H122" s="96">
-        <v>1290</v>
-      </c>
-      <c r="I122" s="96"/>
-      <c r="J122" s="96">
-        <v>1970</v>
+        <v>31.375</v>
+      </c>
+      <c r="G122" s="115">
+        <v>49.84</v>
+      </c>
+      <c r="H122" s="93">
+        <v>490</v>
+      </c>
+      <c r="I122" s="94"/>
+      <c r="J122" s="95">
+        <v>2003</v>
       </c>
       <c r="K122" s="96">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="L122" s="96" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="M122" s="97" t="s">
         <v>234</v>
@@ -8177,9 +8186,9 @@
       <c r="N122" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O122" s="98"/>
+      <c r="O122" s="17"/>
       <c r="P122" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="16">
@@ -8190,32 +8199,30 @@
         <v>232</v>
       </c>
       <c r="C123" s="92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D123" s="92" t="s">
-        <v>237</v>
-      </c>
-      <c r="E123" s="92" t="s">
-        <v>19</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="E123" s="92"/>
       <c r="F123" s="114">
-        <v>32.500999999999998</v>
-      </c>
-      <c r="G123" s="114">
-        <v>50.215000000000003</v>
-      </c>
-      <c r="H123" s="96">
-        <v>2220</v>
-      </c>
-      <c r="I123" s="96"/>
-      <c r="J123" s="96">
-        <v>1998</v>
+        <v>31.256</v>
+      </c>
+      <c r="G123" s="115">
+        <v>49.968000000000004</v>
+      </c>
+      <c r="H123" s="93">
+        <v>675</v>
+      </c>
+      <c r="I123" s="94"/>
+      <c r="J123" s="95">
+        <v>2010</v>
       </c>
       <c r="K123" s="96">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="L123" s="96" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="M123" s="97" t="s">
         <v>234</v>
@@ -8223,9 +8230,9 @@
       <c r="N123" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O123" s="98"/>
+      <c r="O123" s="17"/>
       <c r="P123" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="16">
@@ -8236,29 +8243,29 @@
         <v>232</v>
       </c>
       <c r="C124" s="92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D124" s="92" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E124" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F124" s="114">
-        <v>32.216999999999999</v>
+        <v>34.39</v>
       </c>
       <c r="G124" s="114">
-        <v>50.543999999999997</v>
+        <v>47.436999999999998</v>
       </c>
       <c r="H124" s="96">
-        <v>2016</v>
-      </c>
-      <c r="I124" s="94"/>
+        <v>1290</v>
+      </c>
+      <c r="I124" s="96"/>
       <c r="J124" s="96">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="K124" s="96">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="L124" s="96" t="s">
         <v>112</v>
@@ -8271,7 +8278,7 @@
       </c>
       <c r="O124" s="98"/>
       <c r="P124" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="125" spans="1:16" ht="16">
@@ -8282,29 +8289,29 @@
         <v>232</v>
       </c>
       <c r="C125" s="92">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D125" s="92" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E125" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F125" s="114">
-        <v>29.783000000000001</v>
-      </c>
-      <c r="G125" s="115">
-        <v>51.582999999999998</v>
-      </c>
-      <c r="H125" s="93">
-        <v>820</v>
-      </c>
-      <c r="I125" s="94"/>
-      <c r="J125" s="95">
-        <v>1984</v>
+        <v>32.500999999999998</v>
+      </c>
+      <c r="G125" s="114">
+        <v>50.215000000000003</v>
+      </c>
+      <c r="H125" s="96">
+        <v>2220</v>
+      </c>
+      <c r="I125" s="96"/>
+      <c r="J125" s="96">
+        <v>1998</v>
       </c>
       <c r="K125" s="96">
-        <v>2000</v>
+        <v>2013</v>
       </c>
       <c r="L125" s="96" t="s">
         <v>112</v>
@@ -8313,11 +8320,11 @@
         <v>234</v>
       </c>
       <c r="N125" s="20" t="s">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="O125" s="98"/>
       <c r="P125" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="16">
@@ -8325,45 +8332,45 @@
         <v>231</v>
       </c>
       <c r="B126" s="92" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C126" s="92">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D126" s="92" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E126" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="114">
-        <v>35.6</v>
-      </c>
-      <c r="G126" s="115">
-        <v>45.4</v>
-      </c>
-      <c r="H126" s="93">
-        <v>1625</v>
+        <v>32.216999999999999</v>
+      </c>
+      <c r="G126" s="114">
+        <v>50.543999999999997</v>
+      </c>
+      <c r="H126" s="96">
+        <v>2016</v>
       </c>
       <c r="I126" s="94"/>
-      <c r="J126" s="95">
-        <v>2002</v>
+      <c r="J126" s="96">
+        <v>1998</v>
       </c>
       <c r="K126" s="96">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="L126" s="96" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="M126" s="97" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="N126" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O126" s="98"/>
-      <c r="P126" s="103" t="s">
-        <v>359</v>
+      <c r="P126" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="127" spans="1:16" ht="16">
@@ -8371,70 +8378,162 @@
         <v>231</v>
       </c>
       <c r="B127" s="92" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C127" s="92">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D127" s="92" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E127" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F127" s="114">
-        <v>35.380000000000003</v>
+        <v>29.783000000000001</v>
       </c>
       <c r="G127" s="115">
-        <v>45.83</v>
+        <v>51.582999999999998</v>
       </c>
       <c r="H127" s="93">
-        <v>515</v>
+        <v>820</v>
       </c>
       <c r="I127" s="94"/>
       <c r="J127" s="95">
+        <v>1984</v>
+      </c>
+      <c r="K127" s="96">
+        <v>2000</v>
+      </c>
+      <c r="L127" s="96" t="s">
+        <v>112</v>
+      </c>
+      <c r="M127" s="97" t="s">
+        <v>234</v>
+      </c>
+      <c r="N127" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="O127" s="98"/>
+      <c r="P127" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="16">
+      <c r="A128" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B128" s="92" t="s">
+        <v>241</v>
+      </c>
+      <c r="C128" s="92">
+        <v>7</v>
+      </c>
+      <c r="D128" s="92" t="s">
+        <v>242</v>
+      </c>
+      <c r="E128" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F128" s="114">
+        <v>35.6</v>
+      </c>
+      <c r="G128" s="115">
+        <v>45.4</v>
+      </c>
+      <c r="H128" s="93">
+        <v>1625</v>
+      </c>
+      <c r="I128" s="94"/>
+      <c r="J128" s="95">
+        <v>2002</v>
+      </c>
+      <c r="K128" s="96">
+        <v>2003</v>
+      </c>
+      <c r="L128" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M128" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="N128" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O128" s="98"/>
+      <c r="P128" s="103" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="16">
+      <c r="A129" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B129" s="92" t="s">
+        <v>241</v>
+      </c>
+      <c r="C129" s="92">
+        <v>8</v>
+      </c>
+      <c r="D129" s="92" t="s">
+        <v>243</v>
+      </c>
+      <c r="E129" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F129" s="114">
+        <v>35.380000000000003</v>
+      </c>
+      <c r="G129" s="115">
+        <v>45.83</v>
+      </c>
+      <c r="H129" s="93">
+        <v>515</v>
+      </c>
+      <c r="I129" s="94"/>
+      <c r="J129" s="95">
         <v>2004</v>
       </c>
-      <c r="K127" s="96">
+      <c r="K129" s="96">
         <v>2006</v>
       </c>
-      <c r="L127" s="96" t="s">
-        <v>20</v>
-      </c>
-      <c r="M127" s="97" t="s">
+      <c r="L129" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M129" s="97" t="s">
         <v>117</v>
       </c>
-      <c r="N127" s="20" t="s">
+      <c r="N129" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O127" s="98"/>
-      <c r="P127" s="102" t="s">
+      <c r="O129" s="98"/>
+      <c r="P129" s="102" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="14">
-      <c r="D128" s="99"/>
-    </row>
-    <row r="129" spans="4:14" ht="14">
-      <c r="D129" s="100"/>
-      <c r="E129" s="101"/>
-      <c r="F129" s="100"/>
-      <c r="G129" s="101"/>
-      <c r="H129" s="101"/>
-      <c r="I129" s="101"/>
-      <c r="J129" s="101"/>
-      <c r="K129" s="100"/>
-      <c r="L129" s="100"/>
-      <c r="M129" s="101"/>
-      <c r="N129" s="100"/>
+    <row r="130" spans="1:16" ht="14">
+      <c r="D130" s="99"/>
+    </row>
+    <row r="131" spans="1:16" ht="14">
+      <c r="D131" s="100"/>
+      <c r="E131" s="101"/>
+      <c r="F131" s="100"/>
+      <c r="G131" s="101"/>
+      <c r="H131" s="101"/>
+      <c r="I131" s="101"/>
+      <c r="J131" s="101"/>
+      <c r="K131" s="100"/>
+      <c r="L131" s="100"/>
+      <c r="M131" s="101"/>
+      <c r="N131" s="100"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M119" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M118" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="M117" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="M115" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="M114" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M121" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M120" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M119" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M117" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M116" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="M109" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="M95" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="M94" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>

--- a/Kameraman_metadata.xlsx
+++ b/Kameraman_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/selimcalli/Documents/onemli belgeler/04-PROJELER/EU PROJECT/02_DATA/Mediterranean/00_ALL_SPRING_LIST/02_discharge_edited/01_Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A673F54F-BD93-B841-B1C9-F1A6C92CD72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE09EBA-DD97-E74F-A2B2-DB99DD86D6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="389">
   <si>
     <t>Region</t>
   </si>
@@ -1422,6 +1422,15 @@
   </si>
   <si>
     <t>Plan de Pouts</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Stymfalia</t>
+  </si>
+  <si>
+    <t>Eleni Zagana</t>
   </si>
 </sst>
 </file>
@@ -2411,7 +2420,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P131"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -7234,49 +7243,49 @@
       </c>
     </row>
     <row r="103" spans="1:16" ht="16">
-      <c r="A103" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="B103" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="C103" s="53">
-        <v>1</v>
-      </c>
-      <c r="D103" s="53" t="s">
-        <v>198</v>
-      </c>
-      <c r="E103" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F103" s="109">
-        <v>33.613</v>
-      </c>
-      <c r="G103" s="109">
-        <v>36.146999999999998</v>
-      </c>
-      <c r="H103" s="54">
-        <v>887</v>
-      </c>
-      <c r="I103" s="76"/>
-      <c r="J103" s="56">
-        <v>1987</v>
-      </c>
-      <c r="K103" s="55">
-        <v>2005</v>
-      </c>
-      <c r="L103" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="M103" s="77" t="s">
-        <v>117</v>
+      <c r="A103" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="B103" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="C103" s="68">
+        <v>4</v>
+      </c>
+      <c r="D103" s="68" t="s">
+        <v>387</v>
+      </c>
+      <c r="E103" s="68" t="s">
+        <v>386</v>
+      </c>
+      <c r="F103" s="108">
+        <v>37.868000000000002</v>
+      </c>
+      <c r="G103" s="108">
+        <v>22.472999999999999</v>
+      </c>
+      <c r="H103" s="69">
+        <v>620</v>
+      </c>
+      <c r="I103" s="70"/>
+      <c r="J103" s="71">
+        <v>2016</v>
+      </c>
+      <c r="K103" s="70">
+        <v>2024</v>
+      </c>
+      <c r="L103" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M103" s="73" t="s">
+        <v>388</v>
       </c>
       <c r="N103" s="20" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="O103" s="17"/>
-      <c r="P103" t="s">
-        <v>321</v>
+      <c r="P103" s="102" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="16">
@@ -7287,22 +7296,22 @@
         <v>197</v>
       </c>
       <c r="C104" s="53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" s="53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E104" s="53" t="s">
         <v>19</v>
       </c>
       <c r="F104" s="109">
-        <v>33.618000000000002</v>
+        <v>33.613</v>
       </c>
       <c r="G104" s="109">
-        <v>36.180999999999997</v>
+        <v>36.146999999999998</v>
       </c>
       <c r="H104" s="54">
-        <v>853</v>
+        <v>887</v>
       </c>
       <c r="I104" s="76"/>
       <c r="J104" s="56">
@@ -7314,7 +7323,7 @@
       <c r="L104" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="M104" s="78" t="s">
+      <c r="M104" s="77" t="s">
         <v>117</v>
       </c>
       <c r="N104" s="20" t="s">
@@ -7322,7 +7331,7 @@
       </c>
       <c r="O104" s="17"/>
       <c r="P104" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="16">
@@ -7330,49 +7339,45 @@
         <v>196</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C105" s="53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D105" s="53" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E105" s="53" t="s">
         <v>19</v>
       </c>
       <c r="F105" s="109">
-        <v>33.247999999999998</v>
+        <v>33.618000000000002</v>
       </c>
       <c r="G105" s="109">
-        <v>35.695</v>
+        <v>36.180999999999997</v>
       </c>
       <c r="H105" s="54">
-        <v>390</v>
-      </c>
-      <c r="I105" s="76">
-        <v>120</v>
-      </c>
+        <v>853</v>
+      </c>
+      <c r="I105" s="76"/>
       <c r="J105" s="56">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="K105" s="55">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="L105" s="55" t="s">
         <v>20</v>
       </c>
       <c r="M105" s="78" t="s">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="N105" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="O105" s="17" t="s">
-        <v>203</v>
-      </c>
+      <c r="O105" s="17"/>
       <c r="P105" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="16">
@@ -7383,25 +7388,25 @@
         <v>200</v>
       </c>
       <c r="C106" s="53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D106" s="53" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E106" s="53" t="s">
         <v>19</v>
       </c>
       <c r="F106" s="109">
-        <v>33.249000000000002</v>
+        <v>33.247999999999998</v>
       </c>
       <c r="G106" s="109">
-        <v>35.652999999999999</v>
+        <v>35.695</v>
       </c>
       <c r="H106" s="54">
-        <v>195</v>
+        <v>390</v>
       </c>
       <c r="I106" s="76">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="J106" s="56">
         <v>1989</v>
@@ -7412,8 +7417,8 @@
       <c r="L106" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="M106" s="77" t="s">
-        <v>205</v>
+      <c r="M106" s="78" t="s">
+        <v>202</v>
       </c>
       <c r="N106" s="20" t="s">
         <v>93</v>
@@ -7422,7 +7427,7 @@
         <v>203</v>
       </c>
       <c r="P106" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107" spans="1:16" ht="16">
@@ -7430,47 +7435,49 @@
         <v>196</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C107" s="53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D107" s="53" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E107" s="53" t="s">
         <v>19</v>
       </c>
       <c r="F107" s="109">
-        <v>34.01</v>
+        <v>33.249000000000002</v>
       </c>
       <c r="G107" s="109">
-        <v>35.828000000000003</v>
+        <v>35.652999999999999</v>
       </c>
       <c r="H107" s="54">
-        <v>1390</v>
-      </c>
-      <c r="I107" s="55">
-        <v>15</v>
+        <v>195</v>
+      </c>
+      <c r="I107" s="76">
+        <v>290</v>
       </c>
       <c r="J107" s="56">
-        <v>2014</v>
+        <v>1989</v>
       </c>
       <c r="K107" s="55">
-        <v>2018</v>
+        <v>1999</v>
       </c>
       <c r="L107" s="55" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="M107" s="77" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N107" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O107" s="17"/>
+        <v>93</v>
+      </c>
+      <c r="O107" s="17" t="s">
+        <v>203</v>
+      </c>
       <c r="P107" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="16">
@@ -7481,24 +7488,26 @@
         <v>206</v>
       </c>
       <c r="C108" s="53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D108" s="53" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E108" s="53" t="s">
         <v>19</v>
       </c>
       <c r="F108" s="109">
-        <v>33.944000000000003</v>
+        <v>34.01</v>
       </c>
       <c r="G108" s="109">
-        <v>35.637999999999998</v>
+        <v>35.828000000000003</v>
       </c>
       <c r="H108" s="54">
-        <v>56</v>
-      </c>
-      <c r="I108" s="55"/>
+        <v>1390</v>
+      </c>
+      <c r="I108" s="55">
+        <v>15</v>
+      </c>
       <c r="J108" s="56">
         <v>2014</v>
       </c>
@@ -7516,105 +7525,103 @@
       </c>
       <c r="O108" s="17"/>
       <c r="P108" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="16">
-      <c r="A109" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C109" s="79">
-        <v>1</v>
-      </c>
-      <c r="D109" s="79" t="s">
-        <v>211</v>
-      </c>
-      <c r="E109" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="F109" s="80">
-        <v>42.651800000000001</v>
-      </c>
-      <c r="G109" s="80">
-        <v>1.52E-2</v>
-      </c>
-      <c r="H109" s="81">
-        <v>2000</v>
-      </c>
-      <c r="I109" s="139">
-        <v>14483</v>
-      </c>
-      <c r="J109" s="83">
+      <c r="A109" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="B109" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="C109" s="53">
+        <v>6</v>
+      </c>
+      <c r="D109" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="E109" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" s="109">
+        <v>33.944000000000003</v>
+      </c>
+      <c r="G109" s="109">
+        <v>35.637999999999998</v>
+      </c>
+      <c r="H109" s="54">
+        <v>56</v>
+      </c>
+      <c r="I109" s="55"/>
+      <c r="J109" s="56">
+        <v>2014</v>
+      </c>
+      <c r="K109" s="55">
         <v>2018</v>
       </c>
-      <c r="K109" s="12">
-        <v>2025</v>
-      </c>
-      <c r="L109" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M109" s="84" t="s">
-        <v>212</v>
+      <c r="L109" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="M109" s="77" t="s">
+        <v>208</v>
       </c>
       <c r="N109" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O109" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="P109" s="102" t="s">
-        <v>356</v>
+      <c r="O109" s="17"/>
+      <c r="P109" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="110" spans="1:16" ht="16">
-      <c r="A110" s="79" t="s">
+      <c r="A110" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B110" s="79" t="s">
-        <v>69</v>
+      <c r="B110" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="C110" s="79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110" s="79" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E110" s="79" t="s">
         <v>19</v>
       </c>
       <c r="F110" s="80">
-        <v>42.890999999999998</v>
+        <v>42.651800000000001</v>
       </c>
       <c r="G110" s="80">
-        <v>1.927</v>
+        <v>1.52E-2</v>
       </c>
       <c r="H110" s="81">
-        <v>100</v>
-      </c>
-      <c r="I110" s="82">
-        <v>125</v>
+        <v>2000</v>
+      </c>
+      <c r="I110" s="139">
+        <v>14483</v>
       </c>
       <c r="J110" s="83">
-        <v>1965</v>
+        <v>2018</v>
       </c>
       <c r="K110" s="12">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="L110" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M110" s="67" t="s">
-        <v>174</v>
+      <c r="M110" s="84" t="s">
+        <v>212</v>
       </c>
       <c r="N110" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O110" s="17"/>
+      <c r="O110" s="17" t="s">
+        <v>121</v>
+      </c>
       <c r="P110" s="102" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="111" spans="1:16" ht="16">
@@ -7625,28 +7632,28 @@
         <v>69</v>
       </c>
       <c r="C111" s="79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D111" s="79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E111" s="79" t="s">
         <v>19</v>
       </c>
       <c r="F111" s="80">
-        <v>42.954999999999998</v>
+        <v>42.890999999999998</v>
       </c>
       <c r="G111" s="80">
-        <v>1.0309999999999999</v>
+        <v>1.927</v>
       </c>
       <c r="H111" s="81">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="I111" s="82">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="J111" s="83">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="K111" s="12">
         <v>2026</v>
@@ -7655,14 +7662,14 @@
         <v>20</v>
       </c>
       <c r="M111" s="67" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="N111" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O111" s="17"/>
       <c r="P111" s="102" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="16">
@@ -7673,28 +7680,28 @@
         <v>69</v>
       </c>
       <c r="C112" s="79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D112" s="79" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E112" s="79" t="s">
         <v>19</v>
       </c>
       <c r="F112" s="80">
-        <v>42.99</v>
+        <v>42.954999999999998</v>
       </c>
       <c r="G112" s="80">
-        <v>1.048</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="H112" s="81">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="I112" s="82">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J112" s="83">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="K112" s="12">
         <v>2026</v>
@@ -7710,7 +7717,7 @@
       </c>
       <c r="O112" s="17"/>
       <c r="P112" s="102" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="16">
@@ -7721,26 +7728,28 @@
         <v>69</v>
       </c>
       <c r="C113" s="79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D113" s="79" t="s">
-        <v>382</v>
+        <v>216</v>
       </c>
       <c r="E113" s="79" t="s">
         <v>19</v>
       </c>
       <c r="F113" s="80">
-        <v>42.843000000000004</v>
+        <v>42.99</v>
       </c>
       <c r="G113" s="80">
-        <v>2.2029999999999998</v>
+        <v>1.048</v>
       </c>
       <c r="H113" s="81">
-        <v>317</v>
-      </c>
-      <c r="I113" s="82"/>
+        <v>500</v>
+      </c>
+      <c r="I113" s="82">
+        <v>11</v>
+      </c>
       <c r="J113" s="83">
-        <v>2002</v>
+        <v>1969</v>
       </c>
       <c r="K113" s="12">
         <v>2026</v>
@@ -7749,7 +7758,7 @@
         <v>20</v>
       </c>
       <c r="M113" s="67" t="s">
-        <v>383</v>
+        <v>215</v>
       </c>
       <c r="N113" s="20" t="s">
         <v>84</v>
@@ -7767,22 +7776,22 @@
         <v>69</v>
       </c>
       <c r="C114" s="79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D114" s="79" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E114" s="79" t="s">
         <v>19</v>
       </c>
       <c r="F114" s="80">
-        <v>42.984000000000002</v>
+        <v>42.843000000000004</v>
       </c>
       <c r="G114" s="80">
-        <v>0.9</v>
+        <v>2.2029999999999998</v>
       </c>
       <c r="H114" s="81">
-        <v>435</v>
+        <v>317</v>
       </c>
       <c r="I114" s="82"/>
       <c r="J114" s="83">
@@ -7795,13 +7804,15 @@
         <v>20</v>
       </c>
       <c r="M114" s="67" t="s">
-        <v>215</v>
+        <v>383</v>
       </c>
       <c r="N114" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O114" s="17"/>
-      <c r="P114" s="102"/>
+      <c r="P114" s="102" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="115" spans="1:16" ht="16">
       <c r="A115" s="79" t="s">
@@ -7811,22 +7822,22 @@
         <v>69</v>
       </c>
       <c r="C115" s="79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D115" s="79" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E115" s="79" t="s">
         <v>19</v>
       </c>
       <c r="F115" s="80">
-        <v>43.031999999999996</v>
+        <v>42.984000000000002</v>
       </c>
       <c r="G115" s="80">
-        <v>0.51300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H115" s="81">
-        <v>525</v>
+        <v>435</v>
       </c>
       <c r="I115" s="82"/>
       <c r="J115" s="83">
@@ -7845,58 +7856,52 @@
         <v>84</v>
       </c>
       <c r="O115" s="17"/>
-      <c r="P115" s="102" t="s">
+      <c r="P115" s="102"/>
+    </row>
+    <row r="116" spans="1:16" ht="16">
+      <c r="A116" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B116" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C116" s="79">
+        <v>7</v>
+      </c>
+      <c r="D116" s="79" t="s">
+        <v>385</v>
+      </c>
+      <c r="E116" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116" s="80">
+        <v>43.031999999999996</v>
+      </c>
+      <c r="G116" s="80">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="H116" s="81">
+        <v>525</v>
+      </c>
+      <c r="I116" s="82"/>
+      <c r="J116" s="83">
+        <v>2002</v>
+      </c>
+      <c r="K116" s="12">
+        <v>2026</v>
+      </c>
+      <c r="L116" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M116" s="67" t="s">
+        <v>215</v>
+      </c>
+      <c r="N116" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O116" s="17"/>
+      <c r="P116" s="102" t="s">
         <v>327</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="16">
-      <c r="A116" s="85" t="s">
-        <v>217</v>
-      </c>
-      <c r="B116" s="85" t="s">
-        <v>218</v>
-      </c>
-      <c r="C116" s="85">
-        <v>1</v>
-      </c>
-      <c r="D116" s="85" t="s">
-        <v>219</v>
-      </c>
-      <c r="E116" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F116" s="113">
-        <v>37.113</v>
-      </c>
-      <c r="G116" s="113">
-        <v>32.140999999999998</v>
-      </c>
-      <c r="H116" s="86">
-        <v>1100</v>
-      </c>
-      <c r="I116" s="87">
-        <v>85</v>
-      </c>
-      <c r="J116" s="88">
-        <v>2003</v>
-      </c>
-      <c r="K116" s="87">
-        <v>2019</v>
-      </c>
-      <c r="L116" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="M116" s="89" t="s">
-        <v>220</v>
-      </c>
-      <c r="N116" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="O116" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="P116" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="16">
@@ -7907,36 +7912,36 @@
         <v>218</v>
       </c>
       <c r="C117" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117" s="85" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E117" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F117" s="113">
-        <v>37.094000000000001</v>
+        <v>37.113</v>
       </c>
       <c r="G117" s="113">
-        <v>30.581</v>
-      </c>
-      <c r="H117" s="87">
-        <v>300</v>
+        <v>32.140999999999998</v>
+      </c>
+      <c r="H117" s="86">
+        <v>1100</v>
       </c>
       <c r="I117" s="87">
-        <v>2000</v>
-      </c>
-      <c r="J117" s="87">
+        <v>85</v>
+      </c>
+      <c r="J117" s="88">
         <v>2003</v>
       </c>
       <c r="K117" s="87">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="L117" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M117" s="90" t="s">
+      <c r="M117" s="89" t="s">
         <v>220</v>
       </c>
       <c r="N117" s="20" t="s">
@@ -7946,7 +7951,7 @@
         <v>221</v>
       </c>
       <c r="P117" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="16">
@@ -7957,44 +7962,46 @@
         <v>218</v>
       </c>
       <c r="C118" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D118" s="85" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E118" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F118" s="113">
-        <v>37.302</v>
+        <v>37.094000000000001</v>
       </c>
       <c r="G118" s="113">
-        <v>31.942</v>
+        <v>30.581</v>
       </c>
       <c r="H118" s="87">
-        <v>1099</v>
+        <v>300</v>
       </c>
       <c r="I118" s="87">
-        <v>70</v>
+        <v>2000</v>
       </c>
       <c r="J118" s="87">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="K118" s="87">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="L118" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M118" s="85" t="s">
-        <v>224</v>
+      <c r="M118" s="90" t="s">
+        <v>220</v>
       </c>
       <c r="N118" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="O118" s="17"/>
+      <c r="O118" s="17" t="s">
+        <v>221</v>
+      </c>
       <c r="P118" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="16">
@@ -8005,46 +8012,44 @@
         <v>218</v>
       </c>
       <c r="C119" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D119" s="85" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E119" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F119" s="113">
-        <v>37.468000000000004</v>
+        <v>37.302</v>
       </c>
       <c r="G119" s="113">
-        <v>34.863</v>
+        <v>31.942</v>
       </c>
       <c r="H119" s="87">
-        <v>840</v>
+        <v>1099</v>
       </c>
       <c r="I119" s="87">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="J119" s="87">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="K119" s="87">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L119" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M119" s="91" t="s">
-        <v>226</v>
+      <c r="M119" s="85" t="s">
+        <v>224</v>
       </c>
       <c r="N119" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="O119" s="17" t="s">
-        <v>221</v>
-      </c>
+      <c r="O119" s="17"/>
       <c r="P119" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="16">
@@ -8055,37 +8060,37 @@
         <v>218</v>
       </c>
       <c r="C120" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D120" s="85" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E120" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F120" s="113">
-        <v>37.771000000000001</v>
+        <v>37.468000000000004</v>
       </c>
       <c r="G120" s="113">
-        <v>35.396000000000001</v>
+        <v>34.863</v>
       </c>
       <c r="H120" s="87">
-        <v>660</v>
+        <v>840</v>
       </c>
       <c r="I120" s="87">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="J120" s="87">
         <v>2011</v>
       </c>
       <c r="K120" s="87">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="L120" s="87" t="s">
         <v>20</v>
       </c>
       <c r="M120" s="91" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N120" s="20" t="s">
         <v>147</v>
@@ -8094,7 +8099,7 @@
         <v>221</v>
       </c>
       <c r="P120" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="16">
@@ -8105,37 +8110,37 @@
         <v>218</v>
       </c>
       <c r="C121" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D121" s="85" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E121" s="85" t="s">
         <v>19</v>
       </c>
       <c r="F121" s="113">
-        <v>38.814999999999998</v>
+        <v>37.771000000000001</v>
       </c>
       <c r="G121" s="113">
-        <v>35.863999999999997</v>
+        <v>35.396000000000001</v>
       </c>
       <c r="H121" s="87">
-        <v>1536</v>
+        <v>660</v>
       </c>
       <c r="I121" s="87">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="J121" s="87">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="K121" s="87">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="L121" s="87" t="s">
         <v>20</v>
       </c>
       <c r="M121" s="91" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N121" s="20" t="s">
         <v>147</v>
@@ -8144,51 +8149,57 @@
         <v>221</v>
       </c>
       <c r="P121" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="16">
+      <c r="A122" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B122" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C122" s="85">
+        <v>6</v>
+      </c>
+      <c r="D122" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="E122" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F122" s="113">
+        <v>38.814999999999998</v>
+      </c>
+      <c r="G122" s="113">
+        <v>35.863999999999997</v>
+      </c>
+      <c r="H122" s="87">
+        <v>1536</v>
+      </c>
+      <c r="I122" s="87">
+        <v>10</v>
+      </c>
+      <c r="J122" s="87">
+        <v>2002</v>
+      </c>
+      <c r="K122" s="87">
+        <v>2019</v>
+      </c>
+      <c r="L122" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M122" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="N122" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O122" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="P122" t="s">
         <v>333</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="16">
-      <c r="A122" s="92" t="s">
-        <v>231</v>
-      </c>
-      <c r="B122" s="92" t="s">
-        <v>232</v>
-      </c>
-      <c r="C122" s="92">
-        <v>1</v>
-      </c>
-      <c r="D122" s="92" t="s">
-        <v>233</v>
-      </c>
-      <c r="E122" s="92"/>
-      <c r="F122" s="114">
-        <v>31.375</v>
-      </c>
-      <c r="G122" s="115">
-        <v>49.84</v>
-      </c>
-      <c r="H122" s="93">
-        <v>490</v>
-      </c>
-      <c r="I122" s="94"/>
-      <c r="J122" s="95">
-        <v>2003</v>
-      </c>
-      <c r="K122" s="96">
-        <v>2011</v>
-      </c>
-      <c r="L122" s="96" t="s">
-        <v>20</v>
-      </c>
-      <c r="M122" s="97" t="s">
-        <v>234</v>
-      </c>
-      <c r="N122" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="O122" s="17"/>
-      <c r="P122" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="16">
@@ -8199,27 +8210,27 @@
         <v>232</v>
       </c>
       <c r="C123" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" s="92" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E123" s="92"/>
       <c r="F123" s="114">
-        <v>31.256</v>
+        <v>31.375</v>
       </c>
       <c r="G123" s="115">
-        <v>49.968000000000004</v>
+        <v>49.84</v>
       </c>
       <c r="H123" s="93">
-        <v>675</v>
+        <v>490</v>
       </c>
       <c r="I123" s="94"/>
       <c r="J123" s="95">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="K123" s="96">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="L123" s="96" t="s">
         <v>20</v>
@@ -8232,7 +8243,7 @@
       </c>
       <c r="O123" s="17"/>
       <c r="P123" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="16">
@@ -8243,32 +8254,30 @@
         <v>232</v>
       </c>
       <c r="C124" s="92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="E124" s="92" t="s">
-        <v>19</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="E124" s="92"/>
       <c r="F124" s="114">
-        <v>34.39</v>
-      </c>
-      <c r="G124" s="114">
-        <v>47.436999999999998</v>
-      </c>
-      <c r="H124" s="96">
-        <v>1290</v>
-      </c>
-      <c r="I124" s="96"/>
-      <c r="J124" s="96">
-        <v>1970</v>
+        <v>31.256</v>
+      </c>
+      <c r="G124" s="115">
+        <v>49.968000000000004</v>
+      </c>
+      <c r="H124" s="93">
+        <v>675</v>
+      </c>
+      <c r="I124" s="94"/>
+      <c r="J124" s="95">
+        <v>2010</v>
       </c>
       <c r="K124" s="96">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="L124" s="96" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="M124" s="97" t="s">
         <v>234</v>
@@ -8276,9 +8285,9 @@
       <c r="N124" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="O124" s="98"/>
+      <c r="O124" s="17"/>
       <c r="P124" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="125" spans="1:16" ht="16">
@@ -8289,29 +8298,29 @@
         <v>232</v>
       </c>
       <c r="C125" s="92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D125" s="92" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E125" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F125" s="114">
-        <v>32.500999999999998</v>
+        <v>34.39</v>
       </c>
       <c r="G125" s="114">
-        <v>50.215000000000003</v>
+        <v>47.436999999999998</v>
       </c>
       <c r="H125" s="96">
-        <v>2220</v>
+        <v>1290</v>
       </c>
       <c r="I125" s="96"/>
       <c r="J125" s="96">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="K125" s="96">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="L125" s="96" t="s">
         <v>112</v>
@@ -8324,7 +8333,7 @@
       </c>
       <c r="O125" s="98"/>
       <c r="P125" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="16">
@@ -8335,29 +8344,29 @@
         <v>232</v>
       </c>
       <c r="C126" s="92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" s="92" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E126" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="114">
-        <v>32.216999999999999</v>
+        <v>32.500999999999998</v>
       </c>
       <c r="G126" s="114">
-        <v>50.543999999999997</v>
+        <v>50.215000000000003</v>
       </c>
       <c r="H126" s="96">
-        <v>2016</v>
-      </c>
-      <c r="I126" s="94"/>
+        <v>2220</v>
+      </c>
+      <c r="I126" s="96"/>
       <c r="J126" s="96">
         <v>1998</v>
       </c>
       <c r="K126" s="96">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="L126" s="96" t="s">
         <v>112</v>
@@ -8370,7 +8379,7 @@
       </c>
       <c r="O126" s="98"/>
       <c r="P126" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="127" spans="1:16" ht="16">
@@ -8381,29 +8390,29 @@
         <v>232</v>
       </c>
       <c r="C127" s="92">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D127" s="92" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E127" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F127" s="114">
-        <v>29.783000000000001</v>
-      </c>
-      <c r="G127" s="115">
-        <v>51.582999999999998</v>
-      </c>
-      <c r="H127" s="93">
-        <v>820</v>
+        <v>32.216999999999999</v>
+      </c>
+      <c r="G127" s="114">
+        <v>50.543999999999997</v>
+      </c>
+      <c r="H127" s="96">
+        <v>2016</v>
       </c>
       <c r="I127" s="94"/>
-      <c r="J127" s="95">
-        <v>1984</v>
+      <c r="J127" s="96">
+        <v>1998</v>
       </c>
       <c r="K127" s="96">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="L127" s="96" t="s">
         <v>112</v>
@@ -8412,11 +8421,11 @@
         <v>234</v>
       </c>
       <c r="N127" s="20" t="s">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="O127" s="98"/>
       <c r="P127" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="16">
@@ -8424,45 +8433,45 @@
         <v>231</v>
       </c>
       <c r="B128" s="92" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C128" s="92">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D128" s="92" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E128" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F128" s="114">
-        <v>35.6</v>
+        <v>29.783000000000001</v>
       </c>
       <c r="G128" s="115">
-        <v>45.4</v>
+        <v>51.582999999999998</v>
       </c>
       <c r="H128" s="93">
-        <v>1625</v>
+        <v>820</v>
       </c>
       <c r="I128" s="94"/>
       <c r="J128" s="95">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="K128" s="96">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="L128" s="96" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="M128" s="97" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="N128" s="20" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="O128" s="98"/>
-      <c r="P128" s="103" t="s">
-        <v>359</v>
+      <c r="P128" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="16">
@@ -8473,29 +8482,29 @@
         <v>241</v>
       </c>
       <c r="C129" s="92">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D129" s="92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E129" s="92" t="s">
         <v>19</v>
       </c>
       <c r="F129" s="114">
-        <v>35.380000000000003</v>
+        <v>35.6</v>
       </c>
       <c r="G129" s="115">
-        <v>45.83</v>
+        <v>45.4</v>
       </c>
       <c r="H129" s="93">
-        <v>515</v>
+        <v>1625</v>
       </c>
       <c r="I129" s="94"/>
       <c r="J129" s="95">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="K129" s="96">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="L129" s="96" t="s">
         <v>20</v>
@@ -8507,34 +8516,80 @@
         <v>84</v>
       </c>
       <c r="O129" s="98"/>
-      <c r="P129" s="102" t="s">
+      <c r="P129" s="103" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="16">
+      <c r="A130" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B130" s="92" t="s">
+        <v>241</v>
+      </c>
+      <c r="C130" s="92">
+        <v>8</v>
+      </c>
+      <c r="D130" s="92" t="s">
+        <v>243</v>
+      </c>
+      <c r="E130" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130" s="114">
+        <v>35.380000000000003</v>
+      </c>
+      <c r="G130" s="115">
+        <v>45.83</v>
+      </c>
+      <c r="H130" s="93">
+        <v>515</v>
+      </c>
+      <c r="I130" s="94"/>
+      <c r="J130" s="95">
+        <v>2004</v>
+      </c>
+      <c r="K130" s="96">
+        <v>2006</v>
+      </c>
+      <c r="L130" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="M130" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="N130" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O130" s="98"/>
+      <c r="P130" s="102" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="14">
-      <c r="D130" s="99"/>
-    </row>
     <row r="131" spans="1:16" ht="14">
-      <c r="D131" s="100"/>
-      <c r="E131" s="101"/>
-      <c r="F131" s="100"/>
-      <c r="G131" s="101"/>
-      <c r="H131" s="101"/>
-      <c r="I131" s="101"/>
-      <c r="J131" s="101"/>
-      <c r="K131" s="100"/>
-      <c r="L131" s="100"/>
-      <c r="M131" s="101"/>
-      <c r="N131" s="100"/>
+      <c r="D131" s="99"/>
+    </row>
+    <row r="132" spans="1:16" ht="14">
+      <c r="D132" s="100"/>
+      <c r="E132" s="101"/>
+      <c r="F132" s="100"/>
+      <c r="G132" s="101"/>
+      <c r="H132" s="101"/>
+      <c r="I132" s="101"/>
+      <c r="J132" s="101"/>
+      <c r="K132" s="100"/>
+      <c r="L132" s="100"/>
+      <c r="M132" s="101"/>
+      <c r="N132" s="100"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M121" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M120" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="M119" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="M117" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="M116" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="M109" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M122" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M121" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M120" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M118" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M117" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M110" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="M95" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="M94" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="M93" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
